--- a/Duty.xlsx
+++ b/Duty.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD786E6-2111-4A64-AA4F-122A2065F248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{451E6CA7-5CED-4826-8D79-CD626CF9F62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="70">
   <si>
     <t>Morning</t>
   </si>
@@ -256,6 +256,9 @@
   <si>
     <t>Alauddin</t>
   </si>
+  <si>
+    <t>01723504940</t>
+  </si>
 </sst>
 </file>
 
@@ -379,19 +382,19 @@
     <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -786,7 +789,7 @@
       <c r="A2" s="25">
         <v>46113</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -822,7 +825,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="25"/>
-      <c r="B3" s="21"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="3" t="s">
         <v>36</v>
       </c>
@@ -844,7 +847,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
-      <c r="B4" s="21"/>
+      <c r="B4" s="22"/>
       <c r="C4" s="6" t="s">
         <v>40</v>
       </c>
@@ -866,7 +869,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="25"/>
-      <c r="B5" s="21"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="3" t="s">
         <v>18</v>
       </c>
@@ -888,7 +891,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="25"/>
-      <c r="B6" s="21"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="3" t="s">
         <v>37</v>
       </c>
@@ -902,9 +905,12 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="25"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="24" t="s">
+      <c r="B7" s="22"/>
+      <c r="C7" s="20" t="s">
         <v>66</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="17"/>
@@ -915,7 +921,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="25"/>
-      <c r="B8" s="21"/>
+      <c r="B8" s="22"/>
       <c r="C8" s="5" t="s">
         <v>21</v>
       </c>
@@ -931,7 +937,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="25"/>
-      <c r="B9" s="21"/>
+      <c r="B9" s="22"/>
       <c r="E9" s="3"/>
       <c r="F9" s="17"/>
       <c r="G9" s="3"/>
@@ -943,7 +949,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="25"/>
-      <c r="B10" s="21"/>
+      <c r="B10" s="22"/>
       <c r="E10" s="3"/>
       <c r="F10" s="17"/>
       <c r="G10" s="3"/>
@@ -955,7 +961,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="25"/>
-      <c r="B11" s="21"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="5"/>
       <c r="D11" s="13"/>
       <c r="E11" s="3"/>
@@ -969,7 +975,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="25"/>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -1005,7 +1011,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="25"/>
-      <c r="B13" s="22"/>
+      <c r="B13" s="24"/>
       <c r="C13" s="3" t="s">
         <v>14</v>
       </c>
@@ -1027,7 +1033,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="25"/>
-      <c r="B14" s="22"/>
+      <c r="B14" s="24"/>
       <c r="C14" s="6" t="s">
         <v>41</v>
       </c>
@@ -1049,7 +1055,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="25"/>
-      <c r="B15" s="22"/>
+      <c r="B15" s="24"/>
       <c r="C15" s="6" t="s">
         <v>13</v>
       </c>
@@ -1071,7 +1077,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="25"/>
-      <c r="B16" s="22"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="6" t="s">
         <v>42</v>
       </c>
@@ -1089,7 +1095,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="25"/>
-      <c r="B17" s="22"/>
+      <c r="B17" s="24"/>
       <c r="C17" s="8" t="str">
         <f>E5</f>
         <v>Driver - Shetu</v>
@@ -1109,7 +1115,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="25"/>
-      <c r="B18" s="22"/>
+      <c r="B18" s="24"/>
       <c r="E18" s="6"/>
       <c r="F18" s="18"/>
       <c r="G18" s="6"/>
@@ -1121,7 +1127,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="25"/>
-      <c r="B19" s="22"/>
+      <c r="B19" s="24"/>
       <c r="C19" s="8"/>
       <c r="D19" s="14"/>
       <c r="E19" s="6"/>
@@ -1135,7 +1141,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="25"/>
-      <c r="B20" s="22"/>
+      <c r="B20" s="24"/>
       <c r="C20" s="8"/>
       <c r="D20" s="14"/>
       <c r="E20" s="6"/>
@@ -1149,7 +1155,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="25"/>
-      <c r="B21" s="22"/>
+      <c r="B21" s="24"/>
       <c r="C21" s="8"/>
       <c r="D21" s="14"/>
       <c r="G21" s="6"/>
@@ -1161,7 +1167,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="25"/>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C22" s="9"/>
@@ -1193,7 +1199,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="25"/>
-      <c r="B23" s="20"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="9"/>
       <c r="D23" s="15"/>
       <c r="E23" s="3" t="s">
@@ -1211,7 +1217,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="25"/>
-      <c r="B24" s="20"/>
+      <c r="B24" s="21"/>
       <c r="C24" s="9"/>
       <c r="D24" s="15"/>
       <c r="E24" s="3" t="s">
@@ -1229,7 +1235,7 @@
     </row>
     <row r="25" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="25"/>
-      <c r="B25" s="20"/>
+      <c r="B25" s="21"/>
       <c r="C25" s="9"/>
       <c r="D25" s="15"/>
       <c r="E25" s="5" t="s">
@@ -1249,7 +1255,7 @@
       <c r="A26" s="23">
         <v>46114</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C26" s="3" t="str">
@@ -1261,55 +1267,55 @@
         <v>01703409900</v>
       </c>
       <c r="E26" s="11" t="str">
-        <f>E2</f>
+        <f t="shared" ref="E26:L26" si="0">E2</f>
         <v>Rakib (LM)</v>
       </c>
       <c r="F26" s="19" t="str">
-        <f>F2</f>
+        <f t="shared" si="0"/>
         <v>01767032267</v>
       </c>
       <c r="G26" s="3" t="str">
-        <f>G2</f>
+        <f t="shared" si="0"/>
         <v>Shawon Dass</v>
       </c>
       <c r="H26" s="19" t="str">
-        <f>H2</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I26" s="3" t="str">
-        <f>I2</f>
+        <f t="shared" si="0"/>
         <v>Salim Reza</v>
       </c>
       <c r="J26" s="19" t="str">
-        <f>J2</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K26" s="6" t="str">
-        <f>K2</f>
+        <f t="shared" si="0"/>
         <v>Inul Haque</v>
       </c>
       <c r="L26" s="19" t="str">
-        <f>L2</f>
+        <f t="shared" si="0"/>
         <v>02588855910</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="23"/>
-      <c r="B27" s="21"/>
+      <c r="B27" s="22"/>
       <c r="C27" s="3" t="str">
-        <f t="shared" ref="C27:D31" si="0">C13</f>
+        <f t="shared" ref="C27:D30" si="1">C13</f>
         <v>Abdus Sattar (LM)</v>
       </c>
       <c r="D27" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>01718676281</v>
       </c>
       <c r="E27" s="11" t="str">
-        <f t="shared" ref="E27:F29" si="1">E3</f>
+        <f t="shared" ref="E27:F29" si="2">E3</f>
         <v>Nabi (LH)</v>
       </c>
       <c r="F27" s="19" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>01736352528</v>
       </c>
       <c r="G27" s="3"/>
@@ -1321,21 +1327,21 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="23"/>
-      <c r="B28" s="21"/>
+      <c r="B28" s="22"/>
       <c r="C28" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Sazzad  (LM)</v>
       </c>
       <c r="D28" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>01719106824</v>
       </c>
       <c r="E28" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Anowar (LEM)</v>
       </c>
       <c r="F28" s="19" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>01712439152</v>
       </c>
       <c r="G28" s="3"/>
@@ -1347,21 +1353,21 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="23"/>
-      <c r="B29" s="21"/>
+      <c r="B29" s="22"/>
       <c r="C29" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Jonny (LH)</v>
       </c>
       <c r="D29" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>01712441588</v>
       </c>
       <c r="E29" s="11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Driver - Shetu</v>
       </c>
       <c r="F29" s="19" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>01719034964</v>
       </c>
       <c r="G29" s="3"/>
@@ -1373,13 +1379,13 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="23"/>
-      <c r="B30" s="21"/>
+      <c r="B30" s="22"/>
       <c r="C30" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Nazmul (LEM)</v>
       </c>
       <c r="D30" s="13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>01914595295</v>
       </c>
       <c r="G30" s="3"/>
@@ -1389,14 +1395,13 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="23"/>
-      <c r="B31" s="21"/>
-      <c r="C31" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Driver - Shetu</v>
+      <c r="B31" s="22"/>
+      <c r="C31" s="3" t="str" cm="1">
+        <f t="array" ref="C31:D31">E25:F25</f>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D31" s="13" t="str">
-        <f t="shared" si="0"/>
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="17"/>
@@ -1407,7 +1412,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="23"/>
-      <c r="B32" s="21"/>
+      <c r="B32" s="22"/>
       <c r="C32" s="5"/>
       <c r="D32" s="17"/>
       <c r="E32" s="3"/>
@@ -1419,7 +1424,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="23"/>
-      <c r="B33" s="21"/>
+      <c r="B33" s="22"/>
       <c r="E33" s="3"/>
       <c r="F33" s="17"/>
       <c r="G33" s="3"/>
@@ -1431,7 +1436,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="23"/>
-      <c r="B34" s="21"/>
+      <c r="B34" s="22"/>
       <c r="E34" s="3"/>
       <c r="F34" s="17"/>
       <c r="G34" s="3"/>
@@ -1443,7 +1448,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="23"/>
-      <c r="B35" s="21"/>
+      <c r="B35" s="22"/>
       <c r="C35" s="5"/>
       <c r="D35" s="13"/>
       <c r="E35" s="3"/>
@@ -1457,7 +1462,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="23"/>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C36" s="6" t="str">
@@ -1469,31 +1474,31 @@
         <v>01758212103</v>
       </c>
       <c r="E36" s="3" t="str">
-        <f>E12</f>
+        <f t="shared" ref="E36:K36" si="3">E12</f>
         <v>Maruf Hossain (LM)</v>
       </c>
       <c r="F36" s="13" t="str">
-        <f>F12</f>
+        <f t="shared" si="3"/>
         <v>01943368198</v>
       </c>
       <c r="G36" s="6" t="str">
-        <f>G12</f>
+        <f t="shared" si="3"/>
         <v>Alauddin</v>
       </c>
       <c r="H36" s="19" t="str">
-        <f>H12</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I36" s="6" t="str">
-        <f>I12</f>
+        <f t="shared" si="3"/>
         <v>Moin Uddin</v>
       </c>
       <c r="J36" s="19" t="str">
-        <f>J12</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="K36" s="11" t="str">
-        <f>K12</f>
+        <f t="shared" si="3"/>
         <v>Masud Rana</v>
       </c>
       <c r="L36" s="19" t="str">
@@ -1503,21 +1508,21 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="23"/>
-      <c r="B37" s="22"/>
+      <c r="B37" s="24"/>
       <c r="C37" s="6" t="str">
-        <f t="shared" ref="C37:D42" si="2">C3</f>
+        <f t="shared" ref="C37:D41" si="4">C3</f>
         <v>Monzur Kader (LM)</v>
       </c>
       <c r="D37" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>01705614054</v>
       </c>
       <c r="E37" s="3" t="str">
-        <f t="shared" ref="E37:F37" si="3">E13</f>
+        <f t="shared" ref="E37:F37" si="5">E13</f>
         <v>Sahjahan (LEM)</v>
       </c>
       <c r="F37" s="13" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>01724267460</v>
       </c>
       <c r="G37" s="6"/>
@@ -1529,21 +1534,21 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="23"/>
-      <c r="B38" s="22"/>
+      <c r="B38" s="24"/>
       <c r="C38" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Mosaddek  (LM)</v>
       </c>
       <c r="D38" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>01674272353</v>
       </c>
       <c r="E38" s="3" t="str">
-        <f t="shared" ref="E38:F38" si="4">E14</f>
+        <f t="shared" ref="E38:F38" si="6">E14</f>
         <v>Fuad (LH)</v>
       </c>
       <c r="F38" s="13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>01718279112</v>
       </c>
       <c r="G38" s="6"/>
@@ -1555,21 +1560,21 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="23"/>
-      <c r="B39" s="22"/>
+      <c r="B39" s="24"/>
       <c r="C39" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Abdus Salam (LM)</v>
       </c>
       <c r="D39" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>01756101919</v>
       </c>
       <c r="E39" s="3" t="str">
-        <f t="shared" ref="E39:F39" si="5">E15</f>
+        <f t="shared" ref="E39:F39" si="7">E15</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="F39" s="13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>01748127818</v>
       </c>
       <c r="G39" s="6"/>
@@ -1581,13 +1586,13 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="23"/>
-      <c r="B40" s="22"/>
+      <c r="B40" s="24"/>
       <c r="C40" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Salim Reza-2 (LH)</v>
       </c>
       <c r="D40" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>01719531782</v>
       </c>
       <c r="E40" s="6"/>
@@ -1601,14 +1606,14 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="23"/>
-      <c r="B41" s="22"/>
+      <c r="B41" s="24"/>
       <c r="C41" s="6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D41" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
+      <c r="D41" s="14" t="str">
+        <f t="shared" si="4"/>
+        <v>01723504940</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="18"/>
@@ -1621,14 +1626,13 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="23"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v>Driver - Hasan</v>
+      <c r="B42" s="24"/>
+      <c r="C42" s="6" t="str" cm="1">
+        <f t="array" ref="C42:D42">E29:F29</f>
+        <v>Driver - Shetu</v>
       </c>
       <c r="D42" s="14" t="str">
-        <f t="shared" si="2"/>
-        <v>01730824934</v>
+        <v>01719034964</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="18"/>
@@ -1641,7 +1645,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="23"/>
-      <c r="B43" s="22"/>
+      <c r="B43" s="24"/>
       <c r="C43" s="8"/>
       <c r="D43" s="14"/>
       <c r="E43" s="6"/>
@@ -1655,7 +1659,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="23"/>
-      <c r="B44" s="22"/>
+      <c r="B44" s="24"/>
       <c r="C44" s="8"/>
       <c r="D44" s="14"/>
       <c r="E44" s="6"/>
@@ -1669,7 +1673,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="23"/>
-      <c r="B45" s="22"/>
+      <c r="B45" s="24"/>
       <c r="C45" s="8"/>
       <c r="D45" s="14"/>
       <c r="G45" s="6"/>
@@ -1681,55 +1685,55 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="23"/>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="15"/>
       <c r="E46" s="3" t="str">
-        <f>E22</f>
+        <f t="shared" ref="E46:L46" si="8">E22</f>
         <v>Sumon (LM)</v>
       </c>
       <c r="F46" s="17" t="str">
-        <f>F22</f>
+        <f t="shared" si="8"/>
         <v>01726258394</v>
       </c>
       <c r="G46" s="11" t="str">
-        <f>G22</f>
+        <f t="shared" si="8"/>
         <v>Abdur Rafique</v>
       </c>
       <c r="H46" s="19" t="str">
-        <f>H22</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I46" s="11" t="str">
-        <f>I22</f>
+        <f t="shared" si="8"/>
         <v>Abul Kalam Azad</v>
       </c>
       <c r="J46" s="19" t="str">
-        <f>J22</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K46" s="3" t="str">
-        <f>K22</f>
+        <f t="shared" si="8"/>
         <v>Monzur Ahmed</v>
       </c>
       <c r="L46" s="19" t="str">
-        <f>L22</f>
+        <f t="shared" si="8"/>
         <v>02588855910</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="23"/>
-      <c r="B47" s="20"/>
+      <c r="B47" s="21"/>
       <c r="C47" s="9"/>
       <c r="D47" s="15"/>
       <c r="E47" s="3" t="str">
-        <f t="shared" ref="E47:F47" si="6">E23</f>
+        <f t="shared" ref="E47:F47" si="9">E23</f>
         <v>Arafat (LH)</v>
       </c>
       <c r="F47" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>01755149115</v>
       </c>
       <c r="G47" s="11"/>
@@ -1741,15 +1745,15 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="23"/>
-      <c r="B48" s="20"/>
+      <c r="B48" s="21"/>
       <c r="C48" s="9"/>
       <c r="D48" s="15"/>
       <c r="E48" s="3" t="str">
-        <f t="shared" ref="E48:F48" si="7">E24</f>
+        <f t="shared" ref="E48:F48" si="10">E24</f>
         <v>Mamun (LH)</v>
       </c>
       <c r="F48" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>01718106022</v>
       </c>
       <c r="G48" s="11"/>
@@ -1761,15 +1765,15 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="23"/>
-      <c r="B49" s="20"/>
+      <c r="B49" s="21"/>
       <c r="C49" s="9"/>
       <c r="D49" s="15"/>
       <c r="E49" s="3" t="str">
-        <f t="shared" ref="E49:F49" si="8">E25</f>
+        <f t="shared" ref="E49:F49" si="11">E25</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="F49" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>01730824934</v>
       </c>
       <c r="G49" s="11"/>
@@ -1783,7 +1787,7 @@
       <c r="A50" s="23">
         <v>46115</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C50" s="3" t="str" cm="1">
@@ -1793,12 +1797,12 @@
       <c r="D50" s="13" t="str">
         <v>01703409900</v>
       </c>
-      <c r="E50" s="11" t="str" cm="1">
-        <f t="array" ref="E50:F53">E46:F49</f>
-        <v>Sumon (LM)</v>
-      </c>
-      <c r="F50" s="19" t="str">
-        <v>01726258394</v>
+      <c r="E50" s="3" t="str" cm="1">
+        <f t="array" ref="E50:F53">E36:F39</f>
+        <v>Maruf Hossain (LM)</v>
+      </c>
+      <c r="F50" s="17" t="str">
+        <v>01943368198</v>
       </c>
       <c r="G50" s="3" t="str" cm="1">
         <f t="array" ref="G50:H50">G36:H36</f>
@@ -1824,18 +1828,18 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="23"/>
-      <c r="B51" s="21"/>
+      <c r="B51" s="22"/>
       <c r="C51" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
       <c r="D51" s="13" t="str">
         <v>01718676281</v>
       </c>
-      <c r="E51" s="11" t="str">
-        <v>Arafat (LH)</v>
-      </c>
-      <c r="F51" s="19" t="str">
-        <v>01755149115</v>
+      <c r="E51" s="3" t="str">
+        <v>Sahjahan (LEM)</v>
+      </c>
+      <c r="F51" s="17" t="str">
+        <v>01724267460</v>
       </c>
       <c r="G51" s="3"/>
       <c r="H51" s="4"/>
@@ -1846,18 +1850,18 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="23"/>
-      <c r="B52" s="21"/>
+      <c r="B52" s="22"/>
       <c r="C52" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
       <c r="D52" s="13" t="str">
         <v>01719106824</v>
       </c>
-      <c r="E52" s="11" t="str">
-        <v>Mamun (LH)</v>
-      </c>
-      <c r="F52" s="19" t="str">
-        <v>01718106022</v>
+      <c r="E52" s="3" t="str">
+        <v>Fuad (LH)</v>
+      </c>
+      <c r="F52" s="17" t="str">
+        <v>01718279112</v>
       </c>
       <c r="G52" s="3"/>
       <c r="H52" s="4"/>
@@ -1868,18 +1872,18 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="23"/>
-      <c r="B53" s="21"/>
+      <c r="B53" s="22"/>
       <c r="C53" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
       <c r="D53" s="13" t="str">
         <v>01712441588</v>
       </c>
-      <c r="E53" s="11" t="str">
-        <v>Driver - Hasan</v>
-      </c>
-      <c r="F53" s="19" t="str">
-        <v>01730824934</v>
+      <c r="E53" s="3" t="str">
+        <v>Driver - Noyon</v>
+      </c>
+      <c r="F53" s="17" t="str">
+        <v>01748127818</v>
       </c>
       <c r="G53" s="3"/>
       <c r="H53" s="4"/>
@@ -1890,7 +1894,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="23"/>
-      <c r="B54" s="21"/>
+      <c r="B54" s="22"/>
       <c r="C54" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -1904,7 +1908,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="23"/>
-      <c r="B55" s="21"/>
+      <c r="B55" s="22"/>
       <c r="C55" s="3"/>
       <c r="D55" s="13"/>
       <c r="E55" s="3"/>
@@ -1916,7 +1920,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="23"/>
-      <c r="B56" s="21"/>
+      <c r="B56" s="22"/>
       <c r="C56" s="5" t="str">
         <f>E49</f>
         <v>Driver - Hasan</v>
@@ -1934,7 +1938,7 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="23"/>
-      <c r="B57" s="21"/>
+      <c r="B57" s="22"/>
       <c r="E57" s="3"/>
       <c r="F57" s="17"/>
       <c r="G57" s="3"/>
@@ -1946,7 +1950,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="23"/>
-      <c r="B58" s="21"/>
+      <c r="B58" s="22"/>
       <c r="E58" s="3"/>
       <c r="F58" s="17"/>
       <c r="G58" s="3"/>
@@ -1958,7 +1962,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="23"/>
-      <c r="B59" s="21"/>
+      <c r="B59" s="22"/>
       <c r="C59" s="5"/>
       <c r="D59" s="13"/>
       <c r="E59" s="3"/>
@@ -1972,7 +1976,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="23"/>
-      <c r="B60" s="22" t="s">
+      <c r="B60" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C60" s="6" t="str" cm="1">
@@ -1982,12 +1986,12 @@
       <c r="D60" s="14" t="str">
         <v>01758212103</v>
       </c>
-      <c r="E60" s="3" t="str" cm="1">
-        <f t="array" ref="E60:F63">E26:F29</f>
-        <v>Rakib (LM)</v>
-      </c>
-      <c r="F60" s="13" t="str">
-        <v>01767032267</v>
+      <c r="E60" s="11" t="str" cm="1">
+        <f t="array" ref="E60:F63">E46:F49</f>
+        <v>Sumon (LM)</v>
+      </c>
+      <c r="F60" s="19" t="str">
+        <v>01726258394</v>
       </c>
       <c r="G60" s="6" t="str" cm="1">
         <f t="array" ref="G60:H60">G46:H46</f>
@@ -2013,18 +2017,18 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="23"/>
-      <c r="B61" s="22"/>
+      <c r="B61" s="24"/>
       <c r="C61" s="6" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
       <c r="D61" s="14" t="str">
         <v>01705614054</v>
       </c>
-      <c r="E61" s="3" t="str">
-        <v>Nabi (LH)</v>
-      </c>
-      <c r="F61" s="13" t="str">
-        <v>01736352528</v>
+      <c r="E61" s="11" t="str">
+        <v>Arafat (LH)</v>
+      </c>
+      <c r="F61" s="19" t="str">
+        <v>01755149115</v>
       </c>
       <c r="G61" s="6"/>
       <c r="H61" s="7"/>
@@ -2039,18 +2043,18 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="23"/>
-      <c r="B62" s="22"/>
+      <c r="B62" s="24"/>
       <c r="C62" s="6" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
       <c r="D62" s="14" t="str">
         <v>01674272353</v>
       </c>
-      <c r="E62" s="3" t="str">
-        <v>Anowar (LEM)</v>
-      </c>
-      <c r="F62" s="13" t="str">
-        <v>01712439152</v>
+      <c r="E62" s="11" t="str">
+        <v>Mamun (LH)</v>
+      </c>
+      <c r="F62" s="19" t="str">
+        <v>01718106022</v>
       </c>
       <c r="G62" s="6"/>
       <c r="H62" s="7"/>
@@ -2061,18 +2065,18 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="23"/>
-      <c r="B63" s="22"/>
+      <c r="B63" s="24"/>
       <c r="C63" s="6" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
       <c r="D63" s="14" t="str">
         <v>01756101919</v>
       </c>
-      <c r="E63" s="3" t="str">
-        <v>Driver - Shetu</v>
-      </c>
-      <c r="F63" s="13" t="str">
-        <v>01719034964</v>
+      <c r="E63" s="11" t="str">
+        <v>Driver - Hasan</v>
+      </c>
+      <c r="F63" s="19" t="str">
+        <v>01730824934</v>
       </c>
       <c r="G63" s="6"/>
       <c r="H63" s="7"/>
@@ -2083,7 +2087,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="23"/>
-      <c r="B64" s="22"/>
+      <c r="B64" s="24"/>
       <c r="C64" s="6" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -2101,12 +2105,12 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="23"/>
-      <c r="B65" s="22"/>
+      <c r="B65" s="24"/>
       <c r="C65" s="6" t="str">
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D65" s="14">
-        <v>0</v>
+      <c r="D65" s="14" t="str">
+        <v>01723504940</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="18"/>
@@ -2119,9 +2123,9 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="23"/>
-      <c r="B66" s="22"/>
+      <c r="B66" s="24"/>
       <c r="C66" s="6" t="str" cm="1">
-        <f t="array" ref="C66:D66">E53:F53</f>
+        <f t="array" ref="C66:D66">E63:F63</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="D66" s="14" t="str">
@@ -2138,7 +2142,7 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="23"/>
-      <c r="B67" s="22"/>
+      <c r="B67" s="24"/>
       <c r="C67" s="8"/>
       <c r="D67" s="14"/>
       <c r="E67" s="6"/>
@@ -2152,7 +2156,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="23"/>
-      <c r="B68" s="22"/>
+      <c r="B68" s="24"/>
       <c r="C68" s="8"/>
       <c r="D68" s="14"/>
       <c r="E68" s="6"/>
@@ -2166,7 +2170,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="23"/>
-      <c r="B69" s="22"/>
+      <c r="B69" s="24"/>
       <c r="C69" s="8"/>
       <c r="D69" s="14"/>
       <c r="G69" s="6"/>
@@ -2178,17 +2182,17 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="23"/>
-      <c r="B70" s="20" t="s">
+      <c r="B70" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="15"/>
       <c r="E70" s="3" t="str" cm="1">
-        <f t="array" ref="E70:F73">E36:F39</f>
-        <v>Maruf Hossain (LM)</v>
-      </c>
-      <c r="F70" s="17" t="str">
-        <v>01943368198</v>
+        <f t="array" ref="E70:F73">E26:F29</f>
+        <v>Rakib (LM)</v>
+      </c>
+      <c r="F70" s="13" t="str">
+        <v>01767032267</v>
       </c>
       <c r="G70" s="11" t="str" cm="1">
         <f t="array" ref="G70:H70">G26:H26</f>
@@ -2214,14 +2218,14 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="23"/>
-      <c r="B71" s="20"/>
+      <c r="B71" s="21"/>
       <c r="C71" s="9"/>
       <c r="D71" s="15"/>
       <c r="E71" s="3" t="str">
-        <v>Sahjahan (LEM)</v>
-      </c>
-      <c r="F71" s="17" t="str">
-        <v>01724267460</v>
+        <v>Nabi (LH)</v>
+      </c>
+      <c r="F71" s="13" t="str">
+        <v>01736352528</v>
       </c>
       <c r="G71" s="11"/>
       <c r="H71" s="10"/>
@@ -2232,14 +2236,14 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="23"/>
-      <c r="B72" s="20"/>
+      <c r="B72" s="21"/>
       <c r="C72" s="9"/>
       <c r="D72" s="15"/>
       <c r="E72" s="3" t="str">
-        <v>Fuad (LH)</v>
-      </c>
-      <c r="F72" s="17" t="str">
-        <v>01718279112</v>
+        <v>Anowar (LEM)</v>
+      </c>
+      <c r="F72" s="13" t="str">
+        <v>01712439152</v>
       </c>
       <c r="G72" s="11"/>
       <c r="H72" s="10"/>
@@ -2250,14 +2254,14 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="23"/>
-      <c r="B73" s="20"/>
+      <c r="B73" s="21"/>
       <c r="C73" s="9"/>
       <c r="D73" s="15"/>
       <c r="E73" s="3" t="str">
-        <v>Driver - Noyon</v>
-      </c>
-      <c r="F73" s="17" t="str">
-        <v>01748127818</v>
+        <v>Driver - Shetu</v>
+      </c>
+      <c r="F73" s="13" t="str">
+        <v>01719034964</v>
       </c>
       <c r="G73" s="11"/>
       <c r="H73" s="10"/>
@@ -2270,7 +2274,7 @@
       <c r="A74" s="23">
         <v>46116</v>
       </c>
-      <c r="B74" s="21" t="s">
+      <c r="B74" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C74" s="3" t="str" cm="1">
@@ -2281,7 +2285,7 @@
         <v>01703409900</v>
       </c>
       <c r="E74" s="11" t="str" cm="1">
-        <f t="array" ref="E74:F77">E70:F73</f>
+        <f t="array" ref="E74:F77">E50:F53</f>
         <v>Maruf Hossain (LM)</v>
       </c>
       <c r="F74" s="19" t="str">
@@ -2310,7 +2314,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="23"/>
-      <c r="B75" s="21"/>
+      <c r="B75" s="22"/>
       <c r="C75" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -2332,7 +2336,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="23"/>
-      <c r="B76" s="21"/>
+      <c r="B76" s="22"/>
       <c r="C76" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -2354,7 +2358,7 @@
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="23"/>
-      <c r="B77" s="21"/>
+      <c r="B77" s="22"/>
       <c r="C77" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -2376,7 +2380,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="23"/>
-      <c r="B78" s="21"/>
+      <c r="B78" s="22"/>
       <c r="C78" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -2390,7 +2394,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="23"/>
-      <c r="B79" s="21"/>
+      <c r="B79" s="22"/>
       <c r="C79" s="3"/>
       <c r="D79" s="13"/>
       <c r="E79" s="3"/>
@@ -2402,13 +2406,13 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="23"/>
-      <c r="B80" s="21"/>
+      <c r="B80" s="22"/>
       <c r="C80" s="5" t="str">
-        <f>E73</f>
+        <f>E53</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="D80" s="17" t="str">
-        <f>F73</f>
+        <f>F53</f>
         <v>01748127818</v>
       </c>
       <c r="E80" s="3"/>
@@ -2420,7 +2424,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="23"/>
-      <c r="B81" s="21"/>
+      <c r="B81" s="22"/>
       <c r="E81" s="3"/>
       <c r="F81" s="17"/>
       <c r="G81" s="3"/>
@@ -2432,7 +2436,7 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="23"/>
-      <c r="B82" s="21"/>
+      <c r="B82" s="22"/>
       <c r="E82" s="3"/>
       <c r="F82" s="17"/>
       <c r="G82" s="3"/>
@@ -2444,7 +2448,7 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="23"/>
-      <c r="B83" s="21"/>
+      <c r="B83" s="22"/>
       <c r="C83" s="5"/>
       <c r="D83" s="13"/>
       <c r="E83" s="3"/>
@@ -2458,7 +2462,7 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="23"/>
-      <c r="B84" s="22" t="s">
+      <c r="B84" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C84" s="6" t="str" cm="1">
@@ -2469,7 +2473,7 @@
         <v>01703409900</v>
       </c>
       <c r="E84" s="3" t="str" cm="1">
-        <f t="array" ref="E84:F87">E50:F53</f>
+        <f t="array" ref="E84:F87">E60:F63</f>
         <v>Sumon (LM)</v>
       </c>
       <c r="F84" s="13" t="str">
@@ -2498,7 +2502,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="23"/>
-      <c r="B85" s="22"/>
+      <c r="B85" s="24"/>
       <c r="C85" s="6" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -2520,7 +2524,7 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="23"/>
-      <c r="B86" s="22"/>
+      <c r="B86" s="24"/>
       <c r="C86" s="6" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -2542,7 +2546,7 @@
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="23"/>
-      <c r="B87" s="22"/>
+      <c r="B87" s="24"/>
       <c r="C87" s="6" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -2564,7 +2568,7 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="23"/>
-      <c r="B88" s="22"/>
+      <c r="B88" s="24"/>
       <c r="C88" s="6" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -2582,12 +2586,12 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="23"/>
-      <c r="B89" s="22"/>
+      <c r="B89" s="24"/>
       <c r="C89" s="6" t="str">
-        <v>Driver - Shetu</v>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D89" s="14" t="str">
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E89" s="6"/>
       <c r="F89" s="18"/>
@@ -2600,7 +2604,7 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="23"/>
-      <c r="B90" s="22"/>
+      <c r="B90" s="24"/>
       <c r="C90" s="6" t="str" cm="1">
         <f t="array" ref="C90:D90">E77:F77</f>
         <v>Driver - Noyon</v>
@@ -2619,7 +2623,7 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="23"/>
-      <c r="B91" s="22"/>
+      <c r="B91" s="24"/>
       <c r="C91" s="8"/>
       <c r="D91" s="14"/>
       <c r="E91" s="6"/>
@@ -2633,7 +2637,7 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="23"/>
-      <c r="B92" s="22"/>
+      <c r="B92" s="24"/>
       <c r="C92" s="8"/>
       <c r="D92" s="14"/>
       <c r="E92" s="6"/>
@@ -2647,7 +2651,7 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="23"/>
-      <c r="B93" s="22"/>
+      <c r="B93" s="24"/>
       <c r="C93" s="8"/>
       <c r="D93" s="14"/>
       <c r="G93" s="6"/>
@@ -2659,13 +2663,13 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="23"/>
-      <c r="B94" s="20" t="s">
+      <c r="B94" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="9"/>
       <c r="D94" s="15"/>
       <c r="E94" s="3" t="str" cm="1">
-        <f t="array" ref="E94:F97">E60:F63</f>
+        <f t="array" ref="E94:F97">E70:F73</f>
         <v>Rakib (LM)</v>
       </c>
       <c r="F94" s="17" t="str">
@@ -2694,7 +2698,7 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="23"/>
-      <c r="B95" s="20"/>
+      <c r="B95" s="21"/>
       <c r="C95" s="9"/>
       <c r="D95" s="15"/>
       <c r="E95" s="3" t="str">
@@ -2712,7 +2716,7 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="23"/>
-      <c r="B96" s="20"/>
+      <c r="B96" s="21"/>
       <c r="C96" s="9"/>
       <c r="D96" s="15"/>
       <c r="E96" s="3" t="str">
@@ -2730,7 +2734,7 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="23"/>
-      <c r="B97" s="20"/>
+      <c r="B97" s="21"/>
       <c r="C97" s="9"/>
       <c r="D97" s="15"/>
       <c r="E97" s="3" t="str">
@@ -2750,7 +2754,7 @@
       <c r="A98" s="23">
         <v>46117</v>
       </c>
-      <c r="B98" s="21" t="s">
+      <c r="B98" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C98" s="3" t="str" cm="1">
@@ -2791,7 +2795,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="23"/>
-      <c r="B99" s="21"/>
+      <c r="B99" s="22"/>
       <c r="C99" s="3" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
@@ -2813,7 +2817,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="23"/>
-      <c r="B100" s="21"/>
+      <c r="B100" s="22"/>
       <c r="C100" s="3" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
@@ -2835,7 +2839,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="23"/>
-      <c r="B101" s="21"/>
+      <c r="B101" s="22"/>
       <c r="C101" s="3" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
@@ -2857,7 +2861,7 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="23"/>
-      <c r="B102" s="21"/>
+      <c r="B102" s="22"/>
       <c r="C102" s="3" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -2871,12 +2875,12 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="23"/>
-      <c r="B103" s="21"/>
+      <c r="B103" s="22"/>
       <c r="C103" s="3" t="str">
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D103" s="13">
-        <v>0</v>
+      <c r="D103" s="13" t="str">
+        <v>01723504940</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="17"/>
@@ -2887,7 +2891,7 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="23"/>
-      <c r="B104" s="21"/>
+      <c r="B104" s="22"/>
       <c r="C104" s="5" t="str">
         <f>E97</f>
         <v>Driver - Shetu</v>
@@ -2905,7 +2909,7 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="23"/>
-      <c r="B105" s="21"/>
+      <c r="B105" s="22"/>
       <c r="E105" s="3"/>
       <c r="F105" s="17"/>
       <c r="G105" s="3"/>
@@ -2917,7 +2921,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="23"/>
-      <c r="B106" s="21"/>
+      <c r="B106" s="22"/>
       <c r="E106" s="3"/>
       <c r="F106" s="17"/>
       <c r="G106" s="3"/>
@@ -2929,7 +2933,7 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="23"/>
-      <c r="B107" s="21"/>
+      <c r="B107" s="22"/>
       <c r="C107" s="5"/>
       <c r="D107" s="13"/>
       <c r="E107" s="3"/>
@@ -2943,7 +2947,7 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="23"/>
-      <c r="B108" s="22" t="s">
+      <c r="B108" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C108" s="6" t="str" cm="1">
@@ -2984,7 +2988,7 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="23"/>
-      <c r="B109" s="22"/>
+      <c r="B109" s="24"/>
       <c r="C109" s="6" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -3006,7 +3010,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="23"/>
-      <c r="B110" s="22"/>
+      <c r="B110" s="24"/>
       <c r="C110" s="6" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -3028,7 +3032,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="23"/>
-      <c r="B111" s="22"/>
+      <c r="B111" s="24"/>
       <c r="C111" s="6" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -3050,7 +3054,7 @@
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="23"/>
-      <c r="B112" s="22"/>
+      <c r="B112" s="24"/>
       <c r="C112" s="6" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -3068,7 +3072,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="23"/>
-      <c r="B113" s="22"/>
+      <c r="B113" s="24"/>
       <c r="C113" s="6"/>
       <c r="D113" s="14"/>
       <c r="E113" s="6"/>
@@ -3082,7 +3086,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="23"/>
-      <c r="B114" s="22"/>
+      <c r="B114" s="24"/>
       <c r="C114" s="6" t="str" cm="1">
         <f t="array" ref="C114:D114">E101:F101</f>
         <v>Driver - Hasan</v>
@@ -3101,7 +3105,7 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="23"/>
-      <c r="B115" s="22"/>
+      <c r="B115" s="24"/>
       <c r="C115" s="8"/>
       <c r="D115" s="14"/>
       <c r="E115" s="6"/>
@@ -3115,7 +3119,7 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="23"/>
-      <c r="B116" s="22"/>
+      <c r="B116" s="24"/>
       <c r="C116" s="8"/>
       <c r="D116" s="14"/>
       <c r="E116" s="6"/>
@@ -3129,7 +3133,7 @@
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="23"/>
-      <c r="B117" s="22"/>
+      <c r="B117" s="24"/>
       <c r="C117" s="8"/>
       <c r="D117" s="14"/>
       <c r="G117" s="6"/>
@@ -3141,7 +3145,7 @@
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="23"/>
-      <c r="B118" s="20" t="s">
+      <c r="B118" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C118" s="9"/>
@@ -3177,7 +3181,7 @@
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="23"/>
-      <c r="B119" s="20"/>
+      <c r="B119" s="21"/>
       <c r="C119" s="9"/>
       <c r="D119" s="15"/>
       <c r="E119" s="3" t="str">
@@ -3195,7 +3199,7 @@
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="23"/>
-      <c r="B120" s="20"/>
+      <c r="B120" s="21"/>
       <c r="C120" s="9"/>
       <c r="D120" s="15"/>
       <c r="E120" s="3" t="str">
@@ -3213,7 +3217,7 @@
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="23"/>
-      <c r="B121" s="20"/>
+      <c r="B121" s="21"/>
       <c r="C121" s="9"/>
       <c r="D121" s="15"/>
       <c r="E121" s="3" t="str">
@@ -3233,7 +3237,7 @@
       <c r="A122" s="23">
         <v>46118</v>
       </c>
-      <c r="B122" s="21" t="s">
+      <c r="B122" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C122" s="3" t="str" cm="1">
@@ -3273,7 +3277,7 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="23"/>
-      <c r="B123" s="21"/>
+      <c r="B123" s="22"/>
       <c r="C123" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -3295,7 +3299,7 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="23"/>
-      <c r="B124" s="21"/>
+      <c r="B124" s="22"/>
       <c r="C124" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -3317,7 +3321,7 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="23"/>
-      <c r="B125" s="21"/>
+      <c r="B125" s="22"/>
       <c r="C125" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -3339,7 +3343,7 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="23"/>
-      <c r="B126" s="21"/>
+      <c r="B126" s="22"/>
       <c r="C126" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -3353,12 +3357,12 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="23"/>
-      <c r="B127" s="21"/>
+      <c r="B127" s="22"/>
       <c r="C127" s="3" t="str">
-        <v>Driver - Shetu</v>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D127" s="13" t="str">
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="17"/>
@@ -3369,7 +3373,7 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="23"/>
-      <c r="B128" s="21"/>
+      <c r="B128" s="22"/>
       <c r="C128" s="5" t="str">
         <f>E121</f>
         <v>Driver - Noyon</v>
@@ -3387,7 +3391,7 @@
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="23"/>
-      <c r="B129" s="21"/>
+      <c r="B129" s="22"/>
       <c r="E129" s="3"/>
       <c r="F129" s="17"/>
       <c r="G129" s="3"/>
@@ -3399,7 +3403,7 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="23"/>
-      <c r="B130" s="21"/>
+      <c r="B130" s="22"/>
       <c r="E130" s="3"/>
       <c r="F130" s="17"/>
       <c r="G130" s="3"/>
@@ -3411,7 +3415,7 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="23"/>
-      <c r="B131" s="21"/>
+      <c r="B131" s="22"/>
       <c r="C131" s="5"/>
       <c r="D131" s="13"/>
       <c r="E131" s="3"/>
@@ -3425,7 +3429,7 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="23"/>
-      <c r="B132" s="22" t="s">
+      <c r="B132" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C132" s="6" t="str" cm="1">
@@ -3465,7 +3469,7 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="23"/>
-      <c r="B133" s="22"/>
+      <c r="B133" s="24"/>
       <c r="C133" s="6" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
@@ -3487,7 +3491,7 @@
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="23"/>
-      <c r="B134" s="22"/>
+      <c r="B134" s="24"/>
       <c r="C134" s="6" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
@@ -3509,7 +3513,7 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="23"/>
-      <c r="B135" s="22"/>
+      <c r="B135" s="24"/>
       <c r="C135" s="6" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
@@ -3531,7 +3535,7 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="23"/>
-      <c r="B136" s="22"/>
+      <c r="B136" s="24"/>
       <c r="C136" s="6" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -3549,7 +3553,7 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="23"/>
-      <c r="B137" s="22"/>
+      <c r="B137" s="24"/>
       <c r="C137" s="6"/>
       <c r="D137" s="14"/>
       <c r="E137" s="6"/>
@@ -3563,7 +3567,7 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="23"/>
-      <c r="B138" s="22"/>
+      <c r="B138" s="24"/>
       <c r="C138" s="6" t="str" cm="1">
         <f t="array" ref="C138:D138">E125:F125</f>
         <v>Driver - Hasan</v>
@@ -3582,7 +3586,7 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="23"/>
-      <c r="B139" s="22"/>
+      <c r="B139" s="24"/>
       <c r="C139" s="8"/>
       <c r="D139" s="14"/>
       <c r="E139" s="6"/>
@@ -3596,7 +3600,7 @@
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="23"/>
-      <c r="B140" s="22"/>
+      <c r="B140" s="24"/>
       <c r="C140" s="8"/>
       <c r="D140" s="14"/>
       <c r="E140" s="6"/>
@@ -3610,7 +3614,7 @@
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="23"/>
-      <c r="B141" s="22"/>
+      <c r="B141" s="24"/>
       <c r="C141" s="8"/>
       <c r="D141" s="14"/>
       <c r="G141" s="6"/>
@@ -3622,7 +3626,7 @@
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="23"/>
-      <c r="B142" s="20" t="s">
+      <c r="B142" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C142" s="9"/>
@@ -3657,7 +3661,7 @@
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="23"/>
-      <c r="B143" s="20"/>
+      <c r="B143" s="21"/>
       <c r="C143" s="9"/>
       <c r="D143" s="15"/>
       <c r="E143" s="3" t="str">
@@ -3675,7 +3679,7 @@
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="23"/>
-      <c r="B144" s="20"/>
+      <c r="B144" s="21"/>
       <c r="C144" s="9"/>
       <c r="D144" s="15"/>
       <c r="E144" s="3" t="str">
@@ -3693,7 +3697,7 @@
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="23"/>
-      <c r="B145" s="20"/>
+      <c r="B145" s="21"/>
       <c r="C145" s="9"/>
       <c r="D145" s="15"/>
       <c r="E145" s="3" t="str">
@@ -3713,7 +3717,7 @@
       <c r="A146" s="25">
         <v>46119</v>
       </c>
-      <c r="B146" s="21" t="s">
+      <c r="B146" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C146" s="3" t="s">
@@ -3749,7 +3753,7 @@
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="25"/>
-      <c r="B147" s="21"/>
+      <c r="B147" s="22"/>
       <c r="C147" s="3" t="s">
         <v>36</v>
       </c>
@@ -3771,7 +3775,7 @@
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="25"/>
-      <c r="B148" s="21"/>
+      <c r="B148" s="22"/>
       <c r="C148" s="6" t="s">
         <v>40</v>
       </c>
@@ -3793,7 +3797,7 @@
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="25"/>
-      <c r="B149" s="21"/>
+      <c r="B149" s="22"/>
       <c r="C149" s="3" t="s">
         <v>18</v>
       </c>
@@ -3815,7 +3819,7 @@
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="25"/>
-      <c r="B150" s="21"/>
+      <c r="B150" s="22"/>
       <c r="C150" s="3" t="s">
         <v>37</v>
       </c>
@@ -3829,9 +3833,12 @@
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="25"/>
-      <c r="B151" s="21"/>
-      <c r="C151" s="24" t="s">
+      <c r="B151" s="22"/>
+      <c r="C151" s="20" t="s">
         <v>66</v>
+      </c>
+      <c r="D151" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="E151" s="3"/>
       <c r="F151" s="17"/>
@@ -3842,7 +3849,7 @@
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="25"/>
-      <c r="B152" s="21"/>
+      <c r="B152" s="22"/>
       <c r="C152" s="5" t="s">
         <v>21</v>
       </c>
@@ -3858,7 +3865,7 @@
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="25"/>
-      <c r="B153" s="21"/>
+      <c r="B153" s="22"/>
       <c r="E153" s="3"/>
       <c r="F153" s="17"/>
       <c r="G153" s="3"/>
@@ -3870,7 +3877,7 @@
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="25"/>
-      <c r="B154" s="21"/>
+      <c r="B154" s="22"/>
       <c r="E154" s="3"/>
       <c r="F154" s="17"/>
       <c r="G154" s="3"/>
@@ -3882,7 +3889,7 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="25"/>
-      <c r="B155" s="21"/>
+      <c r="B155" s="22"/>
       <c r="C155" s="5"/>
       <c r="D155" s="13"/>
       <c r="E155" s="3"/>
@@ -3896,7 +3903,7 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="25"/>
-      <c r="B156" s="22" t="s">
+      <c r="B156" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C156" s="6" t="s">
@@ -3932,7 +3939,7 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="25"/>
-      <c r="B157" s="22"/>
+      <c r="B157" s="24"/>
       <c r="C157" s="3" t="s">
         <v>14</v>
       </c>
@@ -3954,7 +3961,7 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="25"/>
-      <c r="B158" s="22"/>
+      <c r="B158" s="24"/>
       <c r="C158" s="6" t="s">
         <v>41</v>
       </c>
@@ -3976,7 +3983,7 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="25"/>
-      <c r="B159" s="22"/>
+      <c r="B159" s="24"/>
       <c r="C159" s="6" t="s">
         <v>13</v>
       </c>
@@ -3998,7 +4005,7 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="25"/>
-      <c r="B160" s="22"/>
+      <c r="B160" s="24"/>
       <c r="C160" s="6" t="s">
         <v>42</v>
       </c>
@@ -4016,13 +4023,13 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="25"/>
-      <c r="B161" s="22"/>
+      <c r="B161" s="24"/>
       <c r="C161" s="8" t="str">
-        <f t="shared" ref="C161:D161" si="9">E149</f>
+        <f t="shared" ref="C161:D161" si="12">E149</f>
         <v>Driver - Shetu</v>
       </c>
       <c r="D161" s="18" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>01719034964</v>
       </c>
       <c r="E161" s="6"/>
@@ -4036,7 +4043,7 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="25"/>
-      <c r="B162" s="22"/>
+      <c r="B162" s="24"/>
       <c r="E162" s="6"/>
       <c r="F162" s="18"/>
       <c r="G162" s="6"/>
@@ -4048,7 +4055,7 @@
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="25"/>
-      <c r="B163" s="22"/>
+      <c r="B163" s="24"/>
       <c r="C163" s="8"/>
       <c r="D163" s="14"/>
       <c r="E163" s="6"/>
@@ -4062,7 +4069,7 @@
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="25"/>
-      <c r="B164" s="22"/>
+      <c r="B164" s="24"/>
       <c r="C164" s="8"/>
       <c r="D164" s="14"/>
       <c r="E164" s="6"/>
@@ -4076,7 +4083,7 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="25"/>
-      <c r="B165" s="22"/>
+      <c r="B165" s="24"/>
       <c r="C165" s="8"/>
       <c r="D165" s="14"/>
       <c r="G165" s="6"/>
@@ -4088,7 +4095,7 @@
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="25"/>
-      <c r="B166" s="20" t="s">
+      <c r="B166" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C166" s="9"/>
@@ -4120,7 +4127,7 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="25"/>
-      <c r="B167" s="20"/>
+      <c r="B167" s="21"/>
       <c r="C167" s="9"/>
       <c r="D167" s="15"/>
       <c r="E167" s="3" t="s">
@@ -4138,7 +4145,7 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="25"/>
-      <c r="B168" s="20"/>
+      <c r="B168" s="21"/>
       <c r="C168" s="9"/>
       <c r="D168" s="15"/>
       <c r="E168" s="3" t="s">
@@ -4156,7 +4163,7 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="25"/>
-      <c r="B169" s="20"/>
+      <c r="B169" s="21"/>
       <c r="C169" s="9"/>
       <c r="D169" s="15"/>
       <c r="E169" s="5" t="s">
@@ -4176,67 +4183,67 @@
       <c r="A170" s="23">
         <v>46120</v>
       </c>
-      <c r="B170" s="21" t="s">
+      <c r="B170" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C170" s="3" t="str">
-        <f t="shared" ref="C170:D170" si="10">C156</f>
+        <f t="shared" ref="C170:D170" si="13">C156</f>
         <v>Monirul Islam  (LM)</v>
       </c>
       <c r="D170" s="13" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>01703409900</v>
       </c>
       <c r="E170" s="11" t="str">
-        <f t="shared" ref="E170:L170" si="11">E146</f>
+        <f t="shared" ref="E170:L170" si="14">E146</f>
         <v>Rakib (LM)</v>
       </c>
       <c r="F170" s="19" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>01767032267</v>
       </c>
       <c r="G170" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>Shawon Dass</v>
       </c>
       <c r="H170" s="19" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="I170" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>Salim Reza</v>
       </c>
       <c r="J170" s="19" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="K170" s="6" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>Inul Haque</v>
       </c>
       <c r="L170" s="19" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>02588855910</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="23"/>
-      <c r="B171" s="21"/>
+      <c r="B171" s="22"/>
       <c r="C171" s="3" t="str">
-        <f t="shared" ref="C171:D171" si="12">C157</f>
+        <f t="shared" ref="C171:D171" si="15">C157</f>
         <v>Abdus Sattar (LM)</v>
       </c>
       <c r="D171" s="13" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>01718676281</v>
       </c>
       <c r="E171" s="11" t="str">
-        <f t="shared" ref="E171:F171" si="13">E147</f>
+        <f t="shared" ref="E171:F171" si="16">E147</f>
         <v>Nabi (LH)</v>
       </c>
       <c r="F171" s="19" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>01736352528</v>
       </c>
       <c r="G171" s="3"/>
@@ -4248,21 +4255,21 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="23"/>
-      <c r="B172" s="21"/>
+      <c r="B172" s="22"/>
       <c r="C172" s="3" t="str">
-        <f t="shared" ref="C172:D172" si="14">C158</f>
+        <f t="shared" ref="C172:D172" si="17">C158</f>
         <v>Sazzad  (LM)</v>
       </c>
       <c r="D172" s="13" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>01719106824</v>
       </c>
       <c r="E172" s="11" t="str">
-        <f t="shared" ref="E172:F172" si="15">E148</f>
+        <f t="shared" ref="E172:F172" si="18">E148</f>
         <v>Anowar (LEM)</v>
       </c>
       <c r="F172" s="19" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="18"/>
         <v>01712439152</v>
       </c>
       <c r="G172" s="3"/>
@@ -4274,21 +4281,21 @@
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" s="23"/>
-      <c r="B173" s="21"/>
+      <c r="B173" s="22"/>
       <c r="C173" s="3" t="str">
-        <f t="shared" ref="C173:D173" si="16">C159</f>
+        <f t="shared" ref="C173:D173" si="19">C159</f>
         <v>Jonny (LH)</v>
       </c>
       <c r="D173" s="13" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="19"/>
         <v>01712441588</v>
       </c>
       <c r="E173" s="11" t="str">
-        <f t="shared" ref="E173:F173" si="17">E149</f>
+        <f t="shared" ref="E173:F173" si="20">E149</f>
         <v>Driver - Shetu</v>
       </c>
       <c r="F173" s="19" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="20"/>
         <v>01719034964</v>
       </c>
       <c r="G173" s="3"/>
@@ -4300,13 +4307,13 @@
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" s="23"/>
-      <c r="B174" s="21"/>
+      <c r="B174" s="22"/>
       <c r="C174" s="3" t="str">
-        <f t="shared" ref="C174:D174" si="18">C160</f>
+        <f t="shared" ref="C174:D174" si="21">C160</f>
         <v>Nazmul (LEM)</v>
       </c>
       <c r="D174" s="13" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="21"/>
         <v>01914595295</v>
       </c>
       <c r="G174" s="3"/>
@@ -4316,14 +4323,13 @@
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" s="23"/>
-      <c r="B175" s="21"/>
-      <c r="C175" s="3" t="str">
-        <f t="shared" ref="C175:D175" si="19">C161</f>
-        <v>Driver - Shetu</v>
+      <c r="B175" s="22"/>
+      <c r="C175" s="3" t="str" cm="1">
+        <f t="array" ref="C175:D175">E169:F169</f>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D175" s="13" t="str">
-        <f t="shared" si="19"/>
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E175" s="3"/>
       <c r="F175" s="17"/>
@@ -4334,7 +4340,7 @@
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" s="23"/>
-      <c r="B176" s="21"/>
+      <c r="B176" s="22"/>
       <c r="C176" s="5"/>
       <c r="D176" s="17"/>
       <c r="E176" s="3"/>
@@ -4346,7 +4352,7 @@
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" s="23"/>
-      <c r="B177" s="21"/>
+      <c r="B177" s="22"/>
       <c r="E177" s="3"/>
       <c r="F177" s="17"/>
       <c r="G177" s="3"/>
@@ -4358,7 +4364,7 @@
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A178" s="23"/>
-      <c r="B178" s="21"/>
+      <c r="B178" s="22"/>
       <c r="E178" s="3"/>
       <c r="F178" s="17"/>
       <c r="G178" s="3"/>
@@ -4370,7 +4376,7 @@
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" s="23"/>
-      <c r="B179" s="21"/>
+      <c r="B179" s="22"/>
       <c r="C179" s="5"/>
       <c r="D179" s="13"/>
       <c r="E179" s="3"/>
@@ -4384,67 +4390,67 @@
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A180" s="23"/>
-      <c r="B180" s="22" t="s">
+      <c r="B180" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C180" s="6" t="str">
-        <f t="shared" ref="C180:D180" si="20">C146</f>
+        <f t="shared" ref="C180:D180" si="22">C146</f>
         <v>Mostafijur (LM)</v>
       </c>
       <c r="D180" s="14" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>01758212103</v>
       </c>
       <c r="E180" s="3" t="str">
-        <f t="shared" ref="E180:K180" si="21">E156</f>
+        <f t="shared" ref="E180:K180" si="23">E156</f>
         <v>Maruf Hossain (LM)</v>
       </c>
       <c r="F180" s="13" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>01943368198</v>
       </c>
       <c r="G180" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>Alauddin</v>
       </c>
       <c r="H180" s="19" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="I180" s="6" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>Moin Uddin</v>
       </c>
       <c r="J180" s="19" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="K180" s="11" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>Masud Rana</v>
       </c>
       <c r="L180" s="19" t="str">
-        <f t="shared" ref="L180" si="22">L190</f>
+        <f t="shared" ref="L180" si="24">L190</f>
         <v>02588855910</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A181" s="23"/>
-      <c r="B181" s="22"/>
+      <c r="B181" s="24"/>
       <c r="C181" s="6" t="str">
-        <f t="shared" ref="C181:D181" si="23">C147</f>
+        <f t="shared" ref="C181:D181" si="25">C147</f>
         <v>Monzur Kader (LM)</v>
       </c>
       <c r="D181" s="14" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>01705614054</v>
       </c>
       <c r="E181" s="3" t="str">
-        <f t="shared" ref="E181:F181" si="24">E157</f>
+        <f t="shared" ref="E181:F181" si="26">E157</f>
         <v>Sahjahan (LEM)</v>
       </c>
       <c r="F181" s="13" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>01724267460</v>
       </c>
       <c r="G181" s="6"/>
@@ -4456,21 +4462,21 @@
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A182" s="23"/>
-      <c r="B182" s="22"/>
+      <c r="B182" s="24"/>
       <c r="C182" s="6" t="str">
-        <f t="shared" ref="C182:D182" si="25">C148</f>
+        <f t="shared" ref="C182:D182" si="27">C148</f>
         <v>Mosaddek  (LM)</v>
       </c>
       <c r="D182" s="14" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>01674272353</v>
       </c>
       <c r="E182" s="3" t="str">
-        <f t="shared" ref="E182:F182" si="26">E158</f>
+        <f t="shared" ref="E182:F182" si="28">E158</f>
         <v>Fuad (LH)</v>
       </c>
       <c r="F182" s="13" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>01718279112</v>
       </c>
       <c r="G182" s="6"/>
@@ -4482,21 +4488,21 @@
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" s="23"/>
-      <c r="B183" s="22"/>
+      <c r="B183" s="24"/>
       <c r="C183" s="6" t="str">
-        <f t="shared" ref="C183:D183" si="27">C149</f>
+        <f t="shared" ref="C183:D183" si="29">C149</f>
         <v>Abdus Salam (LM)</v>
       </c>
       <c r="D183" s="14" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>01756101919</v>
       </c>
       <c r="E183" s="3" t="str">
-        <f t="shared" ref="E183:F183" si="28">E159</f>
+        <f t="shared" ref="E183:F183" si="30">E159</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="F183" s="13" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>01748127818</v>
       </c>
       <c r="G183" s="6"/>
@@ -4508,13 +4514,13 @@
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" s="23"/>
-      <c r="B184" s="22"/>
+      <c r="B184" s="24"/>
       <c r="C184" s="6" t="str">
-        <f t="shared" ref="C184:D184" si="29">C150</f>
+        <f t="shared" ref="C184:D184" si="31">C150</f>
         <v>Salim Reza-2 (LH)</v>
       </c>
       <c r="D184" s="14" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>01719531782</v>
       </c>
       <c r="E184" s="6"/>
@@ -4528,14 +4534,14 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A185" s="23"/>
-      <c r="B185" s="22"/>
+      <c r="B185" s="24"/>
       <c r="C185" s="6" t="str">
-        <f t="shared" ref="C185:D185" si="30">C151</f>
+        <f t="shared" ref="C185:D185" si="32">C151</f>
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D185" s="14">
-        <f t="shared" si="30"/>
-        <v>0</v>
+      <c r="D185" s="14" t="str">
+        <f t="shared" si="32"/>
+        <v>01723504940</v>
       </c>
       <c r="E185" s="6"/>
       <c r="F185" s="18"/>
@@ -4548,14 +4554,13 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" s="23"/>
-      <c r="B186" s="22"/>
-      <c r="C186" s="6" t="str">
-        <f t="shared" ref="C186:D186" si="31">C152</f>
-        <v>Driver - Hasan</v>
+      <c r="B186" s="24"/>
+      <c r="C186" s="6" t="str" cm="1">
+        <f t="array" ref="C186:D186">E173:F173</f>
+        <v>Driver - Shetu</v>
       </c>
       <c r="D186" s="14" t="str">
-        <f t="shared" si="31"/>
-        <v>01730824934</v>
+        <v>01719034964</v>
       </c>
       <c r="E186" s="6"/>
       <c r="F186" s="18"/>
@@ -4568,7 +4573,7 @@
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" s="23"/>
-      <c r="B187" s="22"/>
+      <c r="B187" s="24"/>
       <c r="C187" s="8"/>
       <c r="D187" s="14"/>
       <c r="E187" s="6"/>
@@ -4582,7 +4587,7 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" s="23"/>
-      <c r="B188" s="22"/>
+      <c r="B188" s="24"/>
       <c r="C188" s="8"/>
       <c r="D188" s="14"/>
       <c r="E188" s="6"/>
@@ -4596,7 +4601,7 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" s="23"/>
-      <c r="B189" s="22"/>
+      <c r="B189" s="24"/>
       <c r="C189" s="8"/>
       <c r="D189" s="14"/>
       <c r="G189" s="6"/>
@@ -4608,55 +4613,55 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" s="23"/>
-      <c r="B190" s="20" t="s">
+      <c r="B190" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C190" s="9"/>
       <c r="D190" s="15"/>
       <c r="E190" s="3" t="str">
-        <f t="shared" ref="E190:L190" si="32">E166</f>
+        <f t="shared" ref="E190:L190" si="33">E166</f>
         <v>Sumon (LM)</v>
       </c>
       <c r="F190" s="17" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>01726258394</v>
       </c>
       <c r="G190" s="11" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>Abdur Rafique</v>
       </c>
       <c r="H190" s="19" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="I190" s="11" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>Abul Kalam Azad</v>
       </c>
       <c r="J190" s="19" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="K190" s="3" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>Monzur Ahmed</v>
       </c>
       <c r="L190" s="19" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>02588855910</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" s="23"/>
-      <c r="B191" s="20"/>
+      <c r="B191" s="21"/>
       <c r="C191" s="9"/>
       <c r="D191" s="15"/>
       <c r="E191" s="3" t="str">
-        <f t="shared" ref="E191:F191" si="33">E167</f>
+        <f t="shared" ref="E191:F191" si="34">E167</f>
         <v>Arafat (LH)</v>
       </c>
       <c r="F191" s="17" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>01755149115</v>
       </c>
       <c r="G191" s="11"/>
@@ -4668,15 +4673,15 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" s="23"/>
-      <c r="B192" s="20"/>
+      <c r="B192" s="21"/>
       <c r="C192" s="9"/>
       <c r="D192" s="15"/>
       <c r="E192" s="3" t="str">
-        <f t="shared" ref="E192:F192" si="34">E168</f>
+        <f t="shared" ref="E192:F192" si="35">E168</f>
         <v>Mamun (LH)</v>
       </c>
       <c r="F192" s="17" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>01718106022</v>
       </c>
       <c r="G192" s="11"/>
@@ -4688,15 +4693,15 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" s="23"/>
-      <c r="B193" s="20"/>
+      <c r="B193" s="21"/>
       <c r="C193" s="9"/>
       <c r="D193" s="15"/>
       <c r="E193" s="3" t="str">
-        <f t="shared" ref="E193:F193" si="35">E169</f>
+        <f t="shared" ref="E193:F193" si="36">E169</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="F193" s="17" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>01730824934</v>
       </c>
       <c r="G193" s="11"/>
@@ -4710,7 +4715,7 @@
       <c r="A194" s="23">
         <v>46121</v>
       </c>
-      <c r="B194" s="21" t="s">
+      <c r="B194" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C194" s="3" t="str" cm="1">
@@ -4720,12 +4725,12 @@
       <c r="D194" s="13" t="str">
         <v>01703409900</v>
       </c>
-      <c r="E194" s="11" t="str" cm="1">
-        <f t="array" ref="E194:F197">E190:F193</f>
-        <v>Sumon (LM)</v>
-      </c>
-      <c r="F194" s="19" t="str">
-        <v>01726258394</v>
+      <c r="E194" s="3" t="str" cm="1">
+        <f t="array" ref="E194:F197">E180:F183</f>
+        <v>Maruf Hossain (LM)</v>
+      </c>
+      <c r="F194" s="17" t="str">
+        <v>01943368198</v>
       </c>
       <c r="G194" s="3" t="str" cm="1">
         <f t="array" ref="G194:H194">G180:H180</f>
@@ -4751,18 +4756,18 @@
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" s="23"/>
-      <c r="B195" s="21"/>
+      <c r="B195" s="22"/>
       <c r="C195" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
       <c r="D195" s="13" t="str">
         <v>01718676281</v>
       </c>
-      <c r="E195" s="11" t="str">
-        <v>Arafat (LH)</v>
-      </c>
-      <c r="F195" s="19" t="str">
-        <v>01755149115</v>
+      <c r="E195" s="3" t="str">
+        <v>Sahjahan (LEM)</v>
+      </c>
+      <c r="F195" s="17" t="str">
+        <v>01724267460</v>
       </c>
       <c r="G195" s="3"/>
       <c r="H195" s="4"/>
@@ -4773,18 +4778,18 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" s="23"/>
-      <c r="B196" s="21"/>
+      <c r="B196" s="22"/>
       <c r="C196" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
       <c r="D196" s="13" t="str">
         <v>01719106824</v>
       </c>
-      <c r="E196" s="11" t="str">
-        <v>Mamun (LH)</v>
-      </c>
-      <c r="F196" s="19" t="str">
-        <v>01718106022</v>
+      <c r="E196" s="3" t="str">
+        <v>Fuad (LH)</v>
+      </c>
+      <c r="F196" s="17" t="str">
+        <v>01718279112</v>
       </c>
       <c r="G196" s="3"/>
       <c r="H196" s="4"/>
@@ -4795,18 +4800,18 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" s="23"/>
-      <c r="B197" s="21"/>
+      <c r="B197" s="22"/>
       <c r="C197" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
       <c r="D197" s="13" t="str">
         <v>01712441588</v>
       </c>
-      <c r="E197" s="11" t="str">
-        <v>Driver - Hasan</v>
-      </c>
-      <c r="F197" s="19" t="str">
-        <v>01730824934</v>
+      <c r="E197" s="3" t="str">
+        <v>Driver - Noyon</v>
+      </c>
+      <c r="F197" s="17" t="str">
+        <v>01748127818</v>
       </c>
       <c r="G197" s="3"/>
       <c r="H197" s="4"/>
@@ -4817,7 +4822,7 @@
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" s="23"/>
-      <c r="B198" s="21"/>
+      <c r="B198" s="22"/>
       <c r="C198" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -4831,7 +4836,7 @@
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" s="23"/>
-      <c r="B199" s="21"/>
+      <c r="B199" s="22"/>
       <c r="C199" s="3"/>
       <c r="D199" s="13"/>
       <c r="E199" s="3"/>
@@ -4843,13 +4848,13 @@
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" s="23"/>
-      <c r="B200" s="21"/>
+      <c r="B200" s="22"/>
       <c r="C200" s="5" t="str">
-        <f t="shared" ref="C200:D200" si="36">E193</f>
+        <f t="shared" ref="C200:D200" si="37">E193</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="D200" s="17" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>01730824934</v>
       </c>
       <c r="E200" s="3"/>
@@ -4861,7 +4866,7 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" s="23"/>
-      <c r="B201" s="21"/>
+      <c r="B201" s="22"/>
       <c r="E201" s="3"/>
       <c r="F201" s="17"/>
       <c r="G201" s="3"/>
@@ -4873,7 +4878,7 @@
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" s="23"/>
-      <c r="B202" s="21"/>
+      <c r="B202" s="22"/>
       <c r="E202" s="3"/>
       <c r="F202" s="17"/>
       <c r="G202" s="3"/>
@@ -4885,7 +4890,7 @@
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" s="23"/>
-      <c r="B203" s="21"/>
+      <c r="B203" s="22"/>
       <c r="C203" s="5"/>
       <c r="D203" s="13"/>
       <c r="E203" s="3"/>
@@ -4899,7 +4904,7 @@
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" s="23"/>
-      <c r="B204" s="22" t="s">
+      <c r="B204" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C204" s="6" t="str" cm="1">
@@ -4909,12 +4914,12 @@
       <c r="D204" s="14" t="str">
         <v>01758212103</v>
       </c>
-      <c r="E204" s="3" t="str" cm="1">
-        <f t="array" ref="E204:F207">E170:F173</f>
-        <v>Rakib (LM)</v>
-      </c>
-      <c r="F204" s="13" t="str">
-        <v>01767032267</v>
+      <c r="E204" s="11" t="str" cm="1">
+        <f t="array" ref="E204:F207">E190:F193</f>
+        <v>Sumon (LM)</v>
+      </c>
+      <c r="F204" s="19" t="str">
+        <v>01726258394</v>
       </c>
       <c r="G204" s="6" t="str" cm="1">
         <f t="array" ref="G204:H204">G190:H190</f>
@@ -4940,18 +4945,18 @@
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" s="23"/>
-      <c r="B205" s="22"/>
+      <c r="B205" s="24"/>
       <c r="C205" s="6" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
       <c r="D205" s="14" t="str">
         <v>01705614054</v>
       </c>
-      <c r="E205" s="3" t="str">
-        <v>Nabi (LH)</v>
-      </c>
-      <c r="F205" s="13" t="str">
-        <v>01736352528</v>
+      <c r="E205" s="11" t="str">
+        <v>Arafat (LH)</v>
+      </c>
+      <c r="F205" s="19" t="str">
+        <v>01755149115</v>
       </c>
       <c r="G205" s="6"/>
       <c r="H205" s="7"/>
@@ -4966,18 +4971,18 @@
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" s="23"/>
-      <c r="B206" s="22"/>
+      <c r="B206" s="24"/>
       <c r="C206" s="6" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
       <c r="D206" s="14" t="str">
         <v>01674272353</v>
       </c>
-      <c r="E206" s="3" t="str">
-        <v>Anowar (LEM)</v>
-      </c>
-      <c r="F206" s="13" t="str">
-        <v>01712439152</v>
+      <c r="E206" s="11" t="str">
+        <v>Mamun (LH)</v>
+      </c>
+      <c r="F206" s="19" t="str">
+        <v>01718106022</v>
       </c>
       <c r="G206" s="6"/>
       <c r="H206" s="7"/>
@@ -4988,18 +4993,18 @@
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" s="23"/>
-      <c r="B207" s="22"/>
+      <c r="B207" s="24"/>
       <c r="C207" s="6" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
       <c r="D207" s="14" t="str">
         <v>01756101919</v>
       </c>
-      <c r="E207" s="3" t="str">
-        <v>Driver - Shetu</v>
-      </c>
-      <c r="F207" s="13" t="str">
-        <v>01719034964</v>
+      <c r="E207" s="11" t="str">
+        <v>Driver - Hasan</v>
+      </c>
+      <c r="F207" s="19" t="str">
+        <v>01730824934</v>
       </c>
       <c r="G207" s="6"/>
       <c r="H207" s="7"/>
@@ -5010,7 +5015,7 @@
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" s="23"/>
-      <c r="B208" s="22"/>
+      <c r="B208" s="24"/>
       <c r="C208" s="6" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -5028,12 +5033,12 @@
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" s="23"/>
-      <c r="B209" s="22"/>
+      <c r="B209" s="24"/>
       <c r="C209" s="6" t="str">
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D209" s="14">
-        <v>0</v>
+      <c r="D209" s="14" t="str">
+        <v>01723504940</v>
       </c>
       <c r="E209" s="6"/>
       <c r="F209" s="18"/>
@@ -5046,9 +5051,9 @@
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" s="23"/>
-      <c r="B210" s="22"/>
+      <c r="B210" s="24"/>
       <c r="C210" s="6" t="str" cm="1">
-        <f t="array" ref="C210:D210">E197:F197</f>
+        <f t="array" ref="C210:D210">E207:F207</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="D210" s="14" t="str">
@@ -5065,7 +5070,7 @@
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" s="23"/>
-      <c r="B211" s="22"/>
+      <c r="B211" s="24"/>
       <c r="C211" s="8"/>
       <c r="D211" s="14"/>
       <c r="E211" s="6"/>
@@ -5079,7 +5084,7 @@
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" s="23"/>
-      <c r="B212" s="22"/>
+      <c r="B212" s="24"/>
       <c r="C212" s="8"/>
       <c r="D212" s="14"/>
       <c r="E212" s="6"/>
@@ -5093,7 +5098,7 @@
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" s="23"/>
-      <c r="B213" s="22"/>
+      <c r="B213" s="24"/>
       <c r="C213" s="8"/>
       <c r="D213" s="14"/>
       <c r="G213" s="6"/>
@@ -5105,17 +5110,17 @@
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" s="23"/>
-      <c r="B214" s="20" t="s">
+      <c r="B214" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C214" s="9"/>
       <c r="D214" s="15"/>
       <c r="E214" s="3" t="str" cm="1">
-        <f t="array" ref="E214:F217">E180:F183</f>
-        <v>Maruf Hossain (LM)</v>
-      </c>
-      <c r="F214" s="17" t="str">
-        <v>01943368198</v>
+        <f t="array" ref="E214:F217">E170:F173</f>
+        <v>Rakib (LM)</v>
+      </c>
+      <c r="F214" s="13" t="str">
+        <v>01767032267</v>
       </c>
       <c r="G214" s="11" t="str" cm="1">
         <f t="array" ref="G214:H214">G170:H170</f>
@@ -5141,14 +5146,14 @@
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" s="23"/>
-      <c r="B215" s="20"/>
+      <c r="B215" s="21"/>
       <c r="C215" s="9"/>
       <c r="D215" s="15"/>
       <c r="E215" s="3" t="str">
-        <v>Sahjahan (LEM)</v>
-      </c>
-      <c r="F215" s="17" t="str">
-        <v>01724267460</v>
+        <v>Nabi (LH)</v>
+      </c>
+      <c r="F215" s="13" t="str">
+        <v>01736352528</v>
       </c>
       <c r="G215" s="11"/>
       <c r="H215" s="10"/>
@@ -5159,14 +5164,14 @@
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" s="23"/>
-      <c r="B216" s="20"/>
+      <c r="B216" s="21"/>
       <c r="C216" s="9"/>
       <c r="D216" s="15"/>
       <c r="E216" s="3" t="str">
-        <v>Fuad (LH)</v>
-      </c>
-      <c r="F216" s="17" t="str">
-        <v>01718279112</v>
+        <v>Anowar (LEM)</v>
+      </c>
+      <c r="F216" s="13" t="str">
+        <v>01712439152</v>
       </c>
       <c r="G216" s="11"/>
       <c r="H216" s="10"/>
@@ -5177,14 +5182,14 @@
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" s="23"/>
-      <c r="B217" s="20"/>
+      <c r="B217" s="21"/>
       <c r="C217" s="9"/>
       <c r="D217" s="15"/>
       <c r="E217" s="3" t="str">
-        <v>Driver - Noyon</v>
-      </c>
-      <c r="F217" s="17" t="str">
-        <v>01748127818</v>
+        <v>Driver - Shetu</v>
+      </c>
+      <c r="F217" s="13" t="str">
+        <v>01719034964</v>
       </c>
       <c r="G217" s="11"/>
       <c r="H217" s="10"/>
@@ -5197,7 +5202,7 @@
       <c r="A218" s="23">
         <v>46122</v>
       </c>
-      <c r="B218" s="21" t="s">
+      <c r="B218" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C218" s="3" t="str" cm="1">
@@ -5208,7 +5213,7 @@
         <v>01703409900</v>
       </c>
       <c r="E218" s="11" t="str" cm="1">
-        <f t="array" ref="E218:F221">E214:F217</f>
+        <f t="array" ref="E218:F221">E194:F197</f>
         <v>Maruf Hossain (LM)</v>
       </c>
       <c r="F218" s="19" t="str">
@@ -5237,7 +5242,7 @@
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A219" s="23"/>
-      <c r="B219" s="21"/>
+      <c r="B219" s="22"/>
       <c r="C219" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -5259,7 +5264,7 @@
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" s="23"/>
-      <c r="B220" s="21"/>
+      <c r="B220" s="22"/>
       <c r="C220" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -5281,7 +5286,7 @@
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" s="23"/>
-      <c r="B221" s="21"/>
+      <c r="B221" s="22"/>
       <c r="C221" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -5303,7 +5308,7 @@
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A222" s="23"/>
-      <c r="B222" s="21"/>
+      <c r="B222" s="22"/>
       <c r="C222" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -5317,7 +5322,7 @@
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A223" s="23"/>
-      <c r="B223" s="21"/>
+      <c r="B223" s="22"/>
       <c r="C223" s="3"/>
       <c r="D223" s="13"/>
       <c r="E223" s="3"/>
@@ -5329,13 +5334,13 @@
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A224" s="23"/>
-      <c r="B224" s="21"/>
+      <c r="B224" s="22"/>
       <c r="C224" s="5" t="str">
-        <f t="shared" ref="C224:D224" si="37">E217</f>
+        <f t="shared" ref="C224:D224" si="38">E197</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="D224" s="17" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>01748127818</v>
       </c>
       <c r="E224" s="3"/>
@@ -5347,7 +5352,7 @@
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A225" s="23"/>
-      <c r="B225" s="21"/>
+      <c r="B225" s="22"/>
       <c r="E225" s="3"/>
       <c r="F225" s="17"/>
       <c r="G225" s="3"/>
@@ -5359,7 +5364,7 @@
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A226" s="23"/>
-      <c r="B226" s="21"/>
+      <c r="B226" s="22"/>
       <c r="E226" s="3"/>
       <c r="F226" s="17"/>
       <c r="G226" s="3"/>
@@ -5371,7 +5376,7 @@
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A227" s="23"/>
-      <c r="B227" s="21"/>
+      <c r="B227" s="22"/>
       <c r="C227" s="5"/>
       <c r="D227" s="13"/>
       <c r="E227" s="3"/>
@@ -5385,7 +5390,7 @@
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A228" s="23"/>
-      <c r="B228" s="22" t="s">
+      <c r="B228" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C228" s="6" t="str" cm="1">
@@ -5396,7 +5401,7 @@
         <v>01703409900</v>
       </c>
       <c r="E228" s="3" t="str" cm="1">
-        <f t="array" ref="E228:F231">E194:F197</f>
+        <f t="array" ref="E228:F231">E204:F207</f>
         <v>Sumon (LM)</v>
       </c>
       <c r="F228" s="13" t="str">
@@ -5425,7 +5430,7 @@
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A229" s="23"/>
-      <c r="B229" s="22"/>
+      <c r="B229" s="24"/>
       <c r="C229" s="6" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -5447,7 +5452,7 @@
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" s="23"/>
-      <c r="B230" s="22"/>
+      <c r="B230" s="24"/>
       <c r="C230" s="6" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -5469,7 +5474,7 @@
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A231" s="23"/>
-      <c r="B231" s="22"/>
+      <c r="B231" s="24"/>
       <c r="C231" s="6" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -5491,7 +5496,7 @@
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A232" s="23"/>
-      <c r="B232" s="22"/>
+      <c r="B232" s="24"/>
       <c r="C232" s="6" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -5509,12 +5514,12 @@
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A233" s="23"/>
-      <c r="B233" s="22"/>
+      <c r="B233" s="24"/>
       <c r="C233" s="6" t="str">
-        <v>Driver - Shetu</v>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D233" s="14" t="str">
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E233" s="6"/>
       <c r="F233" s="18"/>
@@ -5527,7 +5532,7 @@
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A234" s="23"/>
-      <c r="B234" s="22"/>
+      <c r="B234" s="24"/>
       <c r="C234" s="6" t="str" cm="1">
         <f t="array" ref="C234:D234">E221:F221</f>
         <v>Driver - Noyon</v>
@@ -5546,7 +5551,7 @@
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" s="23"/>
-      <c r="B235" s="22"/>
+      <c r="B235" s="24"/>
       <c r="C235" s="8"/>
       <c r="D235" s="14"/>
       <c r="E235" s="6"/>
@@ -5560,7 +5565,7 @@
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" s="23"/>
-      <c r="B236" s="22"/>
+      <c r="B236" s="24"/>
       <c r="C236" s="8"/>
       <c r="D236" s="14"/>
       <c r="E236" s="6"/>
@@ -5574,7 +5579,7 @@
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A237" s="23"/>
-      <c r="B237" s="22"/>
+      <c r="B237" s="24"/>
       <c r="C237" s="8"/>
       <c r="D237" s="14"/>
       <c r="G237" s="6"/>
@@ -5586,13 +5591,13 @@
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" s="23"/>
-      <c r="B238" s="20" t="s">
+      <c r="B238" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C238" s="9"/>
       <c r="D238" s="15"/>
       <c r="E238" s="3" t="str" cm="1">
-        <f t="array" ref="E238:F241">E204:F207</f>
+        <f t="array" ref="E238:F241">E214:F217</f>
         <v>Rakib (LM)</v>
       </c>
       <c r="F238" s="17" t="str">
@@ -5621,7 +5626,7 @@
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A239" s="23"/>
-      <c r="B239" s="20"/>
+      <c r="B239" s="21"/>
       <c r="C239" s="9"/>
       <c r="D239" s="15"/>
       <c r="E239" s="3" t="str">
@@ -5639,7 +5644,7 @@
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A240" s="23"/>
-      <c r="B240" s="20"/>
+      <c r="B240" s="21"/>
       <c r="C240" s="9"/>
       <c r="D240" s="15"/>
       <c r="E240" s="3" t="str">
@@ -5657,7 +5662,7 @@
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A241" s="23"/>
-      <c r="B241" s="20"/>
+      <c r="B241" s="21"/>
       <c r="C241" s="9"/>
       <c r="D241" s="15"/>
       <c r="E241" s="3" t="str">
@@ -5677,7 +5682,7 @@
       <c r="A242" s="23">
         <v>46123</v>
       </c>
-      <c r="B242" s="21" t="s">
+      <c r="B242" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C242" s="3" t="str" cm="1">
@@ -5718,7 +5723,7 @@
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A243" s="23"/>
-      <c r="B243" s="21"/>
+      <c r="B243" s="22"/>
       <c r="C243" s="3" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
@@ -5740,7 +5745,7 @@
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A244" s="23"/>
-      <c r="B244" s="21"/>
+      <c r="B244" s="22"/>
       <c r="C244" s="3" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
@@ -5762,7 +5767,7 @@
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A245" s="23"/>
-      <c r="B245" s="21"/>
+      <c r="B245" s="22"/>
       <c r="C245" s="3" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
@@ -5784,7 +5789,7 @@
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A246" s="23"/>
-      <c r="B246" s="21"/>
+      <c r="B246" s="22"/>
       <c r="C246" s="3" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -5798,12 +5803,12 @@
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A247" s="23"/>
-      <c r="B247" s="21"/>
+      <c r="B247" s="22"/>
       <c r="C247" s="3" t="str">
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D247" s="13">
-        <v>0</v>
+      <c r="D247" s="13" t="str">
+        <v>01723504940</v>
       </c>
       <c r="E247" s="3"/>
       <c r="F247" s="17"/>
@@ -5814,13 +5819,13 @@
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" s="23"/>
-      <c r="B248" s="21"/>
+      <c r="B248" s="22"/>
       <c r="C248" s="5" t="str">
-        <f t="shared" ref="C248:D248" si="38">E241</f>
+        <f t="shared" ref="C248:D248" si="39">E241</f>
         <v>Driver - Shetu</v>
       </c>
       <c r="D248" s="17" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>01719034964</v>
       </c>
       <c r="E248" s="3"/>
@@ -5832,7 +5837,7 @@
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A249" s="23"/>
-      <c r="B249" s="21"/>
+      <c r="B249" s="22"/>
       <c r="E249" s="3"/>
       <c r="F249" s="17"/>
       <c r="G249" s="3"/>
@@ -5844,7 +5849,7 @@
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A250" s="23"/>
-      <c r="B250" s="21"/>
+      <c r="B250" s="22"/>
       <c r="E250" s="3"/>
       <c r="F250" s="17"/>
       <c r="G250" s="3"/>
@@ -5856,7 +5861,7 @@
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A251" s="23"/>
-      <c r="B251" s="21"/>
+      <c r="B251" s="22"/>
       <c r="C251" s="5"/>
       <c r="D251" s="13"/>
       <c r="E251" s="3"/>
@@ -5870,7 +5875,7 @@
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A252" s="23"/>
-      <c r="B252" s="22" t="s">
+      <c r="B252" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C252" s="6" t="str" cm="1">
@@ -5911,7 +5916,7 @@
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A253" s="23"/>
-      <c r="B253" s="22"/>
+      <c r="B253" s="24"/>
       <c r="C253" s="6" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -5933,7 +5938,7 @@
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A254" s="23"/>
-      <c r="B254" s="22"/>
+      <c r="B254" s="24"/>
       <c r="C254" s="6" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -5955,7 +5960,7 @@
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A255" s="23"/>
-      <c r="B255" s="22"/>
+      <c r="B255" s="24"/>
       <c r="C255" s="6" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -5977,7 +5982,7 @@
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A256" s="23"/>
-      <c r="B256" s="22"/>
+      <c r="B256" s="24"/>
       <c r="C256" s="6" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -5995,7 +6000,7 @@
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" s="23"/>
-      <c r="B257" s="22"/>
+      <c r="B257" s="24"/>
       <c r="C257" s="6"/>
       <c r="D257" s="14"/>
       <c r="E257" s="6"/>
@@ -6009,7 +6014,7 @@
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A258" s="23"/>
-      <c r="B258" s="22"/>
+      <c r="B258" s="24"/>
       <c r="C258" s="6" t="str" cm="1">
         <f t="array" ref="C258:D258">E245:F245</f>
         <v>Driver - Hasan</v>
@@ -6028,7 +6033,7 @@
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A259" s="23"/>
-      <c r="B259" s="22"/>
+      <c r="B259" s="24"/>
       <c r="C259" s="8"/>
       <c r="D259" s="14"/>
       <c r="E259" s="6"/>
@@ -6042,7 +6047,7 @@
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" s="23"/>
-      <c r="B260" s="22"/>
+      <c r="B260" s="24"/>
       <c r="C260" s="8"/>
       <c r="D260" s="14"/>
       <c r="E260" s="6"/>
@@ -6056,7 +6061,7 @@
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" s="23"/>
-      <c r="B261" s="22"/>
+      <c r="B261" s="24"/>
       <c r="C261" s="8"/>
       <c r="D261" s="14"/>
       <c r="G261" s="6"/>
@@ -6068,7 +6073,7 @@
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A262" s="23"/>
-      <c r="B262" s="20" t="s">
+      <c r="B262" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C262" s="9"/>
@@ -6104,7 +6109,7 @@
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A263" s="23"/>
-      <c r="B263" s="20"/>
+      <c r="B263" s="21"/>
       <c r="C263" s="9"/>
       <c r="D263" s="15"/>
       <c r="E263" s="3" t="str">
@@ -6122,7 +6127,7 @@
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A264" s="23"/>
-      <c r="B264" s="20"/>
+      <c r="B264" s="21"/>
       <c r="C264" s="9"/>
       <c r="D264" s="15"/>
       <c r="E264" s="3" t="str">
@@ -6140,7 +6145,7 @@
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A265" s="23"/>
-      <c r="B265" s="20"/>
+      <c r="B265" s="21"/>
       <c r="C265" s="9"/>
       <c r="D265" s="15"/>
       <c r="E265" s="3" t="str">
@@ -6160,7 +6165,7 @@
       <c r="A266" s="23">
         <v>46124</v>
       </c>
-      <c r="B266" s="21" t="s">
+      <c r="B266" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C266" s="3" t="str" cm="1">
@@ -6200,7 +6205,7 @@
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" s="23"/>
-      <c r="B267" s="21"/>
+      <c r="B267" s="22"/>
       <c r="C267" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -6222,7 +6227,7 @@
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" s="23"/>
-      <c r="B268" s="21"/>
+      <c r="B268" s="22"/>
       <c r="C268" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -6244,7 +6249,7 @@
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A269" s="23"/>
-      <c r="B269" s="21"/>
+      <c r="B269" s="22"/>
       <c r="C269" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -6266,7 +6271,7 @@
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A270" s="23"/>
-      <c r="B270" s="21"/>
+      <c r="B270" s="22"/>
       <c r="C270" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -6280,12 +6285,12 @@
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" s="23"/>
-      <c r="B271" s="21"/>
+      <c r="B271" s="22"/>
       <c r="C271" s="3" t="str">
-        <v>Driver - Shetu</v>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D271" s="13" t="str">
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E271" s="3"/>
       <c r="F271" s="17"/>
@@ -6296,13 +6301,13 @@
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A272" s="23"/>
-      <c r="B272" s="21"/>
+      <c r="B272" s="22"/>
       <c r="C272" s="5" t="str">
-        <f t="shared" ref="C272:D272" si="39">E265</f>
+        <f t="shared" ref="C272:D272" si="40">E265</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="D272" s="17" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>01748127818</v>
       </c>
       <c r="E272" s="3"/>
@@ -6314,7 +6319,7 @@
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" s="23"/>
-      <c r="B273" s="21"/>
+      <c r="B273" s="22"/>
       <c r="E273" s="3"/>
       <c r="F273" s="17"/>
       <c r="G273" s="3"/>
@@ -6326,7 +6331,7 @@
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A274" s="23"/>
-      <c r="B274" s="21"/>
+      <c r="B274" s="22"/>
       <c r="E274" s="3"/>
       <c r="F274" s="17"/>
       <c r="G274" s="3"/>
@@ -6338,7 +6343,7 @@
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" s="23"/>
-      <c r="B275" s="21"/>
+      <c r="B275" s="22"/>
       <c r="C275" s="5"/>
       <c r="D275" s="13"/>
       <c r="E275" s="3"/>
@@ -6352,7 +6357,7 @@
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A276" s="23"/>
-      <c r="B276" s="22" t="s">
+      <c r="B276" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C276" s="6" t="str" cm="1">
@@ -6392,7 +6397,7 @@
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A277" s="23"/>
-      <c r="B277" s="22"/>
+      <c r="B277" s="24"/>
       <c r="C277" s="6" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
@@ -6414,7 +6419,7 @@
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A278" s="23"/>
-      <c r="B278" s="22"/>
+      <c r="B278" s="24"/>
       <c r="C278" s="6" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
@@ -6436,7 +6441,7 @@
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A279" s="23"/>
-      <c r="B279" s="22"/>
+      <c r="B279" s="24"/>
       <c r="C279" s="6" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
@@ -6458,7 +6463,7 @@
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A280" s="23"/>
-      <c r="B280" s="22"/>
+      <c r="B280" s="24"/>
       <c r="C280" s="6" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -6476,7 +6481,7 @@
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A281" s="23"/>
-      <c r="B281" s="22"/>
+      <c r="B281" s="24"/>
       <c r="C281" s="6"/>
       <c r="D281" s="14"/>
       <c r="E281" s="6"/>
@@ -6490,7 +6495,7 @@
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A282" s="23"/>
-      <c r="B282" s="22"/>
+      <c r="B282" s="24"/>
       <c r="C282" s="6" t="str" cm="1">
         <f t="array" ref="C282:D282">E269:F269</f>
         <v>Driver - Hasan</v>
@@ -6509,7 +6514,7 @@
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A283" s="23"/>
-      <c r="B283" s="22"/>
+      <c r="B283" s="24"/>
       <c r="C283" s="8"/>
       <c r="D283" s="14"/>
       <c r="E283" s="6"/>
@@ -6523,7 +6528,7 @@
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A284" s="23"/>
-      <c r="B284" s="22"/>
+      <c r="B284" s="24"/>
       <c r="C284" s="8"/>
       <c r="D284" s="14"/>
       <c r="E284" s="6"/>
@@ -6537,7 +6542,7 @@
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A285" s="23"/>
-      <c r="B285" s="22"/>
+      <c r="B285" s="24"/>
       <c r="C285" s="8"/>
       <c r="D285" s="14"/>
       <c r="G285" s="6"/>
@@ -6549,7 +6554,7 @@
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A286" s="23"/>
-      <c r="B286" s="20" t="s">
+      <c r="B286" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C286" s="9"/>
@@ -6584,7 +6589,7 @@
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A287" s="23"/>
-      <c r="B287" s="20"/>
+      <c r="B287" s="21"/>
       <c r="C287" s="9"/>
       <c r="D287" s="15"/>
       <c r="E287" s="3" t="str">
@@ -6602,7 +6607,7 @@
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A288" s="23"/>
-      <c r="B288" s="20"/>
+      <c r="B288" s="21"/>
       <c r="C288" s="9"/>
       <c r="D288" s="15"/>
       <c r="E288" s="3" t="str">
@@ -6620,7 +6625,7 @@
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A289" s="23"/>
-      <c r="B289" s="20"/>
+      <c r="B289" s="21"/>
       <c r="C289" s="9"/>
       <c r="D289" s="15"/>
       <c r="E289" s="3" t="str">
@@ -6640,7 +6645,7 @@
       <c r="A290" s="25">
         <v>46125</v>
       </c>
-      <c r="B290" s="21" t="s">
+      <c r="B290" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C290" s="3" t="s">
@@ -6676,7 +6681,7 @@
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A291" s="25"/>
-      <c r="B291" s="21"/>
+      <c r="B291" s="22"/>
       <c r="C291" s="3" t="s">
         <v>36</v>
       </c>
@@ -6698,7 +6703,7 @@
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A292" s="25"/>
-      <c r="B292" s="21"/>
+      <c r="B292" s="22"/>
       <c r="C292" s="6" t="s">
         <v>40</v>
       </c>
@@ -6720,7 +6725,7 @@
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A293" s="25"/>
-      <c r="B293" s="21"/>
+      <c r="B293" s="22"/>
       <c r="C293" s="3" t="s">
         <v>18</v>
       </c>
@@ -6742,7 +6747,7 @@
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A294" s="25"/>
-      <c r="B294" s="21"/>
+      <c r="B294" s="22"/>
       <c r="C294" s="3" t="s">
         <v>37</v>
       </c>
@@ -6756,9 +6761,12 @@
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A295" s="25"/>
-      <c r="B295" s="21"/>
-      <c r="C295" s="24" t="s">
+      <c r="B295" s="22"/>
+      <c r="C295" s="20" t="s">
         <v>66</v>
+      </c>
+      <c r="D295" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="E295" s="3"/>
       <c r="F295" s="17"/>
@@ -6769,7 +6777,7 @@
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A296" s="25"/>
-      <c r="B296" s="21"/>
+      <c r="B296" s="22"/>
       <c r="C296" s="5" t="s">
         <v>21</v>
       </c>
@@ -6785,7 +6793,7 @@
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A297" s="25"/>
-      <c r="B297" s="21"/>
+      <c r="B297" s="22"/>
       <c r="E297" s="3"/>
       <c r="F297" s="17"/>
       <c r="G297" s="3"/>
@@ -6797,7 +6805,7 @@
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A298" s="25"/>
-      <c r="B298" s="21"/>
+      <c r="B298" s="22"/>
       <c r="E298" s="3"/>
       <c r="F298" s="17"/>
       <c r="G298" s="3"/>
@@ -6809,7 +6817,7 @@
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A299" s="25"/>
-      <c r="B299" s="21"/>
+      <c r="B299" s="22"/>
       <c r="C299" s="5"/>
       <c r="D299" s="13"/>
       <c r="E299" s="3"/>
@@ -6823,7 +6831,7 @@
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A300" s="25"/>
-      <c r="B300" s="22" t="s">
+      <c r="B300" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C300" s="6" t="s">
@@ -6859,7 +6867,7 @@
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A301" s="25"/>
-      <c r="B301" s="22"/>
+      <c r="B301" s="24"/>
       <c r="C301" s="3" t="s">
         <v>14</v>
       </c>
@@ -6881,7 +6889,7 @@
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A302" s="25"/>
-      <c r="B302" s="22"/>
+      <c r="B302" s="24"/>
       <c r="C302" s="6" t="s">
         <v>41</v>
       </c>
@@ -6903,7 +6911,7 @@
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A303" s="25"/>
-      <c r="B303" s="22"/>
+      <c r="B303" s="24"/>
       <c r="C303" s="6" t="s">
         <v>13</v>
       </c>
@@ -6925,7 +6933,7 @@
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A304" s="25"/>
-      <c r="B304" s="22"/>
+      <c r="B304" s="24"/>
       <c r="C304" s="6" t="s">
         <v>42</v>
       </c>
@@ -6943,13 +6951,13 @@
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A305" s="25"/>
-      <c r="B305" s="22"/>
+      <c r="B305" s="24"/>
       <c r="C305" s="8" t="str">
-        <f t="shared" ref="C305:D305" si="40">E293</f>
+        <f t="shared" ref="C305:D305" si="41">E293</f>
         <v>Driver - Shetu</v>
       </c>
       <c r="D305" s="18" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>01719034964</v>
       </c>
       <c r="E305" s="6"/>
@@ -6963,7 +6971,7 @@
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A306" s="25"/>
-      <c r="B306" s="22"/>
+      <c r="B306" s="24"/>
       <c r="E306" s="6"/>
       <c r="F306" s="18"/>
       <c r="G306" s="6"/>
@@ -6975,7 +6983,7 @@
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A307" s="25"/>
-      <c r="B307" s="22"/>
+      <c r="B307" s="24"/>
       <c r="C307" s="8"/>
       <c r="D307" s="14"/>
       <c r="E307" s="6"/>
@@ -6989,7 +6997,7 @@
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A308" s="25"/>
-      <c r="B308" s="22"/>
+      <c r="B308" s="24"/>
       <c r="C308" s="8"/>
       <c r="D308" s="14"/>
       <c r="E308" s="6"/>
@@ -7003,7 +7011,7 @@
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A309" s="25"/>
-      <c r="B309" s="22"/>
+      <c r="B309" s="24"/>
       <c r="C309" s="8"/>
       <c r="D309" s="14"/>
       <c r="G309" s="6"/>
@@ -7015,7 +7023,7 @@
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A310" s="25"/>
-      <c r="B310" s="20" t="s">
+      <c r="B310" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C310" s="9"/>
@@ -7047,7 +7055,7 @@
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A311" s="25"/>
-      <c r="B311" s="20"/>
+      <c r="B311" s="21"/>
       <c r="C311" s="9"/>
       <c r="D311" s="15"/>
       <c r="E311" s="3" t="s">
@@ -7065,7 +7073,7 @@
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A312" s="25"/>
-      <c r="B312" s="20"/>
+      <c r="B312" s="21"/>
       <c r="C312" s="9"/>
       <c r="D312" s="15"/>
       <c r="E312" s="3" t="s">
@@ -7083,7 +7091,7 @@
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A313" s="25"/>
-      <c r="B313" s="20"/>
+      <c r="B313" s="21"/>
       <c r="C313" s="9"/>
       <c r="D313" s="15"/>
       <c r="E313" s="5" t="s">
@@ -7103,67 +7111,67 @@
       <c r="A314" s="23">
         <v>46126</v>
       </c>
-      <c r="B314" s="21" t="s">
+      <c r="B314" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C314" s="3" t="str">
-        <f t="shared" ref="C314:D314" si="41">C300</f>
+        <f t="shared" ref="C314:D314" si="42">C300</f>
         <v>Monirul Islam  (LM)</v>
       </c>
       <c r="D314" s="13" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>01703409900</v>
       </c>
       <c r="E314" s="11" t="str">
-        <f t="shared" ref="E314:L314" si="42">E290</f>
+        <f t="shared" ref="E314:L314" si="43">E290</f>
         <v>Rakib (LM)</v>
       </c>
       <c r="F314" s="19" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>01767032267</v>
       </c>
       <c r="G314" s="3" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>Shawon Dass</v>
       </c>
       <c r="H314" s="19" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="I314" s="3" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>Salim Reza</v>
       </c>
       <c r="J314" s="19" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="K314" s="6" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>Inul Haque</v>
       </c>
       <c r="L314" s="19" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>02588855910</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A315" s="23"/>
-      <c r="B315" s="21"/>
+      <c r="B315" s="22"/>
       <c r="C315" s="3" t="str">
-        <f t="shared" ref="C315:D315" si="43">C301</f>
+        <f t="shared" ref="C315:D315" si="44">C301</f>
         <v>Abdus Sattar (LM)</v>
       </c>
       <c r="D315" s="13" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>01718676281</v>
       </c>
       <c r="E315" s="11" t="str">
-        <f t="shared" ref="E315:F315" si="44">E291</f>
+        <f t="shared" ref="E315:F315" si="45">E291</f>
         <v>Nabi (LH)</v>
       </c>
       <c r="F315" s="19" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="45"/>
         <v>01736352528</v>
       </c>
       <c r="G315" s="3"/>
@@ -7175,21 +7183,21 @@
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A316" s="23"/>
-      <c r="B316" s="21"/>
+      <c r="B316" s="22"/>
       <c r="C316" s="3" t="str">
-        <f t="shared" ref="C316:D316" si="45">C302</f>
+        <f t="shared" ref="C316:D316" si="46">C302</f>
         <v>Sazzad  (LM)</v>
       </c>
       <c r="D316" s="13" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>01719106824</v>
       </c>
       <c r="E316" s="11" t="str">
-        <f t="shared" ref="E316:F316" si="46">E292</f>
+        <f t="shared" ref="E316:F316" si="47">E292</f>
         <v>Anowar (LEM)</v>
       </c>
       <c r="F316" s="19" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>01712439152</v>
       </c>
       <c r="G316" s="3"/>
@@ -7201,21 +7209,21 @@
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A317" s="23"/>
-      <c r="B317" s="21"/>
+      <c r="B317" s="22"/>
       <c r="C317" s="3" t="str">
-        <f t="shared" ref="C317:D317" si="47">C303</f>
+        <f t="shared" ref="C317:D317" si="48">C303</f>
         <v>Jonny (LH)</v>
       </c>
       <c r="D317" s="13" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>01712441588</v>
       </c>
       <c r="E317" s="11" t="str">
-        <f t="shared" ref="E317:F317" si="48">E293</f>
+        <f t="shared" ref="E317:F317" si="49">E293</f>
         <v>Driver - Shetu</v>
       </c>
       <c r="F317" s="19" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>01719034964</v>
       </c>
       <c r="G317" s="3"/>
@@ -7227,13 +7235,13 @@
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A318" s="23"/>
-      <c r="B318" s="21"/>
+      <c r="B318" s="22"/>
       <c r="C318" s="3" t="str">
-        <f t="shared" ref="C318:D318" si="49">C304</f>
+        <f t="shared" ref="C318:D318" si="50">C304</f>
         <v>Nazmul (LEM)</v>
       </c>
       <c r="D318" s="13" t="str">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>01914595295</v>
       </c>
       <c r="G318" s="3"/>
@@ -7243,14 +7251,13 @@
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A319" s="23"/>
-      <c r="B319" s="21"/>
-      <c r="C319" s="3" t="str">
-        <f t="shared" ref="C319:D319" si="50">C305</f>
-        <v>Driver - Shetu</v>
+      <c r="B319" s="22"/>
+      <c r="C319" s="3" t="str" cm="1">
+        <f t="array" ref="C319:D319">E313:F313</f>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D319" s="13" t="str">
-        <f t="shared" si="50"/>
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E319" s="3"/>
       <c r="F319" s="17"/>
@@ -7261,7 +7268,7 @@
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A320" s="23"/>
-      <c r="B320" s="21"/>
+      <c r="B320" s="22"/>
       <c r="C320" s="5"/>
       <c r="D320" s="17"/>
       <c r="E320" s="3"/>
@@ -7273,7 +7280,7 @@
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A321" s="23"/>
-      <c r="B321" s="21"/>
+      <c r="B321" s="22"/>
       <c r="E321" s="3"/>
       <c r="F321" s="17"/>
       <c r="G321" s="3"/>
@@ -7285,7 +7292,7 @@
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A322" s="23"/>
-      <c r="B322" s="21"/>
+      <c r="B322" s="22"/>
       <c r="E322" s="3"/>
       <c r="F322" s="17"/>
       <c r="G322" s="3"/>
@@ -7297,7 +7304,7 @@
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A323" s="23"/>
-      <c r="B323" s="21"/>
+      <c r="B323" s="22"/>
       <c r="C323" s="5"/>
       <c r="D323" s="13"/>
       <c r="E323" s="3"/>
@@ -7311,7 +7318,7 @@
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A324" s="23"/>
-      <c r="B324" s="22" t="s">
+      <c r="B324" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C324" s="6" t="str">
@@ -7357,7 +7364,7 @@
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A325" s="23"/>
-      <c r="B325" s="22"/>
+      <c r="B325" s="24"/>
       <c r="C325" s="6" t="str">
         <f t="shared" ref="C325:D325" si="54">C291</f>
         <v>Monzur Kader (LM)</v>
@@ -7383,7 +7390,7 @@
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A326" s="23"/>
-      <c r="B326" s="22"/>
+      <c r="B326" s="24"/>
       <c r="C326" s="6" t="str">
         <f t="shared" ref="C326:D326" si="56">C292</f>
         <v>Mosaddek  (LM)</v>
@@ -7409,7 +7416,7 @@
     </row>
     <row r="327" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A327" s="23"/>
-      <c r="B327" s="22"/>
+      <c r="B327" s="24"/>
       <c r="C327" s="6" t="str">
         <f t="shared" ref="C327:D327" si="58">C293</f>
         <v>Abdus Salam (LM)</v>
@@ -7435,7 +7442,7 @@
     </row>
     <row r="328" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A328" s="23"/>
-      <c r="B328" s="22"/>
+      <c r="B328" s="24"/>
       <c r="C328" s="6" t="str">
         <f t="shared" ref="C328:D328" si="60">C294</f>
         <v>Salim Reza-2 (LH)</v>
@@ -7455,14 +7462,14 @@
     </row>
     <row r="329" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A329" s="23"/>
-      <c r="B329" s="22"/>
+      <c r="B329" s="24"/>
       <c r="C329" s="6" t="str">
         <f t="shared" ref="C329:D329" si="61">C295</f>
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D329" s="14">
+      <c r="D329" s="14" t="str">
         <f t="shared" si="61"/>
-        <v>0</v>
+        <v>01723504940</v>
       </c>
       <c r="E329" s="6"/>
       <c r="F329" s="18"/>
@@ -7475,14 +7482,13 @@
     </row>
     <row r="330" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A330" s="23"/>
-      <c r="B330" s="22"/>
-      <c r="C330" s="6" t="str">
-        <f t="shared" ref="C330:D330" si="62">C296</f>
-        <v>Driver - Hasan</v>
+      <c r="B330" s="24"/>
+      <c r="C330" s="6" t="str" cm="1">
+        <f t="array" ref="C330:D330">E317:F317</f>
+        <v>Driver - Shetu</v>
       </c>
       <c r="D330" s="14" t="str">
-        <f t="shared" si="62"/>
-        <v>01730824934</v>
+        <v>01719034964</v>
       </c>
       <c r="E330" s="6"/>
       <c r="F330" s="18"/>
@@ -7495,7 +7501,7 @@
     </row>
     <row r="331" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A331" s="23"/>
-      <c r="B331" s="22"/>
+      <c r="B331" s="24"/>
       <c r="C331" s="8"/>
       <c r="D331" s="14"/>
       <c r="E331" s="6"/>
@@ -7509,7 +7515,7 @@
     </row>
     <row r="332" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A332" s="23"/>
-      <c r="B332" s="22"/>
+      <c r="B332" s="24"/>
       <c r="C332" s="8"/>
       <c r="D332" s="14"/>
       <c r="E332" s="6"/>
@@ -7523,7 +7529,7 @@
     </row>
     <row r="333" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A333" s="23"/>
-      <c r="B333" s="22"/>
+      <c r="B333" s="24"/>
       <c r="C333" s="8"/>
       <c r="D333" s="14"/>
       <c r="G333" s="6"/>
@@ -7535,55 +7541,55 @@
     </row>
     <row r="334" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A334" s="23"/>
-      <c r="B334" s="20" t="s">
+      <c r="B334" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C334" s="9"/>
       <c r="D334" s="15"/>
       <c r="E334" s="3" t="str">
-        <f t="shared" ref="E334:L334" si="63">E310</f>
+        <f t="shared" ref="E334:L334" si="62">E310</f>
         <v>Sumon (LM)</v>
       </c>
       <c r="F334" s="17" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>01726258394</v>
       </c>
       <c r="G334" s="11" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>Abdur Rafique</v>
       </c>
       <c r="H334" s="19" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="I334" s="11" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>Abul Kalam Azad</v>
       </c>
       <c r="J334" s="19" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="K334" s="3" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>Monzur Ahmed</v>
       </c>
       <c r="L334" s="19" t="str">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>02588855910</v>
       </c>
     </row>
     <row r="335" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A335" s="23"/>
-      <c r="B335" s="20"/>
+      <c r="B335" s="21"/>
       <c r="C335" s="9"/>
       <c r="D335" s="15"/>
       <c r="E335" s="3" t="str">
-        <f t="shared" ref="E335:F335" si="64">E311</f>
+        <f t="shared" ref="E335:F335" si="63">E311</f>
         <v>Arafat (LH)</v>
       </c>
       <c r="F335" s="17" t="str">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>01755149115</v>
       </c>
       <c r="G335" s="11"/>
@@ -7595,15 +7601,15 @@
     </row>
     <row r="336" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A336" s="23"/>
-      <c r="B336" s="20"/>
+      <c r="B336" s="21"/>
       <c r="C336" s="9"/>
       <c r="D336" s="15"/>
       <c r="E336" s="3" t="str">
-        <f t="shared" ref="E336:F336" si="65">E312</f>
+        <f t="shared" ref="E336:F336" si="64">E312</f>
         <v>Mamun (LH)</v>
       </c>
       <c r="F336" s="17" t="str">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>01718106022</v>
       </c>
       <c r="G336" s="11"/>
@@ -7615,15 +7621,15 @@
     </row>
     <row r="337" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A337" s="23"/>
-      <c r="B337" s="20"/>
+      <c r="B337" s="21"/>
       <c r="C337" s="9"/>
       <c r="D337" s="15"/>
       <c r="E337" s="3" t="str">
-        <f t="shared" ref="E337:F337" si="66">E313</f>
+        <f t="shared" ref="E337:F337" si="65">E313</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="F337" s="17" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="65"/>
         <v>01730824934</v>
       </c>
       <c r="G337" s="11"/>
@@ -7637,7 +7643,7 @@
       <c r="A338" s="23">
         <v>46127</v>
       </c>
-      <c r="B338" s="21" t="s">
+      <c r="B338" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C338" s="3" t="str" cm="1">
@@ -7647,12 +7653,12 @@
       <c r="D338" s="13" t="str">
         <v>01703409900</v>
       </c>
-      <c r="E338" s="11" t="str" cm="1">
-        <f t="array" ref="E338:F341">E334:F337</f>
-        <v>Sumon (LM)</v>
-      </c>
-      <c r="F338" s="19" t="str">
-        <v>01726258394</v>
+      <c r="E338" s="3" t="str" cm="1">
+        <f t="array" ref="E338:F341">E324:F327</f>
+        <v>Maruf Hossain (LM)</v>
+      </c>
+      <c r="F338" s="17" t="str">
+        <v>01943368198</v>
       </c>
       <c r="G338" s="3" t="str" cm="1">
         <f t="array" ref="G338:H338">G324:H324</f>
@@ -7678,18 +7684,18 @@
     </row>
     <row r="339" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A339" s="23"/>
-      <c r="B339" s="21"/>
+      <c r="B339" s="22"/>
       <c r="C339" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
       <c r="D339" s="13" t="str">
         <v>01718676281</v>
       </c>
-      <c r="E339" s="11" t="str">
-        <v>Arafat (LH)</v>
-      </c>
-      <c r="F339" s="19" t="str">
-        <v>01755149115</v>
+      <c r="E339" s="3" t="str">
+        <v>Sahjahan (LEM)</v>
+      </c>
+      <c r="F339" s="17" t="str">
+        <v>01724267460</v>
       </c>
       <c r="G339" s="3"/>
       <c r="H339" s="4"/>
@@ -7700,18 +7706,18 @@
     </row>
     <row r="340" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A340" s="23"/>
-      <c r="B340" s="21"/>
+      <c r="B340" s="22"/>
       <c r="C340" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
       <c r="D340" s="13" t="str">
         <v>01719106824</v>
       </c>
-      <c r="E340" s="11" t="str">
-        <v>Mamun (LH)</v>
-      </c>
-      <c r="F340" s="19" t="str">
-        <v>01718106022</v>
+      <c r="E340" s="3" t="str">
+        <v>Fuad (LH)</v>
+      </c>
+      <c r="F340" s="17" t="str">
+        <v>01718279112</v>
       </c>
       <c r="G340" s="3"/>
       <c r="H340" s="4"/>
@@ -7722,18 +7728,18 @@
     </row>
     <row r="341" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A341" s="23"/>
-      <c r="B341" s="21"/>
+      <c r="B341" s="22"/>
       <c r="C341" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
       <c r="D341" s="13" t="str">
         <v>01712441588</v>
       </c>
-      <c r="E341" s="11" t="str">
-        <v>Driver - Hasan</v>
-      </c>
-      <c r="F341" s="19" t="str">
-        <v>01730824934</v>
+      <c r="E341" s="3" t="str">
+        <v>Driver - Noyon</v>
+      </c>
+      <c r="F341" s="17" t="str">
+        <v>01748127818</v>
       </c>
       <c r="G341" s="3"/>
       <c r="H341" s="4"/>
@@ -7744,7 +7750,7 @@
     </row>
     <row r="342" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A342" s="23"/>
-      <c r="B342" s="21"/>
+      <c r="B342" s="22"/>
       <c r="C342" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -7758,7 +7764,7 @@
     </row>
     <row r="343" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A343" s="23"/>
-      <c r="B343" s="21"/>
+      <c r="B343" s="22"/>
       <c r="C343" s="3"/>
       <c r="D343" s="13"/>
       <c r="E343" s="3"/>
@@ -7770,13 +7776,13 @@
     </row>
     <row r="344" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A344" s="23"/>
-      <c r="B344" s="21"/>
+      <c r="B344" s="22"/>
       <c r="C344" s="5" t="str">
-        <f t="shared" ref="C344:D344" si="67">E337</f>
+        <f t="shared" ref="C344:D344" si="66">E337</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="D344" s="17" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="66"/>
         <v>01730824934</v>
       </c>
       <c r="E344" s="3"/>
@@ -7788,7 +7794,7 @@
     </row>
     <row r="345" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A345" s="23"/>
-      <c r="B345" s="21"/>
+      <c r="B345" s="22"/>
       <c r="E345" s="3"/>
       <c r="F345" s="17"/>
       <c r="G345" s="3"/>
@@ -7800,7 +7806,7 @@
     </row>
     <row r="346" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A346" s="23"/>
-      <c r="B346" s="21"/>
+      <c r="B346" s="22"/>
       <c r="E346" s="3"/>
       <c r="F346" s="17"/>
       <c r="G346" s="3"/>
@@ -7812,7 +7818,7 @@
     </row>
     <row r="347" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A347" s="23"/>
-      <c r="B347" s="21"/>
+      <c r="B347" s="22"/>
       <c r="C347" s="5"/>
       <c r="D347" s="13"/>
       <c r="E347" s="3"/>
@@ -7826,7 +7832,7 @@
     </row>
     <row r="348" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A348" s="23"/>
-      <c r="B348" s="22" t="s">
+      <c r="B348" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C348" s="6" t="str" cm="1">
@@ -7836,12 +7842,12 @@
       <c r="D348" s="14" t="str">
         <v>01758212103</v>
       </c>
-      <c r="E348" s="3" t="str" cm="1">
-        <f t="array" ref="E348:F351">E314:F317</f>
-        <v>Rakib (LM)</v>
-      </c>
-      <c r="F348" s="13" t="str">
-        <v>01767032267</v>
+      <c r="E348" s="11" t="str" cm="1">
+        <f t="array" ref="E348:F351">E334:F337</f>
+        <v>Sumon (LM)</v>
+      </c>
+      <c r="F348" s="19" t="str">
+        <v>01726258394</v>
       </c>
       <c r="G348" s="6" t="str" cm="1">
         <f t="array" ref="G348:H348">G334:H334</f>
@@ -7867,18 +7873,18 @@
     </row>
     <row r="349" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A349" s="23"/>
-      <c r="B349" s="22"/>
+      <c r="B349" s="24"/>
       <c r="C349" s="6" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
       <c r="D349" s="14" t="str">
         <v>01705614054</v>
       </c>
-      <c r="E349" s="3" t="str">
-        <v>Nabi (LH)</v>
-      </c>
-      <c r="F349" s="13" t="str">
-        <v>01736352528</v>
+      <c r="E349" s="11" t="str">
+        <v>Arafat (LH)</v>
+      </c>
+      <c r="F349" s="19" t="str">
+        <v>01755149115</v>
       </c>
       <c r="G349" s="6"/>
       <c r="H349" s="7"/>
@@ -7893,18 +7899,18 @@
     </row>
     <row r="350" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A350" s="23"/>
-      <c r="B350" s="22"/>
+      <c r="B350" s="24"/>
       <c r="C350" s="6" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
       <c r="D350" s="14" t="str">
         <v>01674272353</v>
       </c>
-      <c r="E350" s="3" t="str">
-        <v>Anowar (LEM)</v>
-      </c>
-      <c r="F350" s="13" t="str">
-        <v>01712439152</v>
+      <c r="E350" s="11" t="str">
+        <v>Mamun (LH)</v>
+      </c>
+      <c r="F350" s="19" t="str">
+        <v>01718106022</v>
       </c>
       <c r="G350" s="6"/>
       <c r="H350" s="7"/>
@@ -7915,18 +7921,18 @@
     </row>
     <row r="351" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A351" s="23"/>
-      <c r="B351" s="22"/>
+      <c r="B351" s="24"/>
       <c r="C351" s="6" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
       <c r="D351" s="14" t="str">
         <v>01756101919</v>
       </c>
-      <c r="E351" s="3" t="str">
-        <v>Driver - Shetu</v>
-      </c>
-      <c r="F351" s="13" t="str">
-        <v>01719034964</v>
+      <c r="E351" s="11" t="str">
+        <v>Driver - Hasan</v>
+      </c>
+      <c r="F351" s="19" t="str">
+        <v>01730824934</v>
       </c>
       <c r="G351" s="6"/>
       <c r="H351" s="7"/>
@@ -7937,7 +7943,7 @@
     </row>
     <row r="352" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A352" s="23"/>
-      <c r="B352" s="22"/>
+      <c r="B352" s="24"/>
       <c r="C352" s="6" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -7955,12 +7961,12 @@
     </row>
     <row r="353" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A353" s="23"/>
-      <c r="B353" s="22"/>
+      <c r="B353" s="24"/>
       <c r="C353" s="6" t="str">
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D353" s="14">
-        <v>0</v>
+      <c r="D353" s="14" t="str">
+        <v>01723504940</v>
       </c>
       <c r="E353" s="6"/>
       <c r="F353" s="18"/>
@@ -7973,9 +7979,9 @@
     </row>
     <row r="354" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A354" s="23"/>
-      <c r="B354" s="22"/>
+      <c r="B354" s="24"/>
       <c r="C354" s="6" t="str" cm="1">
-        <f t="array" ref="C354:D354">E341:F341</f>
+        <f t="array" ref="C354:D354">E351:F351</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="D354" s="14" t="str">
@@ -7992,7 +7998,7 @@
     </row>
     <row r="355" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A355" s="23"/>
-      <c r="B355" s="22"/>
+      <c r="B355" s="24"/>
       <c r="C355" s="8"/>
       <c r="D355" s="14"/>
       <c r="E355" s="6"/>
@@ -8006,7 +8012,7 @@
     </row>
     <row r="356" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A356" s="23"/>
-      <c r="B356" s="22"/>
+      <c r="B356" s="24"/>
       <c r="C356" s="8"/>
       <c r="D356" s="14"/>
       <c r="E356" s="6"/>
@@ -8020,7 +8026,7 @@
     </row>
     <row r="357" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A357" s="23"/>
-      <c r="B357" s="22"/>
+      <c r="B357" s="24"/>
       <c r="C357" s="8"/>
       <c r="D357" s="14"/>
       <c r="G357" s="6"/>
@@ -8032,17 +8038,17 @@
     </row>
     <row r="358" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A358" s="23"/>
-      <c r="B358" s="20" t="s">
+      <c r="B358" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C358" s="9"/>
       <c r="D358" s="15"/>
       <c r="E358" s="3" t="str" cm="1">
-        <f t="array" ref="E358:F361">E324:F327</f>
-        <v>Maruf Hossain (LM)</v>
-      </c>
-      <c r="F358" s="17" t="str">
-        <v>01943368198</v>
+        <f t="array" ref="E358:F361">E314:F317</f>
+        <v>Rakib (LM)</v>
+      </c>
+      <c r="F358" s="13" t="str">
+        <v>01767032267</v>
       </c>
       <c r="G358" s="11" t="str" cm="1">
         <f t="array" ref="G358:H358">G314:H314</f>
@@ -8068,14 +8074,14 @@
     </row>
     <row r="359" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A359" s="23"/>
-      <c r="B359" s="20"/>
+      <c r="B359" s="21"/>
       <c r="C359" s="9"/>
       <c r="D359" s="15"/>
       <c r="E359" s="3" t="str">
-        <v>Sahjahan (LEM)</v>
-      </c>
-      <c r="F359" s="17" t="str">
-        <v>01724267460</v>
+        <v>Nabi (LH)</v>
+      </c>
+      <c r="F359" s="13" t="str">
+        <v>01736352528</v>
       </c>
       <c r="G359" s="11"/>
       <c r="H359" s="10"/>
@@ -8086,14 +8092,14 @@
     </row>
     <row r="360" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A360" s="23"/>
-      <c r="B360" s="20"/>
+      <c r="B360" s="21"/>
       <c r="C360" s="9"/>
       <c r="D360" s="15"/>
       <c r="E360" s="3" t="str">
-        <v>Fuad (LH)</v>
-      </c>
-      <c r="F360" s="17" t="str">
-        <v>01718279112</v>
+        <v>Anowar (LEM)</v>
+      </c>
+      <c r="F360" s="13" t="str">
+        <v>01712439152</v>
       </c>
       <c r="G360" s="11"/>
       <c r="H360" s="10"/>
@@ -8104,14 +8110,14 @@
     </row>
     <row r="361" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A361" s="23"/>
-      <c r="B361" s="20"/>
+      <c r="B361" s="21"/>
       <c r="C361" s="9"/>
       <c r="D361" s="15"/>
       <c r="E361" s="3" t="str">
-        <v>Driver - Noyon</v>
-      </c>
-      <c r="F361" s="17" t="str">
-        <v>01748127818</v>
+        <v>Driver - Shetu</v>
+      </c>
+      <c r="F361" s="13" t="str">
+        <v>01719034964</v>
       </c>
       <c r="G361" s="11"/>
       <c r="H361" s="10"/>
@@ -8124,7 +8130,7 @@
       <c r="A362" s="23">
         <v>46128</v>
       </c>
-      <c r="B362" s="21" t="s">
+      <c r="B362" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C362" s="3" t="str" cm="1">
@@ -8135,7 +8141,7 @@
         <v>01703409900</v>
       </c>
       <c r="E362" s="11" t="str" cm="1">
-        <f t="array" ref="E362:F365">E358:F361</f>
+        <f t="array" ref="E362:F365">E338:F341</f>
         <v>Maruf Hossain (LM)</v>
       </c>
       <c r="F362" s="19" t="str">
@@ -8164,7 +8170,7 @@
     </row>
     <row r="363" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A363" s="23"/>
-      <c r="B363" s="21"/>
+      <c r="B363" s="22"/>
       <c r="C363" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -8186,7 +8192,7 @@
     </row>
     <row r="364" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A364" s="23"/>
-      <c r="B364" s="21"/>
+      <c r="B364" s="22"/>
       <c r="C364" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -8208,7 +8214,7 @@
     </row>
     <row r="365" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A365" s="23"/>
-      <c r="B365" s="21"/>
+      <c r="B365" s="22"/>
       <c r="C365" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -8230,7 +8236,7 @@
     </row>
     <row r="366" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A366" s="23"/>
-      <c r="B366" s="21"/>
+      <c r="B366" s="22"/>
       <c r="C366" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -8244,7 +8250,7 @@
     </row>
     <row r="367" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A367" s="23"/>
-      <c r="B367" s="21"/>
+      <c r="B367" s="22"/>
       <c r="C367" s="3"/>
       <c r="D367" s="13"/>
       <c r="E367" s="3"/>
@@ -8256,13 +8262,13 @@
     </row>
     <row r="368" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A368" s="23"/>
-      <c r="B368" s="21"/>
+      <c r="B368" s="22"/>
       <c r="C368" s="5" t="str">
-        <f t="shared" ref="C368:D368" si="68">E361</f>
+        <f t="shared" ref="C368:D368" si="67">E341</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="D368" s="17" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>01748127818</v>
       </c>
       <c r="E368" s="3"/>
@@ -8274,7 +8280,7 @@
     </row>
     <row r="369" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A369" s="23"/>
-      <c r="B369" s="21"/>
+      <c r="B369" s="22"/>
       <c r="E369" s="3"/>
       <c r="F369" s="17"/>
       <c r="G369" s="3"/>
@@ -8286,7 +8292,7 @@
     </row>
     <row r="370" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A370" s="23"/>
-      <c r="B370" s="21"/>
+      <c r="B370" s="22"/>
       <c r="E370" s="3"/>
       <c r="F370" s="17"/>
       <c r="G370" s="3"/>
@@ -8298,7 +8304,7 @@
     </row>
     <row r="371" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A371" s="23"/>
-      <c r="B371" s="21"/>
+      <c r="B371" s="22"/>
       <c r="C371" s="5"/>
       <c r="D371" s="13"/>
       <c r="E371" s="3"/>
@@ -8312,7 +8318,7 @@
     </row>
     <row r="372" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A372" s="23"/>
-      <c r="B372" s="22" t="s">
+      <c r="B372" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C372" s="6" t="str" cm="1">
@@ -8323,7 +8329,7 @@
         <v>01703409900</v>
       </c>
       <c r="E372" s="3" t="str" cm="1">
-        <f t="array" ref="E372:F375">E338:F341</f>
+        <f t="array" ref="E372:F375">E348:F351</f>
         <v>Sumon (LM)</v>
       </c>
       <c r="F372" s="13" t="str">
@@ -8352,7 +8358,7 @@
     </row>
     <row r="373" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A373" s="23"/>
-      <c r="B373" s="22"/>
+      <c r="B373" s="24"/>
       <c r="C373" s="6" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -8374,7 +8380,7 @@
     </row>
     <row r="374" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A374" s="23"/>
-      <c r="B374" s="22"/>
+      <c r="B374" s="24"/>
       <c r="C374" s="6" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -8396,7 +8402,7 @@
     </row>
     <row r="375" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A375" s="23"/>
-      <c r="B375" s="22"/>
+      <c r="B375" s="24"/>
       <c r="C375" s="6" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -8418,7 +8424,7 @@
     </row>
     <row r="376" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A376" s="23"/>
-      <c r="B376" s="22"/>
+      <c r="B376" s="24"/>
       <c r="C376" s="6" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -8436,12 +8442,12 @@
     </row>
     <row r="377" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A377" s="23"/>
-      <c r="B377" s="22"/>
+      <c r="B377" s="24"/>
       <c r="C377" s="6" t="str">
-        <v>Driver - Shetu</v>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D377" s="14" t="str">
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E377" s="6"/>
       <c r="F377" s="18"/>
@@ -8454,7 +8460,7 @@
     </row>
     <row r="378" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A378" s="23"/>
-      <c r="B378" s="22"/>
+      <c r="B378" s="24"/>
       <c r="C378" s="6" t="str" cm="1">
         <f t="array" ref="C378:D378">E365:F365</f>
         <v>Driver - Noyon</v>
@@ -8473,7 +8479,7 @@
     </row>
     <row r="379" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A379" s="23"/>
-      <c r="B379" s="22"/>
+      <c r="B379" s="24"/>
       <c r="C379" s="8"/>
       <c r="D379" s="14"/>
       <c r="E379" s="6"/>
@@ -8487,7 +8493,7 @@
     </row>
     <row r="380" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A380" s="23"/>
-      <c r="B380" s="22"/>
+      <c r="B380" s="24"/>
       <c r="C380" s="8"/>
       <c r="D380" s="14"/>
       <c r="E380" s="6"/>
@@ -8501,7 +8507,7 @@
     </row>
     <row r="381" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A381" s="23"/>
-      <c r="B381" s="22"/>
+      <c r="B381" s="24"/>
       <c r="C381" s="8"/>
       <c r="D381" s="14"/>
       <c r="G381" s="6"/>
@@ -8513,13 +8519,13 @@
     </row>
     <row r="382" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A382" s="23"/>
-      <c r="B382" s="20" t="s">
+      <c r="B382" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C382" s="9"/>
       <c r="D382" s="15"/>
       <c r="E382" s="3" t="str" cm="1">
-        <f t="array" ref="E382:F385">E348:F351</f>
+        <f t="array" ref="E382:F385">E358:F361</f>
         <v>Rakib (LM)</v>
       </c>
       <c r="F382" s="17" t="str">
@@ -8548,7 +8554,7 @@
     </row>
     <row r="383" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A383" s="23"/>
-      <c r="B383" s="20"/>
+      <c r="B383" s="21"/>
       <c r="C383" s="9"/>
       <c r="D383" s="15"/>
       <c r="E383" s="3" t="str">
@@ -8566,7 +8572,7 @@
     </row>
     <row r="384" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A384" s="23"/>
-      <c r="B384" s="20"/>
+      <c r="B384" s="21"/>
       <c r="C384" s="9"/>
       <c r="D384" s="15"/>
       <c r="E384" s="3" t="str">
@@ -8584,7 +8590,7 @@
     </row>
     <row r="385" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A385" s="23"/>
-      <c r="B385" s="20"/>
+      <c r="B385" s="21"/>
       <c r="C385" s="9"/>
       <c r="D385" s="15"/>
       <c r="E385" s="3" t="str">
@@ -8604,7 +8610,7 @@
       <c r="A386" s="23">
         <v>46129</v>
       </c>
-      <c r="B386" s="21" t="s">
+      <c r="B386" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C386" s="3" t="str" cm="1">
@@ -8645,7 +8651,7 @@
     </row>
     <row r="387" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A387" s="23"/>
-      <c r="B387" s="21"/>
+      <c r="B387" s="22"/>
       <c r="C387" s="3" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
@@ -8667,7 +8673,7 @@
     </row>
     <row r="388" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A388" s="23"/>
-      <c r="B388" s="21"/>
+      <c r="B388" s="22"/>
       <c r="C388" s="3" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
@@ -8689,7 +8695,7 @@
     </row>
     <row r="389" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A389" s="23"/>
-      <c r="B389" s="21"/>
+      <c r="B389" s="22"/>
       <c r="C389" s="3" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
@@ -8711,7 +8717,7 @@
     </row>
     <row r="390" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A390" s="23"/>
-      <c r="B390" s="21"/>
+      <c r="B390" s="22"/>
       <c r="C390" s="3" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -8725,12 +8731,12 @@
     </row>
     <row r="391" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A391" s="23"/>
-      <c r="B391" s="21"/>
+      <c r="B391" s="22"/>
       <c r="C391" s="3" t="str">
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D391" s="13">
-        <v>0</v>
+      <c r="D391" s="13" t="str">
+        <v>01723504940</v>
       </c>
       <c r="E391" s="3"/>
       <c r="F391" s="17"/>
@@ -8741,13 +8747,13 @@
     </row>
     <row r="392" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A392" s="23"/>
-      <c r="B392" s="21"/>
+      <c r="B392" s="22"/>
       <c r="C392" s="5" t="str">
-        <f t="shared" ref="C392:D392" si="69">E385</f>
+        <f t="shared" ref="C392:D392" si="68">E385</f>
         <v>Driver - Shetu</v>
       </c>
       <c r="D392" s="17" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>01719034964</v>
       </c>
       <c r="E392" s="3"/>
@@ -8759,7 +8765,7 @@
     </row>
     <row r="393" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A393" s="23"/>
-      <c r="B393" s="21"/>
+      <c r="B393" s="22"/>
       <c r="E393" s="3"/>
       <c r="F393" s="17"/>
       <c r="G393" s="3"/>
@@ -8771,7 +8777,7 @@
     </row>
     <row r="394" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A394" s="23"/>
-      <c r="B394" s="21"/>
+      <c r="B394" s="22"/>
       <c r="E394" s="3"/>
       <c r="F394" s="17"/>
       <c r="G394" s="3"/>
@@ -8783,7 +8789,7 @@
     </row>
     <row r="395" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A395" s="23"/>
-      <c r="B395" s="21"/>
+      <c r="B395" s="22"/>
       <c r="C395" s="5"/>
       <c r="D395" s="13"/>
       <c r="E395" s="3"/>
@@ -8797,7 +8803,7 @@
     </row>
     <row r="396" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A396" s="23"/>
-      <c r="B396" s="22" t="s">
+      <c r="B396" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C396" s="6" t="str" cm="1">
@@ -8838,7 +8844,7 @@
     </row>
     <row r="397" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A397" s="23"/>
-      <c r="B397" s="22"/>
+      <c r="B397" s="24"/>
       <c r="C397" s="6" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -8860,7 +8866,7 @@
     </row>
     <row r="398" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A398" s="23"/>
-      <c r="B398" s="22"/>
+      <c r="B398" s="24"/>
       <c r="C398" s="6" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -8882,7 +8888,7 @@
     </row>
     <row r="399" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A399" s="23"/>
-      <c r="B399" s="22"/>
+      <c r="B399" s="24"/>
       <c r="C399" s="6" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -8904,7 +8910,7 @@
     </row>
     <row r="400" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A400" s="23"/>
-      <c r="B400" s="22"/>
+      <c r="B400" s="24"/>
       <c r="C400" s="6" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -8922,7 +8928,7 @@
     </row>
     <row r="401" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A401" s="23"/>
-      <c r="B401" s="22"/>
+      <c r="B401" s="24"/>
       <c r="C401" s="6"/>
       <c r="D401" s="14"/>
       <c r="E401" s="6"/>
@@ -8936,7 +8942,7 @@
     </row>
     <row r="402" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A402" s="23"/>
-      <c r="B402" s="22"/>
+      <c r="B402" s="24"/>
       <c r="C402" s="6" t="str" cm="1">
         <f t="array" ref="C402:D402">E389:F389</f>
         <v>Driver - Hasan</v>
@@ -8955,7 +8961,7 @@
     </row>
     <row r="403" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A403" s="23"/>
-      <c r="B403" s="22"/>
+      <c r="B403" s="24"/>
       <c r="C403" s="8"/>
       <c r="D403" s="14"/>
       <c r="E403" s="6"/>
@@ -8969,7 +8975,7 @@
     </row>
     <row r="404" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A404" s="23"/>
-      <c r="B404" s="22"/>
+      <c r="B404" s="24"/>
       <c r="C404" s="8"/>
       <c r="D404" s="14"/>
       <c r="E404" s="6"/>
@@ -8983,7 +8989,7 @@
     </row>
     <row r="405" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A405" s="23"/>
-      <c r="B405" s="22"/>
+      <c r="B405" s="24"/>
       <c r="C405" s="8"/>
       <c r="D405" s="14"/>
       <c r="G405" s="6"/>
@@ -8995,7 +9001,7 @@
     </row>
     <row r="406" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A406" s="23"/>
-      <c r="B406" s="20" t="s">
+      <c r="B406" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C406" s="9"/>
@@ -9031,7 +9037,7 @@
     </row>
     <row r="407" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A407" s="23"/>
-      <c r="B407" s="20"/>
+      <c r="B407" s="21"/>
       <c r="C407" s="9"/>
       <c r="D407" s="15"/>
       <c r="E407" s="3" t="str">
@@ -9049,7 +9055,7 @@
     </row>
     <row r="408" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A408" s="23"/>
-      <c r="B408" s="20"/>
+      <c r="B408" s="21"/>
       <c r="C408" s="9"/>
       <c r="D408" s="15"/>
       <c r="E408" s="3" t="str">
@@ -9067,7 +9073,7 @@
     </row>
     <row r="409" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A409" s="23"/>
-      <c r="B409" s="20"/>
+      <c r="B409" s="21"/>
       <c r="C409" s="9"/>
       <c r="D409" s="15"/>
       <c r="E409" s="3" t="str">
@@ -9087,7 +9093,7 @@
       <c r="A410" s="23">
         <v>46130</v>
       </c>
-      <c r="B410" s="21" t="s">
+      <c r="B410" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C410" s="3" t="str" cm="1">
@@ -9127,7 +9133,7 @@
     </row>
     <row r="411" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A411" s="23"/>
-      <c r="B411" s="21"/>
+      <c r="B411" s="22"/>
       <c r="C411" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -9149,7 +9155,7 @@
     </row>
     <row r="412" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A412" s="23"/>
-      <c r="B412" s="21"/>
+      <c r="B412" s="22"/>
       <c r="C412" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -9171,7 +9177,7 @@
     </row>
     <row r="413" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A413" s="23"/>
-      <c r="B413" s="21"/>
+      <c r="B413" s="22"/>
       <c r="C413" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -9193,7 +9199,7 @@
     </row>
     <row r="414" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A414" s="23"/>
-      <c r="B414" s="21"/>
+      <c r="B414" s="22"/>
       <c r="C414" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -9207,12 +9213,12 @@
     </row>
     <row r="415" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A415" s="23"/>
-      <c r="B415" s="21"/>
+      <c r="B415" s="22"/>
       <c r="C415" s="3" t="str">
-        <v>Driver - Shetu</v>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D415" s="13" t="str">
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E415" s="3"/>
       <c r="F415" s="17"/>
@@ -9223,13 +9229,13 @@
     </row>
     <row r="416" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A416" s="23"/>
-      <c r="B416" s="21"/>
+      <c r="B416" s="22"/>
       <c r="C416" s="5" t="str">
-        <f t="shared" ref="C416:D416" si="70">E409</f>
+        <f t="shared" ref="C416:D416" si="69">E409</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="D416" s="17" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>01748127818</v>
       </c>
       <c r="E416" s="3"/>
@@ -9241,7 +9247,7 @@
     </row>
     <row r="417" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A417" s="23"/>
-      <c r="B417" s="21"/>
+      <c r="B417" s="22"/>
       <c r="E417" s="3"/>
       <c r="F417" s="17"/>
       <c r="G417" s="3"/>
@@ -9253,7 +9259,7 @@
     </row>
     <row r="418" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A418" s="23"/>
-      <c r="B418" s="21"/>
+      <c r="B418" s="22"/>
       <c r="E418" s="3"/>
       <c r="F418" s="17"/>
       <c r="G418" s="3"/>
@@ -9265,7 +9271,7 @@
     </row>
     <row r="419" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A419" s="23"/>
-      <c r="B419" s="21"/>
+      <c r="B419" s="22"/>
       <c r="C419" s="5"/>
       <c r="D419" s="13"/>
       <c r="E419" s="3"/>
@@ -9279,7 +9285,7 @@
     </row>
     <row r="420" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A420" s="23"/>
-      <c r="B420" s="22" t="s">
+      <c r="B420" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C420" s="6" t="str" cm="1">
@@ -9319,7 +9325,7 @@
     </row>
     <row r="421" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A421" s="23"/>
-      <c r="B421" s="22"/>
+      <c r="B421" s="24"/>
       <c r="C421" s="6" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
@@ -9341,7 +9347,7 @@
     </row>
     <row r="422" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A422" s="23"/>
-      <c r="B422" s="22"/>
+      <c r="B422" s="24"/>
       <c r="C422" s="6" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
@@ -9363,7 +9369,7 @@
     </row>
     <row r="423" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A423" s="23"/>
-      <c r="B423" s="22"/>
+      <c r="B423" s="24"/>
       <c r="C423" s="6" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
@@ -9385,7 +9391,7 @@
     </row>
     <row r="424" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A424" s="23"/>
-      <c r="B424" s="22"/>
+      <c r="B424" s="24"/>
       <c r="C424" s="6" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -9403,7 +9409,7 @@
     </row>
     <row r="425" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A425" s="23"/>
-      <c r="B425" s="22"/>
+      <c r="B425" s="24"/>
       <c r="C425" s="6"/>
       <c r="D425" s="14"/>
       <c r="E425" s="6"/>
@@ -9417,7 +9423,7 @@
     </row>
     <row r="426" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A426" s="23"/>
-      <c r="B426" s="22"/>
+      <c r="B426" s="24"/>
       <c r="C426" s="6" t="str" cm="1">
         <f t="array" ref="C426:D426">E413:F413</f>
         <v>Driver - Hasan</v>
@@ -9436,7 +9442,7 @@
     </row>
     <row r="427" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A427" s="23"/>
-      <c r="B427" s="22"/>
+      <c r="B427" s="24"/>
       <c r="C427" s="8"/>
       <c r="D427" s="14"/>
       <c r="E427" s="6"/>
@@ -9450,7 +9456,7 @@
     </row>
     <row r="428" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A428" s="23"/>
-      <c r="B428" s="22"/>
+      <c r="B428" s="24"/>
       <c r="C428" s="8"/>
       <c r="D428" s="14"/>
       <c r="E428" s="6"/>
@@ -9464,7 +9470,7 @@
     </row>
     <row r="429" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A429" s="23"/>
-      <c r="B429" s="22"/>
+      <c r="B429" s="24"/>
       <c r="C429" s="8"/>
       <c r="D429" s="14"/>
       <c r="G429" s="6"/>
@@ -9476,7 +9482,7 @@
     </row>
     <row r="430" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A430" s="23"/>
-      <c r="B430" s="20" t="s">
+      <c r="B430" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C430" s="9"/>
@@ -9511,7 +9517,7 @@
     </row>
     <row r="431" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A431" s="23"/>
-      <c r="B431" s="20"/>
+      <c r="B431" s="21"/>
       <c r="C431" s="9"/>
       <c r="D431" s="15"/>
       <c r="E431" s="3" t="str">
@@ -9529,7 +9535,7 @@
     </row>
     <row r="432" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A432" s="23"/>
-      <c r="B432" s="20"/>
+      <c r="B432" s="21"/>
       <c r="C432" s="9"/>
       <c r="D432" s="15"/>
       <c r="E432" s="3" t="str">
@@ -9547,7 +9553,7 @@
     </row>
     <row r="433" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A433" s="23"/>
-      <c r="B433" s="20"/>
+      <c r="B433" s="21"/>
       <c r="C433" s="9"/>
       <c r="D433" s="15"/>
       <c r="E433" s="3" t="str">
@@ -9567,7 +9573,7 @@
       <c r="A434" s="25">
         <v>46131</v>
       </c>
-      <c r="B434" s="21" t="s">
+      <c r="B434" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C434" s="3" t="s">
@@ -9603,7 +9609,7 @@
     </row>
     <row r="435" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A435" s="25"/>
-      <c r="B435" s="21"/>
+      <c r="B435" s="22"/>
       <c r="C435" s="3" t="s">
         <v>36</v>
       </c>
@@ -9625,7 +9631,7 @@
     </row>
     <row r="436" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A436" s="25"/>
-      <c r="B436" s="21"/>
+      <c r="B436" s="22"/>
       <c r="C436" s="6" t="s">
         <v>40</v>
       </c>
@@ -9647,7 +9653,7 @@
     </row>
     <row r="437" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A437" s="25"/>
-      <c r="B437" s="21"/>
+      <c r="B437" s="22"/>
       <c r="C437" s="3" t="s">
         <v>18</v>
       </c>
@@ -9669,7 +9675,7 @@
     </row>
     <row r="438" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A438" s="25"/>
-      <c r="B438" s="21"/>
+      <c r="B438" s="22"/>
       <c r="C438" s="3" t="s">
         <v>37</v>
       </c>
@@ -9683,9 +9689,12 @@
     </row>
     <row r="439" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A439" s="25"/>
-      <c r="B439" s="21"/>
-      <c r="C439" s="24" t="s">
+      <c r="B439" s="22"/>
+      <c r="C439" s="20" t="s">
         <v>66</v>
+      </c>
+      <c r="D439" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="E439" s="3"/>
       <c r="F439" s="17"/>
@@ -9696,7 +9705,7 @@
     </row>
     <row r="440" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A440" s="25"/>
-      <c r="B440" s="21"/>
+      <c r="B440" s="22"/>
       <c r="C440" s="5" t="s">
         <v>21</v>
       </c>
@@ -9712,7 +9721,7 @@
     </row>
     <row r="441" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A441" s="25"/>
-      <c r="B441" s="21"/>
+      <c r="B441" s="22"/>
       <c r="E441" s="3"/>
       <c r="F441" s="17"/>
       <c r="G441" s="3"/>
@@ -9724,7 +9733,7 @@
     </row>
     <row r="442" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A442" s="25"/>
-      <c r="B442" s="21"/>
+      <c r="B442" s="22"/>
       <c r="E442" s="3"/>
       <c r="F442" s="17"/>
       <c r="G442" s="3"/>
@@ -9736,7 +9745,7 @@
     </row>
     <row r="443" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A443" s="25"/>
-      <c r="B443" s="21"/>
+      <c r="B443" s="22"/>
       <c r="C443" s="5"/>
       <c r="D443" s="13"/>
       <c r="E443" s="3"/>
@@ -9750,7 +9759,7 @@
     </row>
     <row r="444" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A444" s="25"/>
-      <c r="B444" s="22" t="s">
+      <c r="B444" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C444" s="6" t="s">
@@ -9786,7 +9795,7 @@
     </row>
     <row r="445" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A445" s="25"/>
-      <c r="B445" s="22"/>
+      <c r="B445" s="24"/>
       <c r="C445" s="3" t="s">
         <v>14</v>
       </c>
@@ -9808,7 +9817,7 @@
     </row>
     <row r="446" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A446" s="25"/>
-      <c r="B446" s="22"/>
+      <c r="B446" s="24"/>
       <c r="C446" s="6" t="s">
         <v>41</v>
       </c>
@@ -9830,7 +9839,7 @@
     </row>
     <row r="447" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A447" s="25"/>
-      <c r="B447" s="22"/>
+      <c r="B447" s="24"/>
       <c r="C447" s="6" t="s">
         <v>13</v>
       </c>
@@ -9852,7 +9861,7 @@
     </row>
     <row r="448" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A448" s="25"/>
-      <c r="B448" s="22"/>
+      <c r="B448" s="24"/>
       <c r="C448" s="6" t="s">
         <v>42</v>
       </c>
@@ -9870,13 +9879,13 @@
     </row>
     <row r="449" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A449" s="25"/>
-      <c r="B449" s="22"/>
+      <c r="B449" s="24"/>
       <c r="C449" s="8" t="str">
-        <f t="shared" ref="C449:D449" si="71">E437</f>
+        <f t="shared" ref="C449:D449" si="70">E437</f>
         <v>Driver - Shetu</v>
       </c>
       <c r="D449" s="18" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>01719034964</v>
       </c>
       <c r="E449" s="6"/>
@@ -9890,7 +9899,7 @@
     </row>
     <row r="450" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A450" s="25"/>
-      <c r="B450" s="22"/>
+      <c r="B450" s="24"/>
       <c r="E450" s="6"/>
       <c r="F450" s="18"/>
       <c r="G450" s="6"/>
@@ -9902,7 +9911,7 @@
     </row>
     <row r="451" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A451" s="25"/>
-      <c r="B451" s="22"/>
+      <c r="B451" s="24"/>
       <c r="C451" s="8"/>
       <c r="D451" s="14"/>
       <c r="E451" s="6"/>
@@ -9916,7 +9925,7 @@
     </row>
     <row r="452" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A452" s="25"/>
-      <c r="B452" s="22"/>
+      <c r="B452" s="24"/>
       <c r="C452" s="8"/>
       <c r="D452" s="14"/>
       <c r="E452" s="6"/>
@@ -9930,7 +9939,7 @@
     </row>
     <row r="453" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A453" s="25"/>
-      <c r="B453" s="22"/>
+      <c r="B453" s="24"/>
       <c r="C453" s="8"/>
       <c r="D453" s="14"/>
       <c r="G453" s="6"/>
@@ -9942,7 +9951,7 @@
     </row>
     <row r="454" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A454" s="25"/>
-      <c r="B454" s="20" t="s">
+      <c r="B454" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C454" s="9"/>
@@ -9974,7 +9983,7 @@
     </row>
     <row r="455" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A455" s="25"/>
-      <c r="B455" s="20"/>
+      <c r="B455" s="21"/>
       <c r="C455" s="9"/>
       <c r="D455" s="15"/>
       <c r="E455" s="3" t="s">
@@ -9992,7 +10001,7 @@
     </row>
     <row r="456" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A456" s="25"/>
-      <c r="B456" s="20"/>
+      <c r="B456" s="21"/>
       <c r="C456" s="9"/>
       <c r="D456" s="15"/>
       <c r="E456" s="3" t="s">
@@ -10010,7 +10019,7 @@
     </row>
     <row r="457" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A457" s="25"/>
-      <c r="B457" s="20"/>
+      <c r="B457" s="21"/>
       <c r="C457" s="9"/>
       <c r="D457" s="15"/>
       <c r="E457" s="5" t="s">
@@ -10030,67 +10039,67 @@
       <c r="A458" s="23">
         <v>46132</v>
       </c>
-      <c r="B458" s="21" t="s">
+      <c r="B458" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C458" s="3" t="str">
-        <f t="shared" ref="C458:D458" si="72">C444</f>
+        <f t="shared" ref="C458:D458" si="71">C444</f>
         <v>Monirul Islam  (LM)</v>
       </c>
       <c r="D458" s="13" t="str">
+        <f t="shared" si="71"/>
+        <v>01703409900</v>
+      </c>
+      <c r="E458" s="11" t="str">
+        <f t="shared" ref="E458:L458" si="72">E434</f>
+        <v>Rakib (LM)</v>
+      </c>
+      <c r="F458" s="19" t="str">
         <f t="shared" si="72"/>
-        <v>01703409900</v>
-      </c>
-      <c r="E458" s="11" t="str">
-        <f t="shared" ref="E458:L458" si="73">E434</f>
-        <v>Rakib (LM)</v>
-      </c>
-      <c r="F458" s="19" t="str">
-        <f t="shared" si="73"/>
         <v>01767032267</v>
       </c>
       <c r="G458" s="3" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>Shawon Dass</v>
       </c>
       <c r="H458" s="19" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="I458" s="3" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>Salim Reza</v>
       </c>
       <c r="J458" s="19" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K458" s="6" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>Inul Haque</v>
       </c>
       <c r="L458" s="19" t="str">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>02588855910</v>
       </c>
     </row>
     <row r="459" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A459" s="23"/>
-      <c r="B459" s="21"/>
+      <c r="B459" s="22"/>
       <c r="C459" s="3" t="str">
-        <f t="shared" ref="C459:D459" si="74">C445</f>
+        <f t="shared" ref="C459:D459" si="73">C445</f>
         <v>Abdus Sattar (LM)</v>
       </c>
       <c r="D459" s="13" t="str">
+        <f t="shared" si="73"/>
+        <v>01718676281</v>
+      </c>
+      <c r="E459" s="11" t="str">
+        <f t="shared" ref="E459:F459" si="74">E435</f>
+        <v>Nabi (LH)</v>
+      </c>
+      <c r="F459" s="19" t="str">
         <f t="shared" si="74"/>
-        <v>01718676281</v>
-      </c>
-      <c r="E459" s="11" t="str">
-        <f t="shared" ref="E459:F459" si="75">E435</f>
-        <v>Nabi (LH)</v>
-      </c>
-      <c r="F459" s="19" t="str">
-        <f t="shared" si="75"/>
         <v>01736352528</v>
       </c>
       <c r="G459" s="3"/>
@@ -10102,21 +10111,21 @@
     </row>
     <row r="460" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A460" s="23"/>
-      <c r="B460" s="21"/>
+      <c r="B460" s="22"/>
       <c r="C460" s="3" t="str">
-        <f t="shared" ref="C460:D460" si="76">C446</f>
+        <f t="shared" ref="C460:D460" si="75">C446</f>
         <v>Sazzad  (LM)</v>
       </c>
       <c r="D460" s="13" t="str">
+        <f t="shared" si="75"/>
+        <v>01719106824</v>
+      </c>
+      <c r="E460" s="11" t="str">
+        <f t="shared" ref="E460:F460" si="76">E436</f>
+        <v>Anowar (LEM)</v>
+      </c>
+      <c r="F460" s="19" t="str">
         <f t="shared" si="76"/>
-        <v>01719106824</v>
-      </c>
-      <c r="E460" s="11" t="str">
-        <f t="shared" ref="E460:F460" si="77">E436</f>
-        <v>Anowar (LEM)</v>
-      </c>
-      <c r="F460" s="19" t="str">
-        <f t="shared" si="77"/>
         <v>01712439152</v>
       </c>
       <c r="G460" s="3"/>
@@ -10128,21 +10137,21 @@
     </row>
     <row r="461" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A461" s="23"/>
-      <c r="B461" s="21"/>
+      <c r="B461" s="22"/>
       <c r="C461" s="3" t="str">
-        <f t="shared" ref="C461:D461" si="78">C447</f>
+        <f t="shared" ref="C461:D461" si="77">C447</f>
         <v>Jonny (LH)</v>
       </c>
       <c r="D461" s="13" t="str">
+        <f t="shared" si="77"/>
+        <v>01712441588</v>
+      </c>
+      <c r="E461" s="11" t="str">
+        <f t="shared" ref="E461:F461" si="78">E437</f>
+        <v>Driver - Shetu</v>
+      </c>
+      <c r="F461" s="19" t="str">
         <f t="shared" si="78"/>
-        <v>01712441588</v>
-      </c>
-      <c r="E461" s="11" t="str">
-        <f t="shared" ref="E461:F461" si="79">E437</f>
-        <v>Driver - Shetu</v>
-      </c>
-      <c r="F461" s="19" t="str">
-        <f t="shared" si="79"/>
         <v>01719034964</v>
       </c>
       <c r="G461" s="3"/>
@@ -10154,13 +10163,13 @@
     </row>
     <row r="462" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A462" s="23"/>
-      <c r="B462" s="21"/>
+      <c r="B462" s="22"/>
       <c r="C462" s="3" t="str">
-        <f t="shared" ref="C462:D462" si="80">C448</f>
+        <f t="shared" ref="C462:D462" si="79">C448</f>
         <v>Nazmul (LEM)</v>
       </c>
       <c r="D462" s="13" t="str">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>01914595295</v>
       </c>
       <c r="G462" s="3"/>
@@ -10170,14 +10179,13 @@
     </row>
     <row r="463" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A463" s="23"/>
-      <c r="B463" s="21"/>
-      <c r="C463" s="3" t="str">
-        <f t="shared" ref="C463:D463" si="81">C449</f>
-        <v>Driver - Shetu</v>
+      <c r="B463" s="22"/>
+      <c r="C463" s="3" t="str" cm="1">
+        <f t="array" ref="C463:D463">E457:F457</f>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D463" s="13" t="str">
-        <f t="shared" si="81"/>
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E463" s="3"/>
       <c r="F463" s="17"/>
@@ -10188,7 +10196,7 @@
     </row>
     <row r="464" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A464" s="23"/>
-      <c r="B464" s="21"/>
+      <c r="B464" s="22"/>
       <c r="C464" s="5"/>
       <c r="D464" s="17"/>
       <c r="E464" s="3"/>
@@ -10200,7 +10208,7 @@
     </row>
     <row r="465" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A465" s="23"/>
-      <c r="B465" s="21"/>
+      <c r="B465" s="22"/>
       <c r="E465" s="3"/>
       <c r="F465" s="17"/>
       <c r="G465" s="3"/>
@@ -10212,7 +10220,7 @@
     </row>
     <row r="466" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A466" s="23"/>
-      <c r="B466" s="21"/>
+      <c r="B466" s="22"/>
       <c r="E466" s="3"/>
       <c r="F466" s="17"/>
       <c r="G466" s="3"/>
@@ -10224,7 +10232,7 @@
     </row>
     <row r="467" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A467" s="23"/>
-      <c r="B467" s="21"/>
+      <c r="B467" s="22"/>
       <c r="C467" s="5"/>
       <c r="D467" s="13"/>
       <c r="E467" s="3"/>
@@ -10238,67 +10246,67 @@
     </row>
     <row r="468" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A468" s="23"/>
-      <c r="B468" s="22" t="s">
+      <c r="B468" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C468" s="6" t="str">
-        <f t="shared" ref="C468:D468" si="82">C434</f>
+        <f t="shared" ref="C468:D468" si="80">C434</f>
         <v>Mostafijur (LM)</v>
       </c>
       <c r="D468" s="14" t="str">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>01758212103</v>
       </c>
       <c r="E468" s="3" t="str">
-        <f t="shared" ref="E468:K468" si="83">E444</f>
+        <f t="shared" ref="E468:K468" si="81">E444</f>
         <v>Maruf Hossain (LM)</v>
       </c>
       <c r="F468" s="13" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>01943368198</v>
       </c>
       <c r="G468" s="6" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>Alauddin</v>
       </c>
       <c r="H468" s="19" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="I468" s="6" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>Moin Uddin</v>
       </c>
       <c r="J468" s="19" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0</v>
       </c>
       <c r="K468" s="11" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>Masud Rana</v>
       </c>
       <c r="L468" s="19" t="str">
-        <f t="shared" ref="L468" si="84">L478</f>
+        <f t="shared" ref="L468" si="82">L478</f>
         <v>02588855910</v>
       </c>
     </row>
     <row r="469" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A469" s="23"/>
-      <c r="B469" s="22"/>
+      <c r="B469" s="24"/>
       <c r="C469" s="6" t="str">
-        <f t="shared" ref="C469:D469" si="85">C435</f>
+        <f t="shared" ref="C469:D469" si="83">C435</f>
         <v>Monzur Kader (LM)</v>
       </c>
       <c r="D469" s="14" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>01705614054</v>
       </c>
       <c r="E469" s="3" t="str">
-        <f t="shared" ref="E469:F469" si="86">E445</f>
+        <f t="shared" ref="E469:F469" si="84">E445</f>
         <v>Sahjahan (LEM)</v>
       </c>
       <c r="F469" s="13" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>01724267460</v>
       </c>
       <c r="G469" s="6"/>
@@ -10310,21 +10318,21 @@
     </row>
     <row r="470" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A470" s="23"/>
-      <c r="B470" s="22"/>
+      <c r="B470" s="24"/>
       <c r="C470" s="6" t="str">
-        <f t="shared" ref="C470:D470" si="87">C436</f>
+        <f t="shared" ref="C470:D470" si="85">C436</f>
         <v>Mosaddek  (LM)</v>
       </c>
       <c r="D470" s="14" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="85"/>
         <v>01674272353</v>
       </c>
       <c r="E470" s="3" t="str">
-        <f t="shared" ref="E470:F470" si="88">E446</f>
+        <f t="shared" ref="E470:F470" si="86">E446</f>
         <v>Fuad (LH)</v>
       </c>
       <c r="F470" s="13" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>01718279112</v>
       </c>
       <c r="G470" s="6"/>
@@ -10336,21 +10344,21 @@
     </row>
     <row r="471" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A471" s="23"/>
-      <c r="B471" s="22"/>
+      <c r="B471" s="24"/>
       <c r="C471" s="6" t="str">
-        <f t="shared" ref="C471:D471" si="89">C437</f>
+        <f t="shared" ref="C471:D471" si="87">C437</f>
         <v>Abdus Salam (LM)</v>
       </c>
       <c r="D471" s="14" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="87"/>
         <v>01756101919</v>
       </c>
       <c r="E471" s="3" t="str">
-        <f t="shared" ref="E471:F471" si="90">E447</f>
+        <f t="shared" ref="E471:F471" si="88">E447</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="F471" s="13" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="88"/>
         <v>01748127818</v>
       </c>
       <c r="G471" s="6"/>
@@ -10362,13 +10370,13 @@
     </row>
     <row r="472" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A472" s="23"/>
-      <c r="B472" s="22"/>
+      <c r="B472" s="24"/>
       <c r="C472" s="6" t="str">
-        <f t="shared" ref="C472:D472" si="91">C438</f>
+        <f t="shared" ref="C472:D472" si="89">C438</f>
         <v>Salim Reza-2 (LH)</v>
       </c>
       <c r="D472" s="14" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="89"/>
         <v>01719531782</v>
       </c>
       <c r="E472" s="6"/>
@@ -10382,14 +10390,14 @@
     </row>
     <row r="473" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A473" s="23"/>
-      <c r="B473" s="22"/>
+      <c r="B473" s="24"/>
       <c r="C473" s="6" t="str">
-        <f t="shared" ref="C473:D473" si="92">C439</f>
+        <f t="shared" ref="C473:D473" si="90">C439</f>
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D473" s="14">
-        <f t="shared" si="92"/>
-        <v>0</v>
+      <c r="D473" s="14" t="str">
+        <f t="shared" si="90"/>
+        <v>01723504940</v>
       </c>
       <c r="E473" s="6"/>
       <c r="F473" s="18"/>
@@ -10402,14 +10410,13 @@
     </row>
     <row r="474" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A474" s="23"/>
-      <c r="B474" s="22"/>
-      <c r="C474" s="6" t="str">
-        <f t="shared" ref="C474:D474" si="93">C440</f>
-        <v>Driver - Hasan</v>
+      <c r="B474" s="24"/>
+      <c r="C474" s="6" t="str" cm="1">
+        <f t="array" ref="C474:D474">E461:F461</f>
+        <v>Driver - Shetu</v>
       </c>
       <c r="D474" s="14" t="str">
-        <f t="shared" si="93"/>
-        <v>01730824934</v>
+        <v>01719034964</v>
       </c>
       <c r="E474" s="6"/>
       <c r="F474" s="18"/>
@@ -10422,7 +10429,7 @@
     </row>
     <row r="475" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A475" s="23"/>
-      <c r="B475" s="22"/>
+      <c r="B475" s="24"/>
       <c r="C475" s="8"/>
       <c r="D475" s="14"/>
       <c r="E475" s="6"/>
@@ -10436,7 +10443,7 @@
     </row>
     <row r="476" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A476" s="23"/>
-      <c r="B476" s="22"/>
+      <c r="B476" s="24"/>
       <c r="C476" s="8"/>
       <c r="D476" s="14"/>
       <c r="E476" s="6"/>
@@ -10450,7 +10457,7 @@
     </row>
     <row r="477" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A477" s="23"/>
-      <c r="B477" s="22"/>
+      <c r="B477" s="24"/>
       <c r="C477" s="8"/>
       <c r="D477" s="14"/>
       <c r="G477" s="6"/>
@@ -10462,55 +10469,55 @@
     </row>
     <row r="478" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A478" s="23"/>
-      <c r="B478" s="20" t="s">
+      <c r="B478" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C478" s="9"/>
       <c r="D478" s="15"/>
       <c r="E478" s="3" t="str">
-        <f t="shared" ref="E478:L478" si="94">E454</f>
+        <f t="shared" ref="E478:L478" si="91">E454</f>
         <v>Sumon (LM)</v>
       </c>
       <c r="F478" s="17" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="91"/>
         <v>01726258394</v>
       </c>
       <c r="G478" s="11" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="91"/>
         <v>Abdur Rafique</v>
       </c>
       <c r="H478" s="19" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="I478" s="11" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="91"/>
         <v>Abul Kalam Azad</v>
       </c>
       <c r="J478" s="19" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="91"/>
         <v>0</v>
       </c>
       <c r="K478" s="3" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="91"/>
         <v>Monzur Ahmed</v>
       </c>
       <c r="L478" s="19" t="str">
-        <f t="shared" si="94"/>
+        <f t="shared" si="91"/>
         <v>02588855910</v>
       </c>
     </row>
     <row r="479" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A479" s="23"/>
-      <c r="B479" s="20"/>
+      <c r="B479" s="21"/>
       <c r="C479" s="9"/>
       <c r="D479" s="15"/>
       <c r="E479" s="3" t="str">
-        <f t="shared" ref="E479:F479" si="95">E455</f>
+        <f t="shared" ref="E479:F479" si="92">E455</f>
         <v>Arafat (LH)</v>
       </c>
       <c r="F479" s="17" t="str">
-        <f t="shared" si="95"/>
+        <f t="shared" si="92"/>
         <v>01755149115</v>
       </c>
       <c r="G479" s="11"/>
@@ -10522,15 +10529,15 @@
     </row>
     <row r="480" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A480" s="23"/>
-      <c r="B480" s="20"/>
+      <c r="B480" s="21"/>
       <c r="C480" s="9"/>
       <c r="D480" s="15"/>
       <c r="E480" s="3" t="str">
-        <f t="shared" ref="E480:F480" si="96">E456</f>
+        <f t="shared" ref="E480:F480" si="93">E456</f>
         <v>Mamun (LH)</v>
       </c>
       <c r="F480" s="17" t="str">
-        <f t="shared" si="96"/>
+        <f t="shared" si="93"/>
         <v>01718106022</v>
       </c>
       <c r="G480" s="11"/>
@@ -10542,15 +10549,15 @@
     </row>
     <row r="481" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A481" s="23"/>
-      <c r="B481" s="20"/>
+      <c r="B481" s="21"/>
       <c r="C481" s="9"/>
       <c r="D481" s="15"/>
       <c r="E481" s="3" t="str">
-        <f t="shared" ref="E481:F481" si="97">E457</f>
+        <f t="shared" ref="E481:F481" si="94">E457</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="F481" s="17" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="94"/>
         <v>01730824934</v>
       </c>
       <c r="G481" s="11"/>
@@ -10564,7 +10571,7 @@
       <c r="A482" s="23">
         <v>46133</v>
       </c>
-      <c r="B482" s="21" t="s">
+      <c r="B482" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C482" s="3" t="str" cm="1">
@@ -10574,12 +10581,12 @@
       <c r="D482" s="13" t="str">
         <v>01703409900</v>
       </c>
-      <c r="E482" s="11" t="str" cm="1">
-        <f t="array" ref="E482:F485">E478:F481</f>
-        <v>Sumon (LM)</v>
-      </c>
-      <c r="F482" s="19" t="str">
-        <v>01726258394</v>
+      <c r="E482" s="3" t="str" cm="1">
+        <f t="array" ref="E482:F485">E468:F471</f>
+        <v>Maruf Hossain (LM)</v>
+      </c>
+      <c r="F482" s="17" t="str">
+        <v>01943368198</v>
       </c>
       <c r="G482" s="3" t="str" cm="1">
         <f t="array" ref="G482:H482">G468:H468</f>
@@ -10605,18 +10612,18 @@
     </row>
     <row r="483" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A483" s="23"/>
-      <c r="B483" s="21"/>
+      <c r="B483" s="22"/>
       <c r="C483" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
       <c r="D483" s="13" t="str">
         <v>01718676281</v>
       </c>
-      <c r="E483" s="11" t="str">
-        <v>Arafat (LH)</v>
-      </c>
-      <c r="F483" s="19" t="str">
-        <v>01755149115</v>
+      <c r="E483" s="3" t="str">
+        <v>Sahjahan (LEM)</v>
+      </c>
+      <c r="F483" s="17" t="str">
+        <v>01724267460</v>
       </c>
       <c r="G483" s="3"/>
       <c r="H483" s="4"/>
@@ -10627,18 +10634,18 @@
     </row>
     <row r="484" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A484" s="23"/>
-      <c r="B484" s="21"/>
+      <c r="B484" s="22"/>
       <c r="C484" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
       <c r="D484" s="13" t="str">
         <v>01719106824</v>
       </c>
-      <c r="E484" s="11" t="str">
-        <v>Mamun (LH)</v>
-      </c>
-      <c r="F484" s="19" t="str">
-        <v>01718106022</v>
+      <c r="E484" s="3" t="str">
+        <v>Fuad (LH)</v>
+      </c>
+      <c r="F484" s="17" t="str">
+        <v>01718279112</v>
       </c>
       <c r="G484" s="3"/>
       <c r="H484" s="4"/>
@@ -10649,18 +10656,18 @@
     </row>
     <row r="485" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A485" s="23"/>
-      <c r="B485" s="21"/>
+      <c r="B485" s="22"/>
       <c r="C485" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
       <c r="D485" s="13" t="str">
         <v>01712441588</v>
       </c>
-      <c r="E485" s="11" t="str">
-        <v>Driver - Hasan</v>
-      </c>
-      <c r="F485" s="19" t="str">
-        <v>01730824934</v>
+      <c r="E485" s="3" t="str">
+        <v>Driver - Noyon</v>
+      </c>
+      <c r="F485" s="17" t="str">
+        <v>01748127818</v>
       </c>
       <c r="G485" s="3"/>
       <c r="H485" s="4"/>
@@ -10671,7 +10678,7 @@
     </row>
     <row r="486" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A486" s="23"/>
-      <c r="B486" s="21"/>
+      <c r="B486" s="22"/>
       <c r="C486" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -10685,7 +10692,7 @@
     </row>
     <row r="487" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A487" s="23"/>
-      <c r="B487" s="21"/>
+      <c r="B487" s="22"/>
       <c r="C487" s="3"/>
       <c r="D487" s="13"/>
       <c r="E487" s="3"/>
@@ -10697,13 +10704,13 @@
     </row>
     <row r="488" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A488" s="23"/>
-      <c r="B488" s="21"/>
+      <c r="B488" s="22"/>
       <c r="C488" s="5" t="str">
-        <f t="shared" ref="C488:D488" si="98">E481</f>
+        <f t="shared" ref="C488:D488" si="95">E481</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="D488" s="17" t="str">
-        <f t="shared" si="98"/>
+        <f t="shared" si="95"/>
         <v>01730824934</v>
       </c>
       <c r="E488" s="3"/>
@@ -10715,7 +10722,7 @@
     </row>
     <row r="489" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A489" s="23"/>
-      <c r="B489" s="21"/>
+      <c r="B489" s="22"/>
       <c r="E489" s="3"/>
       <c r="F489" s="17"/>
       <c r="G489" s="3"/>
@@ -10727,7 +10734,7 @@
     </row>
     <row r="490" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A490" s="23"/>
-      <c r="B490" s="21"/>
+      <c r="B490" s="22"/>
       <c r="E490" s="3"/>
       <c r="F490" s="17"/>
       <c r="G490" s="3"/>
@@ -10739,7 +10746,7 @@
     </row>
     <row r="491" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A491" s="23"/>
-      <c r="B491" s="21"/>
+      <c r="B491" s="22"/>
       <c r="C491" s="5"/>
       <c r="D491" s="13"/>
       <c r="E491" s="3"/>
@@ -10753,7 +10760,7 @@
     </row>
     <row r="492" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A492" s="23"/>
-      <c r="B492" s="22" t="s">
+      <c r="B492" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C492" s="6" t="str" cm="1">
@@ -10763,12 +10770,12 @@
       <c r="D492" s="14" t="str">
         <v>01758212103</v>
       </c>
-      <c r="E492" s="3" t="str" cm="1">
-        <f t="array" ref="E492:F495">E458:F461</f>
-        <v>Rakib (LM)</v>
-      </c>
-      <c r="F492" s="13" t="str">
-        <v>01767032267</v>
+      <c r="E492" s="11" t="str" cm="1">
+        <f t="array" ref="E492:F495">E478:F481</f>
+        <v>Sumon (LM)</v>
+      </c>
+      <c r="F492" s="19" t="str">
+        <v>01726258394</v>
       </c>
       <c r="G492" s="6" t="str" cm="1">
         <f t="array" ref="G492:H492">G478:H478</f>
@@ -10794,18 +10801,18 @@
     </row>
     <row r="493" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A493" s="23"/>
-      <c r="B493" s="22"/>
+      <c r="B493" s="24"/>
       <c r="C493" s="6" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
       <c r="D493" s="14" t="str">
         <v>01705614054</v>
       </c>
-      <c r="E493" s="3" t="str">
-        <v>Nabi (LH)</v>
-      </c>
-      <c r="F493" s="13" t="str">
-        <v>01736352528</v>
+      <c r="E493" s="11" t="str">
+        <v>Arafat (LH)</v>
+      </c>
+      <c r="F493" s="19" t="str">
+        <v>01755149115</v>
       </c>
       <c r="G493" s="6"/>
       <c r="H493" s="7"/>
@@ -10820,18 +10827,18 @@
     </row>
     <row r="494" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A494" s="23"/>
-      <c r="B494" s="22"/>
+      <c r="B494" s="24"/>
       <c r="C494" s="6" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
       <c r="D494" s="14" t="str">
         <v>01674272353</v>
       </c>
-      <c r="E494" s="3" t="str">
-        <v>Anowar (LEM)</v>
-      </c>
-      <c r="F494" s="13" t="str">
-        <v>01712439152</v>
+      <c r="E494" s="11" t="str">
+        <v>Mamun (LH)</v>
+      </c>
+      <c r="F494" s="19" t="str">
+        <v>01718106022</v>
       </c>
       <c r="G494" s="6"/>
       <c r="H494" s="7"/>
@@ -10842,18 +10849,18 @@
     </row>
     <row r="495" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A495" s="23"/>
-      <c r="B495" s="22"/>
+      <c r="B495" s="24"/>
       <c r="C495" s="6" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
       <c r="D495" s="14" t="str">
         <v>01756101919</v>
       </c>
-      <c r="E495" s="3" t="str">
-        <v>Driver - Shetu</v>
-      </c>
-      <c r="F495" s="13" t="str">
-        <v>01719034964</v>
+      <c r="E495" s="11" t="str">
+        <v>Driver - Hasan</v>
+      </c>
+      <c r="F495" s="19" t="str">
+        <v>01730824934</v>
       </c>
       <c r="G495" s="6"/>
       <c r="H495" s="7"/>
@@ -10864,7 +10871,7 @@
     </row>
     <row r="496" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A496" s="23"/>
-      <c r="B496" s="22"/>
+      <c r="B496" s="24"/>
       <c r="C496" s="6" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -10882,12 +10889,12 @@
     </row>
     <row r="497" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A497" s="23"/>
-      <c r="B497" s="22"/>
+      <c r="B497" s="24"/>
       <c r="C497" s="6" t="str">
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D497" s="14">
-        <v>0</v>
+      <c r="D497" s="14" t="str">
+        <v>01723504940</v>
       </c>
       <c r="E497" s="6"/>
       <c r="F497" s="18"/>
@@ -10900,9 +10907,9 @@
     </row>
     <row r="498" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A498" s="23"/>
-      <c r="B498" s="22"/>
+      <c r="B498" s="24"/>
       <c r="C498" s="6" t="str" cm="1">
-        <f t="array" ref="C498:D498">E485:F485</f>
+        <f t="array" ref="C498:D498">E495:F495</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="D498" s="14" t="str">
@@ -10919,7 +10926,7 @@
     </row>
     <row r="499" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A499" s="23"/>
-      <c r="B499" s="22"/>
+      <c r="B499" s="24"/>
       <c r="C499" s="8"/>
       <c r="D499" s="14"/>
       <c r="E499" s="6"/>
@@ -10933,7 +10940,7 @@
     </row>
     <row r="500" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A500" s="23"/>
-      <c r="B500" s="22"/>
+      <c r="B500" s="24"/>
       <c r="C500" s="8"/>
       <c r="D500" s="14"/>
       <c r="E500" s="6"/>
@@ -10947,7 +10954,7 @@
     </row>
     <row r="501" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A501" s="23"/>
-      <c r="B501" s="22"/>
+      <c r="B501" s="24"/>
       <c r="C501" s="8"/>
       <c r="D501" s="14"/>
       <c r="G501" s="6"/>
@@ -10959,17 +10966,17 @@
     </row>
     <row r="502" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A502" s="23"/>
-      <c r="B502" s="20" t="s">
+      <c r="B502" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C502" s="9"/>
       <c r="D502" s="15"/>
       <c r="E502" s="3" t="str" cm="1">
-        <f t="array" ref="E502:F505">E468:F471</f>
-        <v>Maruf Hossain (LM)</v>
-      </c>
-      <c r="F502" s="17" t="str">
-        <v>01943368198</v>
+        <f t="array" ref="E502:F505">E458:F461</f>
+        <v>Rakib (LM)</v>
+      </c>
+      <c r="F502" s="13" t="str">
+        <v>01767032267</v>
       </c>
       <c r="G502" s="11" t="str" cm="1">
         <f t="array" ref="G502:H502">G458:H458</f>
@@ -10995,14 +11002,14 @@
     </row>
     <row r="503" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A503" s="23"/>
-      <c r="B503" s="20"/>
+      <c r="B503" s="21"/>
       <c r="C503" s="9"/>
       <c r="D503" s="15"/>
       <c r="E503" s="3" t="str">
-        <v>Sahjahan (LEM)</v>
-      </c>
-      <c r="F503" s="17" t="str">
-        <v>01724267460</v>
+        <v>Nabi (LH)</v>
+      </c>
+      <c r="F503" s="13" t="str">
+        <v>01736352528</v>
       </c>
       <c r="G503" s="11"/>
       <c r="H503" s="10"/>
@@ -11013,14 +11020,14 @@
     </row>
     <row r="504" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A504" s="23"/>
-      <c r="B504" s="20"/>
+      <c r="B504" s="21"/>
       <c r="C504" s="9"/>
       <c r="D504" s="15"/>
       <c r="E504" s="3" t="str">
-        <v>Fuad (LH)</v>
-      </c>
-      <c r="F504" s="17" t="str">
-        <v>01718279112</v>
+        <v>Anowar (LEM)</v>
+      </c>
+      <c r="F504" s="13" t="str">
+        <v>01712439152</v>
       </c>
       <c r="G504" s="11"/>
       <c r="H504" s="10"/>
@@ -11031,14 +11038,14 @@
     </row>
     <row r="505" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A505" s="23"/>
-      <c r="B505" s="20"/>
+      <c r="B505" s="21"/>
       <c r="C505" s="9"/>
       <c r="D505" s="15"/>
       <c r="E505" s="3" t="str">
-        <v>Driver - Noyon</v>
-      </c>
-      <c r="F505" s="17" t="str">
-        <v>01748127818</v>
+        <v>Driver - Shetu</v>
+      </c>
+      <c r="F505" s="13" t="str">
+        <v>01719034964</v>
       </c>
       <c r="G505" s="11"/>
       <c r="H505" s="10"/>
@@ -11051,7 +11058,7 @@
       <c r="A506" s="23">
         <v>46134</v>
       </c>
-      <c r="B506" s="21" t="s">
+      <c r="B506" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C506" s="3" t="str" cm="1">
@@ -11062,7 +11069,7 @@
         <v>01703409900</v>
       </c>
       <c r="E506" s="11" t="str" cm="1">
-        <f t="array" ref="E506:F509">E502:F505</f>
+        <f t="array" ref="E506:F509">E482:F485</f>
         <v>Maruf Hossain (LM)</v>
       </c>
       <c r="F506" s="19" t="str">
@@ -11091,7 +11098,7 @@
     </row>
     <row r="507" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A507" s="23"/>
-      <c r="B507" s="21"/>
+      <c r="B507" s="22"/>
       <c r="C507" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -11113,7 +11120,7 @@
     </row>
     <row r="508" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A508" s="23"/>
-      <c r="B508" s="21"/>
+      <c r="B508" s="22"/>
       <c r="C508" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -11135,7 +11142,7 @@
     </row>
     <row r="509" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A509" s="23"/>
-      <c r="B509" s="21"/>
+      <c r="B509" s="22"/>
       <c r="C509" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -11157,7 +11164,7 @@
     </row>
     <row r="510" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A510" s="23"/>
-      <c r="B510" s="21"/>
+      <c r="B510" s="22"/>
       <c r="C510" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -11171,7 +11178,7 @@
     </row>
     <row r="511" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A511" s="23"/>
-      <c r="B511" s="21"/>
+      <c r="B511" s="22"/>
       <c r="C511" s="3"/>
       <c r="D511" s="13"/>
       <c r="E511" s="3"/>
@@ -11183,13 +11190,13 @@
     </row>
     <row r="512" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A512" s="23"/>
-      <c r="B512" s="21"/>
+      <c r="B512" s="22"/>
       <c r="C512" s="5" t="str">
-        <f t="shared" ref="C512:D512" si="99">E505</f>
+        <f t="shared" ref="C512:D512" si="96">E485</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="D512" s="17" t="str">
-        <f t="shared" si="99"/>
+        <f t="shared" si="96"/>
         <v>01748127818</v>
       </c>
       <c r="E512" s="3"/>
@@ -11201,7 +11208,7 @@
     </row>
     <row r="513" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A513" s="23"/>
-      <c r="B513" s="21"/>
+      <c r="B513" s="22"/>
       <c r="E513" s="3"/>
       <c r="F513" s="17"/>
       <c r="G513" s="3"/>
@@ -11213,7 +11220,7 @@
     </row>
     <row r="514" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A514" s="23"/>
-      <c r="B514" s="21"/>
+      <c r="B514" s="22"/>
       <c r="E514" s="3"/>
       <c r="F514" s="17"/>
       <c r="G514" s="3"/>
@@ -11225,7 +11232,7 @@
     </row>
     <row r="515" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A515" s="23"/>
-      <c r="B515" s="21"/>
+      <c r="B515" s="22"/>
       <c r="C515" s="5"/>
       <c r="D515" s="13"/>
       <c r="E515" s="3"/>
@@ -11239,7 +11246,7 @@
     </row>
     <row r="516" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A516" s="23"/>
-      <c r="B516" s="22" t="s">
+      <c r="B516" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C516" s="6" t="str" cm="1">
@@ -11250,7 +11257,7 @@
         <v>01703409900</v>
       </c>
       <c r="E516" s="3" t="str" cm="1">
-        <f t="array" ref="E516:F519">E482:F485</f>
+        <f t="array" ref="E516:F519">E492:F495</f>
         <v>Sumon (LM)</v>
       </c>
       <c r="F516" s="13" t="str">
@@ -11279,7 +11286,7 @@
     </row>
     <row r="517" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A517" s="23"/>
-      <c r="B517" s="22"/>
+      <c r="B517" s="24"/>
       <c r="C517" s="6" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -11301,7 +11308,7 @@
     </row>
     <row r="518" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A518" s="23"/>
-      <c r="B518" s="22"/>
+      <c r="B518" s="24"/>
       <c r="C518" s="6" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -11323,7 +11330,7 @@
     </row>
     <row r="519" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A519" s="23"/>
-      <c r="B519" s="22"/>
+      <c r="B519" s="24"/>
       <c r="C519" s="6" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -11345,7 +11352,7 @@
     </row>
     <row r="520" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A520" s="23"/>
-      <c r="B520" s="22"/>
+      <c r="B520" s="24"/>
       <c r="C520" s="6" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -11363,12 +11370,12 @@
     </row>
     <row r="521" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A521" s="23"/>
-      <c r="B521" s="22"/>
+      <c r="B521" s="24"/>
       <c r="C521" s="6" t="str">
-        <v>Driver - Shetu</v>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D521" s="14" t="str">
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E521" s="6"/>
       <c r="F521" s="18"/>
@@ -11381,7 +11388,7 @@
     </row>
     <row r="522" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A522" s="23"/>
-      <c r="B522" s="22"/>
+      <c r="B522" s="24"/>
       <c r="C522" s="6" t="str" cm="1">
         <f t="array" ref="C522:D522">E509:F509</f>
         <v>Driver - Noyon</v>
@@ -11400,7 +11407,7 @@
     </row>
     <row r="523" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A523" s="23"/>
-      <c r="B523" s="22"/>
+      <c r="B523" s="24"/>
       <c r="C523" s="8"/>
       <c r="D523" s="14"/>
       <c r="E523" s="6"/>
@@ -11414,7 +11421,7 @@
     </row>
     <row r="524" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A524" s="23"/>
-      <c r="B524" s="22"/>
+      <c r="B524" s="24"/>
       <c r="C524" s="8"/>
       <c r="D524" s="14"/>
       <c r="E524" s="6"/>
@@ -11428,7 +11435,7 @@
     </row>
     <row r="525" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A525" s="23"/>
-      <c r="B525" s="22"/>
+      <c r="B525" s="24"/>
       <c r="C525" s="8"/>
       <c r="D525" s="14"/>
       <c r="G525" s="6"/>
@@ -11440,13 +11447,13 @@
     </row>
     <row r="526" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A526" s="23"/>
-      <c r="B526" s="20" t="s">
+      <c r="B526" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C526" s="9"/>
       <c r="D526" s="15"/>
       <c r="E526" s="3" t="str" cm="1">
-        <f t="array" ref="E526:F529">E492:F495</f>
+        <f t="array" ref="E526:F529">E502:F505</f>
         <v>Rakib (LM)</v>
       </c>
       <c r="F526" s="17" t="str">
@@ -11475,7 +11482,7 @@
     </row>
     <row r="527" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A527" s="23"/>
-      <c r="B527" s="20"/>
+      <c r="B527" s="21"/>
       <c r="C527" s="9"/>
       <c r="D527" s="15"/>
       <c r="E527" s="3" t="str">
@@ -11493,7 +11500,7 @@
     </row>
     <row r="528" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A528" s="23"/>
-      <c r="B528" s="20"/>
+      <c r="B528" s="21"/>
       <c r="C528" s="9"/>
       <c r="D528" s="15"/>
       <c r="E528" s="3" t="str">
@@ -11511,7 +11518,7 @@
     </row>
     <row r="529" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A529" s="23"/>
-      <c r="B529" s="20"/>
+      <c r="B529" s="21"/>
       <c r="C529" s="9"/>
       <c r="D529" s="15"/>
       <c r="E529" s="3" t="str">
@@ -11531,7 +11538,7 @@
       <c r="A530" s="23">
         <v>46135</v>
       </c>
-      <c r="B530" s="21" t="s">
+      <c r="B530" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C530" s="3" t="str" cm="1">
@@ -11572,7 +11579,7 @@
     </row>
     <row r="531" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A531" s="23"/>
-      <c r="B531" s="21"/>
+      <c r="B531" s="22"/>
       <c r="C531" s="3" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
@@ -11594,7 +11601,7 @@
     </row>
     <row r="532" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A532" s="23"/>
-      <c r="B532" s="21"/>
+      <c r="B532" s="22"/>
       <c r="C532" s="3" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
@@ -11616,7 +11623,7 @@
     </row>
     <row r="533" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A533" s="23"/>
-      <c r="B533" s="21"/>
+      <c r="B533" s="22"/>
       <c r="C533" s="3" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
@@ -11638,7 +11645,7 @@
     </row>
     <row r="534" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A534" s="23"/>
-      <c r="B534" s="21"/>
+      <c r="B534" s="22"/>
       <c r="C534" s="3" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -11652,12 +11659,12 @@
     </row>
     <row r="535" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A535" s="23"/>
-      <c r="B535" s="21"/>
+      <c r="B535" s="22"/>
       <c r="C535" s="3" t="str">
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D535" s="13">
-        <v>0</v>
+      <c r="D535" s="13" t="str">
+        <v>01723504940</v>
       </c>
       <c r="E535" s="3"/>
       <c r="F535" s="17"/>
@@ -11668,13 +11675,13 @@
     </row>
     <row r="536" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A536" s="23"/>
-      <c r="B536" s="21"/>
+      <c r="B536" s="22"/>
       <c r="C536" s="5" t="str">
-        <f t="shared" ref="C536:D536" si="100">E529</f>
+        <f t="shared" ref="C536:D536" si="97">E529</f>
         <v>Driver - Shetu</v>
       </c>
       <c r="D536" s="17" t="str">
-        <f t="shared" si="100"/>
+        <f t="shared" si="97"/>
         <v>01719034964</v>
       </c>
       <c r="E536" s="3"/>
@@ -11686,7 +11693,7 @@
     </row>
     <row r="537" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A537" s="23"/>
-      <c r="B537" s="21"/>
+      <c r="B537" s="22"/>
       <c r="E537" s="3"/>
       <c r="F537" s="17"/>
       <c r="G537" s="3"/>
@@ -11698,7 +11705,7 @@
     </row>
     <row r="538" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A538" s="23"/>
-      <c r="B538" s="21"/>
+      <c r="B538" s="22"/>
       <c r="E538" s="3"/>
       <c r="F538" s="17"/>
       <c r="G538" s="3"/>
@@ -11710,7 +11717,7 @@
     </row>
     <row r="539" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A539" s="23"/>
-      <c r="B539" s="21"/>
+      <c r="B539" s="22"/>
       <c r="C539" s="5"/>
       <c r="D539" s="13"/>
       <c r="E539" s="3"/>
@@ -11724,7 +11731,7 @@
     </row>
     <row r="540" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A540" s="23"/>
-      <c r="B540" s="22" t="s">
+      <c r="B540" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C540" s="6" t="str" cm="1">
@@ -11765,7 +11772,7 @@
     </row>
     <row r="541" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A541" s="23"/>
-      <c r="B541" s="22"/>
+      <c r="B541" s="24"/>
       <c r="C541" s="6" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -11787,7 +11794,7 @@
     </row>
     <row r="542" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A542" s="23"/>
-      <c r="B542" s="22"/>
+      <c r="B542" s="24"/>
       <c r="C542" s="6" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -11809,7 +11816,7 @@
     </row>
     <row r="543" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A543" s="23"/>
-      <c r="B543" s="22"/>
+      <c r="B543" s="24"/>
       <c r="C543" s="6" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -11831,7 +11838,7 @@
     </row>
     <row r="544" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A544" s="23"/>
-      <c r="B544" s="22"/>
+      <c r="B544" s="24"/>
       <c r="C544" s="6" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -11849,7 +11856,7 @@
     </row>
     <row r="545" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A545" s="23"/>
-      <c r="B545" s="22"/>
+      <c r="B545" s="24"/>
       <c r="C545" s="6"/>
       <c r="D545" s="14"/>
       <c r="E545" s="6"/>
@@ -11863,7 +11870,7 @@
     </row>
     <row r="546" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A546" s="23"/>
-      <c r="B546" s="22"/>
+      <c r="B546" s="24"/>
       <c r="C546" s="6" t="str" cm="1">
         <f t="array" ref="C546:D546">E533:F533</f>
         <v>Driver - Hasan</v>
@@ -11882,7 +11889,7 @@
     </row>
     <row r="547" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A547" s="23"/>
-      <c r="B547" s="22"/>
+      <c r="B547" s="24"/>
       <c r="C547" s="8"/>
       <c r="D547" s="14"/>
       <c r="E547" s="6"/>
@@ -11896,7 +11903,7 @@
     </row>
     <row r="548" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A548" s="23"/>
-      <c r="B548" s="22"/>
+      <c r="B548" s="24"/>
       <c r="C548" s="8"/>
       <c r="D548" s="14"/>
       <c r="E548" s="6"/>
@@ -11910,7 +11917,7 @@
     </row>
     <row r="549" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A549" s="23"/>
-      <c r="B549" s="22"/>
+      <c r="B549" s="24"/>
       <c r="C549" s="8"/>
       <c r="D549" s="14"/>
       <c r="G549" s="6"/>
@@ -11922,7 +11929,7 @@
     </row>
     <row r="550" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A550" s="23"/>
-      <c r="B550" s="20" t="s">
+      <c r="B550" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C550" s="9"/>
@@ -11958,7 +11965,7 @@
     </row>
     <row r="551" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A551" s="23"/>
-      <c r="B551" s="20"/>
+      <c r="B551" s="21"/>
       <c r="C551" s="9"/>
       <c r="D551" s="15"/>
       <c r="E551" s="3" t="str">
@@ -11976,7 +11983,7 @@
     </row>
     <row r="552" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A552" s="23"/>
-      <c r="B552" s="20"/>
+      <c r="B552" s="21"/>
       <c r="C552" s="9"/>
       <c r="D552" s="15"/>
       <c r="E552" s="3" t="str">
@@ -11994,7 +12001,7 @@
     </row>
     <row r="553" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A553" s="23"/>
-      <c r="B553" s="20"/>
+      <c r="B553" s="21"/>
       <c r="C553" s="9"/>
       <c r="D553" s="15"/>
       <c r="E553" s="3" t="str">
@@ -12014,7 +12021,7 @@
       <c r="A554" s="23">
         <v>46136</v>
       </c>
-      <c r="B554" s="21" t="s">
+      <c r="B554" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C554" s="3" t="str" cm="1">
@@ -12054,7 +12061,7 @@
     </row>
     <row r="555" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A555" s="23"/>
-      <c r="B555" s="21"/>
+      <c r="B555" s="22"/>
       <c r="C555" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -12076,7 +12083,7 @@
     </row>
     <row r="556" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A556" s="23"/>
-      <c r="B556" s="21"/>
+      <c r="B556" s="22"/>
       <c r="C556" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -12098,7 +12105,7 @@
     </row>
     <row r="557" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A557" s="23"/>
-      <c r="B557" s="21"/>
+      <c r="B557" s="22"/>
       <c r="C557" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -12120,7 +12127,7 @@
     </row>
     <row r="558" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A558" s="23"/>
-      <c r="B558" s="21"/>
+      <c r="B558" s="22"/>
       <c r="C558" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -12134,12 +12141,12 @@
     </row>
     <row r="559" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A559" s="23"/>
-      <c r="B559" s="21"/>
+      <c r="B559" s="22"/>
       <c r="C559" s="3" t="str">
-        <v>Driver - Shetu</v>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D559" s="13" t="str">
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E559" s="3"/>
       <c r="F559" s="17"/>
@@ -12150,13 +12157,13 @@
     </row>
     <row r="560" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A560" s="23"/>
-      <c r="B560" s="21"/>
+      <c r="B560" s="22"/>
       <c r="C560" s="5" t="str">
-        <f t="shared" ref="C560:D560" si="101">E553</f>
+        <f t="shared" ref="C560:D560" si="98">E553</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="D560" s="17" t="str">
-        <f t="shared" si="101"/>
+        <f t="shared" si="98"/>
         <v>01748127818</v>
       </c>
       <c r="E560" s="3"/>
@@ -12168,7 +12175,7 @@
     </row>
     <row r="561" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A561" s="23"/>
-      <c r="B561" s="21"/>
+      <c r="B561" s="22"/>
       <c r="E561" s="3"/>
       <c r="F561" s="17"/>
       <c r="G561" s="3"/>
@@ -12180,7 +12187,7 @@
     </row>
     <row r="562" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A562" s="23"/>
-      <c r="B562" s="21"/>
+      <c r="B562" s="22"/>
       <c r="E562" s="3"/>
       <c r="F562" s="17"/>
       <c r="G562" s="3"/>
@@ -12192,7 +12199,7 @@
     </row>
     <row r="563" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A563" s="23"/>
-      <c r="B563" s="21"/>
+      <c r="B563" s="22"/>
       <c r="C563" s="5"/>
       <c r="D563" s="13"/>
       <c r="E563" s="3"/>
@@ -12206,7 +12213,7 @@
     </row>
     <row r="564" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A564" s="23"/>
-      <c r="B564" s="22" t="s">
+      <c r="B564" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C564" s="6" t="str" cm="1">
@@ -12246,7 +12253,7 @@
     </row>
     <row r="565" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A565" s="23"/>
-      <c r="B565" s="22"/>
+      <c r="B565" s="24"/>
       <c r="C565" s="6" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
@@ -12268,7 +12275,7 @@
     </row>
     <row r="566" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A566" s="23"/>
-      <c r="B566" s="22"/>
+      <c r="B566" s="24"/>
       <c r="C566" s="6" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
@@ -12290,7 +12297,7 @@
     </row>
     <row r="567" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A567" s="23"/>
-      <c r="B567" s="22"/>
+      <c r="B567" s="24"/>
       <c r="C567" s="6" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
@@ -12312,7 +12319,7 @@
     </row>
     <row r="568" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A568" s="23"/>
-      <c r="B568" s="22"/>
+      <c r="B568" s="24"/>
       <c r="C568" s="6" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -12330,7 +12337,7 @@
     </row>
     <row r="569" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A569" s="23"/>
-      <c r="B569" s="22"/>
+      <c r="B569" s="24"/>
       <c r="C569" s="6"/>
       <c r="D569" s="14"/>
       <c r="E569" s="6"/>
@@ -12344,7 +12351,7 @@
     </row>
     <row r="570" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A570" s="23"/>
-      <c r="B570" s="22"/>
+      <c r="B570" s="24"/>
       <c r="C570" s="6" t="str" cm="1">
         <f t="array" ref="C570:D570">E557:F557</f>
         <v>Driver - Hasan</v>
@@ -12363,7 +12370,7 @@
     </row>
     <row r="571" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A571" s="23"/>
-      <c r="B571" s="22"/>
+      <c r="B571" s="24"/>
       <c r="C571" s="8"/>
       <c r="D571" s="14"/>
       <c r="E571" s="6"/>
@@ -12377,7 +12384,7 @@
     </row>
     <row r="572" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A572" s="23"/>
-      <c r="B572" s="22"/>
+      <c r="B572" s="24"/>
       <c r="C572" s="8"/>
       <c r="D572" s="14"/>
       <c r="E572" s="6"/>
@@ -12391,7 +12398,7 @@
     </row>
     <row r="573" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A573" s="23"/>
-      <c r="B573" s="22"/>
+      <c r="B573" s="24"/>
       <c r="C573" s="8"/>
       <c r="D573" s="14"/>
       <c r="G573" s="6"/>
@@ -12403,7 +12410,7 @@
     </row>
     <row r="574" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A574" s="23"/>
-      <c r="B574" s="20" t="s">
+      <c r="B574" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C574" s="9"/>
@@ -12438,7 +12445,7 @@
     </row>
     <row r="575" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A575" s="23"/>
-      <c r="B575" s="20"/>
+      <c r="B575" s="21"/>
       <c r="C575" s="9"/>
       <c r="D575" s="15"/>
       <c r="E575" s="3" t="str">
@@ -12456,7 +12463,7 @@
     </row>
     <row r="576" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A576" s="23"/>
-      <c r="B576" s="20"/>
+      <c r="B576" s="21"/>
       <c r="C576" s="9"/>
       <c r="D576" s="15"/>
       <c r="E576" s="3" t="str">
@@ -12474,7 +12481,7 @@
     </row>
     <row r="577" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A577" s="23"/>
-      <c r="B577" s="20"/>
+      <c r="B577" s="21"/>
       <c r="C577" s="9"/>
       <c r="D577" s="15"/>
       <c r="E577" s="3" t="str">
@@ -12494,7 +12501,7 @@
       <c r="A578" s="25">
         <v>46137</v>
       </c>
-      <c r="B578" s="21" t="s">
+      <c r="B578" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C578" s="3" t="s">
@@ -12530,7 +12537,7 @@
     </row>
     <row r="579" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A579" s="25"/>
-      <c r="B579" s="21"/>
+      <c r="B579" s="22"/>
       <c r="C579" s="3" t="s">
         <v>36</v>
       </c>
@@ -12552,7 +12559,7 @@
     </row>
     <row r="580" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A580" s="25"/>
-      <c r="B580" s="21"/>
+      <c r="B580" s="22"/>
       <c r="C580" s="6" t="s">
         <v>40</v>
       </c>
@@ -12574,7 +12581,7 @@
     </row>
     <row r="581" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A581" s="25"/>
-      <c r="B581" s="21"/>
+      <c r="B581" s="22"/>
       <c r="C581" s="3" t="s">
         <v>18</v>
       </c>
@@ -12596,7 +12603,7 @@
     </row>
     <row r="582" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A582" s="25"/>
-      <c r="B582" s="21"/>
+      <c r="B582" s="22"/>
       <c r="C582" s="3" t="s">
         <v>37</v>
       </c>
@@ -12610,9 +12617,12 @@
     </row>
     <row r="583" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A583" s="25"/>
-      <c r="B583" s="21"/>
-      <c r="C583" s="24" t="s">
+      <c r="B583" s="22"/>
+      <c r="C583" s="20" t="s">
         <v>66</v>
+      </c>
+      <c r="D583" s="4" t="s">
+        <v>69</v>
       </c>
       <c r="E583" s="3"/>
       <c r="F583" s="17"/>
@@ -12623,7 +12633,7 @@
     </row>
     <row r="584" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A584" s="25"/>
-      <c r="B584" s="21"/>
+      <c r="B584" s="22"/>
       <c r="C584" s="5" t="s">
         <v>21</v>
       </c>
@@ -12639,7 +12649,7 @@
     </row>
     <row r="585" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A585" s="25"/>
-      <c r="B585" s="21"/>
+      <c r="B585" s="22"/>
       <c r="E585" s="3"/>
       <c r="F585" s="17"/>
       <c r="G585" s="3"/>
@@ -12651,7 +12661,7 @@
     </row>
     <row r="586" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A586" s="25"/>
-      <c r="B586" s="21"/>
+      <c r="B586" s="22"/>
       <c r="E586" s="3"/>
       <c r="F586" s="17"/>
       <c r="G586" s="3"/>
@@ -12663,7 +12673,7 @@
     </row>
     <row r="587" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A587" s="25"/>
-      <c r="B587" s="21"/>
+      <c r="B587" s="22"/>
       <c r="C587" s="5"/>
       <c r="D587" s="13"/>
       <c r="E587" s="3"/>
@@ -12677,7 +12687,7 @@
     </row>
     <row r="588" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A588" s="25"/>
-      <c r="B588" s="22" t="s">
+      <c r="B588" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C588" s="6" t="s">
@@ -12713,7 +12723,7 @@
     </row>
     <row r="589" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A589" s="25"/>
-      <c r="B589" s="22"/>
+      <c r="B589" s="24"/>
       <c r="C589" s="3" t="s">
         <v>14</v>
       </c>
@@ -12735,7 +12745,7 @@
     </row>
     <row r="590" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A590" s="25"/>
-      <c r="B590" s="22"/>
+      <c r="B590" s="24"/>
       <c r="C590" s="6" t="s">
         <v>41</v>
       </c>
@@ -12757,7 +12767,7 @@
     </row>
     <row r="591" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A591" s="25"/>
-      <c r="B591" s="22"/>
+      <c r="B591" s="24"/>
       <c r="C591" s="6" t="s">
         <v>13</v>
       </c>
@@ -12779,7 +12789,7 @@
     </row>
     <row r="592" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A592" s="25"/>
-      <c r="B592" s="22"/>
+      <c r="B592" s="24"/>
       <c r="C592" s="6" t="s">
         <v>42</v>
       </c>
@@ -12797,13 +12807,13 @@
     </row>
     <row r="593" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A593" s="25"/>
-      <c r="B593" s="22"/>
+      <c r="B593" s="24"/>
       <c r="C593" s="8" t="str">
-        <f t="shared" ref="C593:D593" si="102">E581</f>
+        <f t="shared" ref="C593:D593" si="99">E581</f>
         <v>Driver - Shetu</v>
       </c>
       <c r="D593" s="18" t="str">
-        <f t="shared" si="102"/>
+        <f t="shared" si="99"/>
         <v>01719034964</v>
       </c>
       <c r="E593" s="6"/>
@@ -12817,7 +12827,7 @@
     </row>
     <row r="594" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A594" s="25"/>
-      <c r="B594" s="22"/>
+      <c r="B594" s="24"/>
       <c r="E594" s="6"/>
       <c r="F594" s="18"/>
       <c r="G594" s="6"/>
@@ -12829,7 +12839,7 @@
     </row>
     <row r="595" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A595" s="25"/>
-      <c r="B595" s="22"/>
+      <c r="B595" s="24"/>
       <c r="C595" s="8"/>
       <c r="D595" s="14"/>
       <c r="E595" s="6"/>
@@ -12843,7 +12853,7 @@
     </row>
     <row r="596" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A596" s="25"/>
-      <c r="B596" s="22"/>
+      <c r="B596" s="24"/>
       <c r="C596" s="8"/>
       <c r="D596" s="14"/>
       <c r="E596" s="6"/>
@@ -12857,7 +12867,7 @@
     </row>
     <row r="597" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A597" s="25"/>
-      <c r="B597" s="22"/>
+      <c r="B597" s="24"/>
       <c r="C597" s="8"/>
       <c r="D597" s="14"/>
       <c r="G597" s="6"/>
@@ -12869,7 +12879,7 @@
     </row>
     <row r="598" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A598" s="25"/>
-      <c r="B598" s="20" t="s">
+      <c r="B598" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C598" s="9"/>
@@ -12901,7 +12911,7 @@
     </row>
     <row r="599" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A599" s="25"/>
-      <c r="B599" s="20"/>
+      <c r="B599" s="21"/>
       <c r="C599" s="9"/>
       <c r="D599" s="15"/>
       <c r="E599" s="3" t="s">
@@ -12919,7 +12929,7 @@
     </row>
     <row r="600" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A600" s="25"/>
-      <c r="B600" s="20"/>
+      <c r="B600" s="21"/>
       <c r="C600" s="9"/>
       <c r="D600" s="15"/>
       <c r="E600" s="3" t="s">
@@ -12937,7 +12947,7 @@
     </row>
     <row r="601" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A601" s="25"/>
-      <c r="B601" s="20"/>
+      <c r="B601" s="21"/>
       <c r="C601" s="9"/>
       <c r="D601" s="15"/>
       <c r="E601" s="5" t="s">
@@ -12957,67 +12967,67 @@
       <c r="A602" s="23">
         <v>46138</v>
       </c>
-      <c r="B602" s="21" t="s">
+      <c r="B602" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C602" s="3" t="str">
-        <f t="shared" ref="C602:D602" si="103">C588</f>
+        <f t="shared" ref="C602:D602" si="100">C588</f>
         <v>Monirul Islam  (LM)</v>
       </c>
       <c r="D602" s="13" t="str">
-        <f t="shared" si="103"/>
+        <f t="shared" si="100"/>
         <v>01703409900</v>
       </c>
       <c r="E602" s="11" t="str">
-        <f t="shared" ref="E602:L602" si="104">E578</f>
+        <f t="shared" ref="E602:L602" si="101">E578</f>
         <v>Rakib (LM)</v>
       </c>
       <c r="F602" s="19" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="101"/>
         <v>01767032267</v>
       </c>
       <c r="G602" s="3" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="101"/>
         <v>Shawon Dass</v>
       </c>
       <c r="H602" s="19" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="I602" s="3" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="101"/>
         <v>Salim Reza</v>
       </c>
       <c r="J602" s="19" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="101"/>
         <v>0</v>
       </c>
       <c r="K602" s="6" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="101"/>
         <v>Inul Haque</v>
       </c>
       <c r="L602" s="19" t="str">
-        <f t="shared" si="104"/>
+        <f t="shared" si="101"/>
         <v>02588855910</v>
       </c>
     </row>
     <row r="603" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A603" s="23"/>
-      <c r="B603" s="21"/>
+      <c r="B603" s="22"/>
       <c r="C603" s="3" t="str">
-        <f t="shared" ref="C603:D603" si="105">C589</f>
+        <f t="shared" ref="C603:D603" si="102">C589</f>
         <v>Abdus Sattar (LM)</v>
       </c>
       <c r="D603" s="13" t="str">
-        <f t="shared" si="105"/>
+        <f t="shared" si="102"/>
         <v>01718676281</v>
       </c>
       <c r="E603" s="11" t="str">
-        <f t="shared" ref="E603:F603" si="106">E579</f>
+        <f t="shared" ref="E603:F603" si="103">E579</f>
         <v>Nabi (LH)</v>
       </c>
       <c r="F603" s="19" t="str">
-        <f t="shared" si="106"/>
+        <f t="shared" si="103"/>
         <v>01736352528</v>
       </c>
       <c r="G603" s="3"/>
@@ -13029,21 +13039,21 @@
     </row>
     <row r="604" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A604" s="23"/>
-      <c r="B604" s="21"/>
+      <c r="B604" s="22"/>
       <c r="C604" s="3" t="str">
-        <f t="shared" ref="C604:D604" si="107">C590</f>
+        <f t="shared" ref="C604:D604" si="104">C590</f>
         <v>Sazzad  (LM)</v>
       </c>
       <c r="D604" s="13" t="str">
-        <f t="shared" si="107"/>
+        <f t="shared" si="104"/>
         <v>01719106824</v>
       </c>
       <c r="E604" s="11" t="str">
-        <f t="shared" ref="E604:F604" si="108">E580</f>
+        <f t="shared" ref="E604:F604" si="105">E580</f>
         <v>Anowar (LEM)</v>
       </c>
       <c r="F604" s="19" t="str">
-        <f t="shared" si="108"/>
+        <f t="shared" si="105"/>
         <v>01712439152</v>
       </c>
       <c r="G604" s="3"/>
@@ -13055,21 +13065,21 @@
     </row>
     <row r="605" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A605" s="23"/>
-      <c r="B605" s="21"/>
+      <c r="B605" s="22"/>
       <c r="C605" s="3" t="str">
-        <f t="shared" ref="C605:D605" si="109">C591</f>
+        <f t="shared" ref="C605:D605" si="106">C591</f>
         <v>Jonny (LH)</v>
       </c>
       <c r="D605" s="13" t="str">
-        <f t="shared" si="109"/>
+        <f t="shared" si="106"/>
         <v>01712441588</v>
       </c>
       <c r="E605" s="11" t="str">
-        <f t="shared" ref="E605:F605" si="110">E581</f>
+        <f t="shared" ref="E605:F605" si="107">E581</f>
         <v>Driver - Shetu</v>
       </c>
       <c r="F605" s="19" t="str">
-        <f t="shared" si="110"/>
+        <f t="shared" si="107"/>
         <v>01719034964</v>
       </c>
       <c r="G605" s="3"/>
@@ -13081,13 +13091,13 @@
     </row>
     <row r="606" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A606" s="23"/>
-      <c r="B606" s="21"/>
+      <c r="B606" s="22"/>
       <c r="C606" s="3" t="str">
-        <f t="shared" ref="C606:D606" si="111">C592</f>
+        <f t="shared" ref="C606:D606" si="108">C592</f>
         <v>Nazmul (LEM)</v>
       </c>
       <c r="D606" s="13" t="str">
-        <f t="shared" si="111"/>
+        <f t="shared" si="108"/>
         <v>01914595295</v>
       </c>
       <c r="G606" s="3"/>
@@ -13097,14 +13107,13 @@
     </row>
     <row r="607" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A607" s="23"/>
-      <c r="B607" s="21"/>
-      <c r="C607" s="3" t="str">
-        <f t="shared" ref="C607:D607" si="112">C593</f>
-        <v>Driver - Shetu</v>
+      <c r="B607" s="22"/>
+      <c r="C607" s="3" t="str" cm="1">
+        <f t="array" ref="C607:D607">E601:F601</f>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D607" s="13" t="str">
-        <f t="shared" si="112"/>
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E607" s="3"/>
       <c r="F607" s="17"/>
@@ -13115,7 +13124,7 @@
     </row>
     <row r="608" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A608" s="23"/>
-      <c r="B608" s="21"/>
+      <c r="B608" s="22"/>
       <c r="C608" s="5"/>
       <c r="D608" s="17"/>
       <c r="E608" s="3"/>
@@ -13127,7 +13136,7 @@
     </row>
     <row r="609" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A609" s="23"/>
-      <c r="B609" s="21"/>
+      <c r="B609" s="22"/>
       <c r="E609" s="3"/>
       <c r="F609" s="17"/>
       <c r="G609" s="3"/>
@@ -13139,7 +13148,7 @@
     </row>
     <row r="610" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A610" s="23"/>
-      <c r="B610" s="21"/>
+      <c r="B610" s="22"/>
       <c r="E610" s="3"/>
       <c r="F610" s="17"/>
       <c r="G610" s="3"/>
@@ -13151,7 +13160,7 @@
     </row>
     <row r="611" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A611" s="23"/>
-      <c r="B611" s="21"/>
+      <c r="B611" s="22"/>
       <c r="C611" s="5"/>
       <c r="D611" s="13"/>
       <c r="E611" s="3"/>
@@ -13165,67 +13174,67 @@
     </row>
     <row r="612" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A612" s="23"/>
-      <c r="B612" s="22" t="s">
+      <c r="B612" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C612" s="6" t="str">
-        <f t="shared" ref="C612:D612" si="113">C578</f>
+        <f t="shared" ref="C612:D612" si="109">C578</f>
         <v>Mostafijur (LM)</v>
       </c>
       <c r="D612" s="14" t="str">
-        <f t="shared" si="113"/>
+        <f t="shared" si="109"/>
         <v>01758212103</v>
       </c>
       <c r="E612" s="3" t="str">
-        <f t="shared" ref="E612:K612" si="114">E588</f>
+        <f t="shared" ref="E612:K612" si="110">E588</f>
         <v>Maruf Hossain (LM)</v>
       </c>
       <c r="F612" s="13" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="110"/>
         <v>01943368198</v>
       </c>
       <c r="G612" s="6" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="110"/>
         <v>Alauddin</v>
       </c>
       <c r="H612" s="19" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="I612" s="6" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="110"/>
         <v>Moin Uddin</v>
       </c>
       <c r="J612" s="19" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="110"/>
         <v>0</v>
       </c>
       <c r="K612" s="11" t="str">
-        <f t="shared" si="114"/>
+        <f t="shared" si="110"/>
         <v>Masud Rana</v>
       </c>
       <c r="L612" s="19" t="str">
-        <f t="shared" ref="L612" si="115">L622</f>
+        <f t="shared" ref="L612" si="111">L622</f>
         <v>02588855910</v>
       </c>
     </row>
     <row r="613" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A613" s="23"/>
-      <c r="B613" s="22"/>
+      <c r="B613" s="24"/>
       <c r="C613" s="6" t="str">
-        <f t="shared" ref="C613:D613" si="116">C579</f>
+        <f t="shared" ref="C613:D613" si="112">C579</f>
         <v>Monzur Kader (LM)</v>
       </c>
       <c r="D613" s="14" t="str">
-        <f t="shared" si="116"/>
+        <f t="shared" si="112"/>
         <v>01705614054</v>
       </c>
       <c r="E613" s="3" t="str">
-        <f t="shared" ref="E613:F613" si="117">E589</f>
+        <f t="shared" ref="E613:F613" si="113">E589</f>
         <v>Sahjahan (LEM)</v>
       </c>
       <c r="F613" s="13" t="str">
-        <f t="shared" si="117"/>
+        <f t="shared" si="113"/>
         <v>01724267460</v>
       </c>
       <c r="G613" s="6"/>
@@ -13237,21 +13246,21 @@
     </row>
     <row r="614" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A614" s="23"/>
-      <c r="B614" s="22"/>
+      <c r="B614" s="24"/>
       <c r="C614" s="6" t="str">
-        <f t="shared" ref="C614:D614" si="118">C580</f>
+        <f t="shared" ref="C614:D614" si="114">C580</f>
         <v>Mosaddek  (LM)</v>
       </c>
       <c r="D614" s="14" t="str">
-        <f t="shared" si="118"/>
+        <f t="shared" si="114"/>
         <v>01674272353</v>
       </c>
       <c r="E614" s="3" t="str">
-        <f t="shared" ref="E614:F614" si="119">E590</f>
+        <f t="shared" ref="E614:F614" si="115">E590</f>
         <v>Fuad (LH)</v>
       </c>
       <c r="F614" s="13" t="str">
-        <f t="shared" si="119"/>
+        <f t="shared" si="115"/>
         <v>01718279112</v>
       </c>
       <c r="G614" s="6"/>
@@ -13263,21 +13272,21 @@
     </row>
     <row r="615" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A615" s="23"/>
-      <c r="B615" s="22"/>
+      <c r="B615" s="24"/>
       <c r="C615" s="6" t="str">
-        <f t="shared" ref="C615:D615" si="120">C581</f>
+        <f t="shared" ref="C615:D615" si="116">C581</f>
         <v>Abdus Salam (LM)</v>
       </c>
       <c r="D615" s="14" t="str">
-        <f t="shared" si="120"/>
+        <f t="shared" si="116"/>
         <v>01756101919</v>
       </c>
       <c r="E615" s="3" t="str">
-        <f t="shared" ref="E615:F615" si="121">E591</f>
+        <f t="shared" ref="E615:F615" si="117">E591</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="F615" s="13" t="str">
-        <f t="shared" si="121"/>
+        <f t="shared" si="117"/>
         <v>01748127818</v>
       </c>
       <c r="G615" s="6"/>
@@ -13289,13 +13298,13 @@
     </row>
     <row r="616" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A616" s="23"/>
-      <c r="B616" s="22"/>
+      <c r="B616" s="24"/>
       <c r="C616" s="6" t="str">
-        <f t="shared" ref="C616:D616" si="122">C582</f>
+        <f t="shared" ref="C616:D616" si="118">C582</f>
         <v>Salim Reza-2 (LH)</v>
       </c>
       <c r="D616" s="14" t="str">
-        <f t="shared" si="122"/>
+        <f t="shared" si="118"/>
         <v>01719531782</v>
       </c>
       <c r="E616" s="6"/>
@@ -13309,14 +13318,14 @@
     </row>
     <row r="617" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A617" s="23"/>
-      <c r="B617" s="22"/>
+      <c r="B617" s="24"/>
       <c r="C617" s="6" t="str">
-        <f t="shared" ref="C617:D617" si="123">C583</f>
+        <f t="shared" ref="C617:D617" si="119">C583</f>
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D617" s="14">
-        <f t="shared" si="123"/>
-        <v>0</v>
+      <c r="D617" s="14" t="str">
+        <f t="shared" si="119"/>
+        <v>01723504940</v>
       </c>
       <c r="E617" s="6"/>
       <c r="F617" s="18"/>
@@ -13329,14 +13338,13 @@
     </row>
     <row r="618" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A618" s="23"/>
-      <c r="B618" s="22"/>
-      <c r="C618" s="6" t="str">
-        <f t="shared" ref="C618:D618" si="124">C584</f>
-        <v>Driver - Hasan</v>
+      <c r="B618" s="24"/>
+      <c r="C618" s="6" t="str" cm="1">
+        <f t="array" ref="C618:D618">E605:F605</f>
+        <v>Driver - Shetu</v>
       </c>
       <c r="D618" s="14" t="str">
-        <f t="shared" si="124"/>
-        <v>01730824934</v>
+        <v>01719034964</v>
       </c>
       <c r="E618" s="6"/>
       <c r="F618" s="18"/>
@@ -13349,7 +13357,7 @@
     </row>
     <row r="619" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A619" s="23"/>
-      <c r="B619" s="22"/>
+      <c r="B619" s="24"/>
       <c r="C619" s="8"/>
       <c r="D619" s="14"/>
       <c r="E619" s="6"/>
@@ -13363,7 +13371,7 @@
     </row>
     <row r="620" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A620" s="23"/>
-      <c r="B620" s="22"/>
+      <c r="B620" s="24"/>
       <c r="C620" s="8"/>
       <c r="D620" s="14"/>
       <c r="E620" s="6"/>
@@ -13377,7 +13385,7 @@
     </row>
     <row r="621" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A621" s="23"/>
-      <c r="B621" s="22"/>
+      <c r="B621" s="24"/>
       <c r="C621" s="8"/>
       <c r="D621" s="14"/>
       <c r="G621" s="6"/>
@@ -13389,55 +13397,55 @@
     </row>
     <row r="622" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A622" s="23"/>
-      <c r="B622" s="20" t="s">
+      <c r="B622" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C622" s="9"/>
       <c r="D622" s="15"/>
       <c r="E622" s="3" t="str">
-        <f t="shared" ref="E622:L622" si="125">E598</f>
+        <f t="shared" ref="E622:L622" si="120">E598</f>
         <v>Sumon (LM)</v>
       </c>
       <c r="F622" s="17" t="str">
-        <f t="shared" si="125"/>
+        <f t="shared" si="120"/>
         <v>01726258394</v>
       </c>
       <c r="G622" s="11" t="str">
-        <f t="shared" si="125"/>
+        <f t="shared" si="120"/>
         <v>Abdur Rafique</v>
       </c>
       <c r="H622" s="19" t="str">
-        <f t="shared" si="125"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="I622" s="11" t="str">
-        <f t="shared" si="125"/>
+        <f t="shared" si="120"/>
         <v>Abul Kalam Azad</v>
       </c>
       <c r="J622" s="19" t="str">
-        <f t="shared" si="125"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="K622" s="3" t="str">
-        <f t="shared" si="125"/>
+        <f t="shared" si="120"/>
         <v>Monzur Ahmed</v>
       </c>
       <c r="L622" s="19" t="str">
-        <f t="shared" si="125"/>
+        <f t="shared" si="120"/>
         <v>02588855910</v>
       </c>
     </row>
     <row r="623" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A623" s="23"/>
-      <c r="B623" s="20"/>
+      <c r="B623" s="21"/>
       <c r="C623" s="9"/>
       <c r="D623" s="15"/>
       <c r="E623" s="3" t="str">
-        <f t="shared" ref="E623:F623" si="126">E599</f>
+        <f t="shared" ref="E623:F623" si="121">E599</f>
         <v>Arafat (LH)</v>
       </c>
       <c r="F623" s="17" t="str">
-        <f t="shared" si="126"/>
+        <f t="shared" si="121"/>
         <v>01755149115</v>
       </c>
       <c r="G623" s="11"/>
@@ -13449,15 +13457,15 @@
     </row>
     <row r="624" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A624" s="23"/>
-      <c r="B624" s="20"/>
+      <c r="B624" s="21"/>
       <c r="C624" s="9"/>
       <c r="D624" s="15"/>
       <c r="E624" s="3" t="str">
-        <f t="shared" ref="E624:F624" si="127">E600</f>
+        <f t="shared" ref="E624:F624" si="122">E600</f>
         <v>Mamun (LH)</v>
       </c>
       <c r="F624" s="17" t="str">
-        <f t="shared" si="127"/>
+        <f t="shared" si="122"/>
         <v>01718106022</v>
       </c>
       <c r="G624" s="11"/>
@@ -13469,15 +13477,15 @@
     </row>
     <row r="625" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A625" s="23"/>
-      <c r="B625" s="20"/>
+      <c r="B625" s="21"/>
       <c r="C625" s="9"/>
       <c r="D625" s="15"/>
       <c r="E625" s="3" t="str">
-        <f t="shared" ref="E625:F625" si="128">E601</f>
+        <f t="shared" ref="E625:F625" si="123">E601</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="F625" s="17" t="str">
-        <f t="shared" si="128"/>
+        <f t="shared" si="123"/>
         <v>01730824934</v>
       </c>
       <c r="G625" s="11"/>
@@ -13491,7 +13499,7 @@
       <c r="A626" s="23">
         <v>46139</v>
       </c>
-      <c r="B626" s="21" t="s">
+      <c r="B626" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C626" s="3" t="str" cm="1">
@@ -13501,12 +13509,12 @@
       <c r="D626" s="13" t="str">
         <v>01703409900</v>
       </c>
-      <c r="E626" s="11" t="str" cm="1">
-        <f t="array" ref="E626:F629">E622:F625</f>
-        <v>Sumon (LM)</v>
-      </c>
-      <c r="F626" s="19" t="str">
-        <v>01726258394</v>
+      <c r="E626" s="3" t="str" cm="1">
+        <f t="array" ref="E626:F629">E612:F615</f>
+        <v>Maruf Hossain (LM)</v>
+      </c>
+      <c r="F626" s="17" t="str">
+        <v>01943368198</v>
       </c>
       <c r="G626" s="3" t="str" cm="1">
         <f t="array" ref="G626:H626">G612:H612</f>
@@ -13532,18 +13540,18 @@
     </row>
     <row r="627" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A627" s="23"/>
-      <c r="B627" s="21"/>
+      <c r="B627" s="22"/>
       <c r="C627" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
       <c r="D627" s="13" t="str">
         <v>01718676281</v>
       </c>
-      <c r="E627" s="11" t="str">
-        <v>Arafat (LH)</v>
-      </c>
-      <c r="F627" s="19" t="str">
-        <v>01755149115</v>
+      <c r="E627" s="3" t="str">
+        <v>Sahjahan (LEM)</v>
+      </c>
+      <c r="F627" s="17" t="str">
+        <v>01724267460</v>
       </c>
       <c r="G627" s="3"/>
       <c r="H627" s="4"/>
@@ -13554,18 +13562,18 @@
     </row>
     <row r="628" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A628" s="23"/>
-      <c r="B628" s="21"/>
+      <c r="B628" s="22"/>
       <c r="C628" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
       <c r="D628" s="13" t="str">
         <v>01719106824</v>
       </c>
-      <c r="E628" s="11" t="str">
-        <v>Mamun (LH)</v>
-      </c>
-      <c r="F628" s="19" t="str">
-        <v>01718106022</v>
+      <c r="E628" s="3" t="str">
+        <v>Fuad (LH)</v>
+      </c>
+      <c r="F628" s="17" t="str">
+        <v>01718279112</v>
       </c>
       <c r="G628" s="3"/>
       <c r="H628" s="4"/>
@@ -13576,18 +13584,18 @@
     </row>
     <row r="629" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A629" s="23"/>
-      <c r="B629" s="21"/>
+      <c r="B629" s="22"/>
       <c r="C629" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
       <c r="D629" s="13" t="str">
         <v>01712441588</v>
       </c>
-      <c r="E629" s="11" t="str">
-        <v>Driver - Hasan</v>
-      </c>
-      <c r="F629" s="19" t="str">
-        <v>01730824934</v>
+      <c r="E629" s="3" t="str">
+        <v>Driver - Noyon</v>
+      </c>
+      <c r="F629" s="17" t="str">
+        <v>01748127818</v>
       </c>
       <c r="G629" s="3"/>
       <c r="H629" s="4"/>
@@ -13598,7 +13606,7 @@
     </row>
     <row r="630" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A630" s="23"/>
-      <c r="B630" s="21"/>
+      <c r="B630" s="22"/>
       <c r="C630" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -13612,7 +13620,7 @@
     </row>
     <row r="631" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A631" s="23"/>
-      <c r="B631" s="21"/>
+      <c r="B631" s="22"/>
       <c r="C631" s="3"/>
       <c r="D631" s="13"/>
       <c r="E631" s="3"/>
@@ -13624,13 +13632,13 @@
     </row>
     <row r="632" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A632" s="23"/>
-      <c r="B632" s="21"/>
+      <c r="B632" s="22"/>
       <c r="C632" s="5" t="str">
-        <f t="shared" ref="C632:D632" si="129">E625</f>
+        <f t="shared" ref="C632:D632" si="124">E625</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="D632" s="17" t="str">
-        <f t="shared" si="129"/>
+        <f t="shared" si="124"/>
         <v>01730824934</v>
       </c>
       <c r="E632" s="3"/>
@@ -13642,7 +13650,7 @@
     </row>
     <row r="633" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A633" s="23"/>
-      <c r="B633" s="21"/>
+      <c r="B633" s="22"/>
       <c r="E633" s="3"/>
       <c r="F633" s="17"/>
       <c r="G633" s="3"/>
@@ -13654,7 +13662,7 @@
     </row>
     <row r="634" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A634" s="23"/>
-      <c r="B634" s="21"/>
+      <c r="B634" s="22"/>
       <c r="E634" s="3"/>
       <c r="F634" s="17"/>
       <c r="G634" s="3"/>
@@ -13666,7 +13674,7 @@
     </row>
     <row r="635" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A635" s="23"/>
-      <c r="B635" s="21"/>
+      <c r="B635" s="22"/>
       <c r="C635" s="5"/>
       <c r="D635" s="13"/>
       <c r="E635" s="3"/>
@@ -13680,7 +13688,7 @@
     </row>
     <row r="636" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A636" s="23"/>
-      <c r="B636" s="22" t="s">
+      <c r="B636" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C636" s="6" t="str" cm="1">
@@ -13690,12 +13698,12 @@
       <c r="D636" s="14" t="str">
         <v>01758212103</v>
       </c>
-      <c r="E636" s="3" t="str" cm="1">
-        <f t="array" ref="E636:F639">E602:F605</f>
-        <v>Rakib (LM)</v>
-      </c>
-      <c r="F636" s="13" t="str">
-        <v>01767032267</v>
+      <c r="E636" s="11" t="str" cm="1">
+        <f t="array" ref="E636:F639">E622:F625</f>
+        <v>Sumon (LM)</v>
+      </c>
+      <c r="F636" s="19" t="str">
+        <v>01726258394</v>
       </c>
       <c r="G636" s="6" t="str" cm="1">
         <f t="array" ref="G636:H636">G622:H622</f>
@@ -13721,18 +13729,18 @@
     </row>
     <row r="637" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A637" s="23"/>
-      <c r="B637" s="22"/>
+      <c r="B637" s="24"/>
       <c r="C637" s="6" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
       <c r="D637" s="14" t="str">
         <v>01705614054</v>
       </c>
-      <c r="E637" s="3" t="str">
-        <v>Nabi (LH)</v>
-      </c>
-      <c r="F637" s="13" t="str">
-        <v>01736352528</v>
+      <c r="E637" s="11" t="str">
+        <v>Arafat (LH)</v>
+      </c>
+      <c r="F637" s="19" t="str">
+        <v>01755149115</v>
       </c>
       <c r="G637" s="6"/>
       <c r="H637" s="7"/>
@@ -13747,18 +13755,18 @@
     </row>
     <row r="638" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A638" s="23"/>
-      <c r="B638" s="22"/>
+      <c r="B638" s="24"/>
       <c r="C638" s="6" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
       <c r="D638" s="14" t="str">
         <v>01674272353</v>
       </c>
-      <c r="E638" s="3" t="str">
-        <v>Anowar (LEM)</v>
-      </c>
-      <c r="F638" s="13" t="str">
-        <v>01712439152</v>
+      <c r="E638" s="11" t="str">
+        <v>Mamun (LH)</v>
+      </c>
+      <c r="F638" s="19" t="str">
+        <v>01718106022</v>
       </c>
       <c r="G638" s="6"/>
       <c r="H638" s="7"/>
@@ -13769,18 +13777,18 @@
     </row>
     <row r="639" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A639" s="23"/>
-      <c r="B639" s="22"/>
+      <c r="B639" s="24"/>
       <c r="C639" s="6" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
       <c r="D639" s="14" t="str">
         <v>01756101919</v>
       </c>
-      <c r="E639" s="3" t="str">
-        <v>Driver - Shetu</v>
-      </c>
-      <c r="F639" s="13" t="str">
-        <v>01719034964</v>
+      <c r="E639" s="11" t="str">
+        <v>Driver - Hasan</v>
+      </c>
+      <c r="F639" s="19" t="str">
+        <v>01730824934</v>
       </c>
       <c r="G639" s="6"/>
       <c r="H639" s="7"/>
@@ -13791,7 +13799,7 @@
     </row>
     <row r="640" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A640" s="23"/>
-      <c r="B640" s="22"/>
+      <c r="B640" s="24"/>
       <c r="C640" s="6" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -13809,12 +13817,12 @@
     </row>
     <row r="641" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A641" s="23"/>
-      <c r="B641" s="22"/>
+      <c r="B641" s="24"/>
       <c r="C641" s="6" t="str">
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D641" s="14">
-        <v>0</v>
+      <c r="D641" s="14" t="str">
+        <v>01723504940</v>
       </c>
       <c r="E641" s="6"/>
       <c r="F641" s="18"/>
@@ -13827,9 +13835,9 @@
     </row>
     <row r="642" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A642" s="23"/>
-      <c r="B642" s="22"/>
+      <c r="B642" s="24"/>
       <c r="C642" s="6" t="str" cm="1">
-        <f t="array" ref="C642:D642">E629:F629</f>
+        <f t="array" ref="C642:D642">E639:F639</f>
         <v>Driver - Hasan</v>
       </c>
       <c r="D642" s="14" t="str">
@@ -13846,7 +13854,7 @@
     </row>
     <row r="643" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A643" s="23"/>
-      <c r="B643" s="22"/>
+      <c r="B643" s="24"/>
       <c r="C643" s="8"/>
       <c r="D643" s="14"/>
       <c r="E643" s="6"/>
@@ -13860,7 +13868,7 @@
     </row>
     <row r="644" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A644" s="23"/>
-      <c r="B644" s="22"/>
+      <c r="B644" s="24"/>
       <c r="C644" s="8"/>
       <c r="D644" s="14"/>
       <c r="E644" s="6"/>
@@ -13874,7 +13882,7 @@
     </row>
     <row r="645" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A645" s="23"/>
-      <c r="B645" s="22"/>
+      <c r="B645" s="24"/>
       <c r="C645" s="8"/>
       <c r="D645" s="14"/>
       <c r="G645" s="6"/>
@@ -13886,17 +13894,17 @@
     </row>
     <row r="646" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A646" s="23"/>
-      <c r="B646" s="20" t="s">
+      <c r="B646" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C646" s="9"/>
       <c r="D646" s="15"/>
       <c r="E646" s="3" t="str" cm="1">
-        <f t="array" ref="E646:F649">E612:F615</f>
-        <v>Maruf Hossain (LM)</v>
-      </c>
-      <c r="F646" s="17" t="str">
-        <v>01943368198</v>
+        <f t="array" ref="E646:F649">E602:F605</f>
+        <v>Rakib (LM)</v>
+      </c>
+      <c r="F646" s="13" t="str">
+        <v>01767032267</v>
       </c>
       <c r="G646" s="11" t="str" cm="1">
         <f t="array" ref="G646:H646">G602:H602</f>
@@ -13922,14 +13930,14 @@
     </row>
     <row r="647" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A647" s="23"/>
-      <c r="B647" s="20"/>
+      <c r="B647" s="21"/>
       <c r="C647" s="9"/>
       <c r="D647" s="15"/>
       <c r="E647" s="3" t="str">
-        <v>Sahjahan (LEM)</v>
-      </c>
-      <c r="F647" s="17" t="str">
-        <v>01724267460</v>
+        <v>Nabi (LH)</v>
+      </c>
+      <c r="F647" s="13" t="str">
+        <v>01736352528</v>
       </c>
       <c r="G647" s="11"/>
       <c r="H647" s="10"/>
@@ -13940,14 +13948,14 @@
     </row>
     <row r="648" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A648" s="23"/>
-      <c r="B648" s="20"/>
+      <c r="B648" s="21"/>
       <c r="C648" s="9"/>
       <c r="D648" s="15"/>
       <c r="E648" s="3" t="str">
-        <v>Fuad (LH)</v>
-      </c>
-      <c r="F648" s="17" t="str">
-        <v>01718279112</v>
+        <v>Anowar (LEM)</v>
+      </c>
+      <c r="F648" s="13" t="str">
+        <v>01712439152</v>
       </c>
       <c r="G648" s="11"/>
       <c r="H648" s="10"/>
@@ -13958,14 +13966,14 @@
     </row>
     <row r="649" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A649" s="23"/>
-      <c r="B649" s="20"/>
+      <c r="B649" s="21"/>
       <c r="C649" s="9"/>
       <c r="D649" s="15"/>
       <c r="E649" s="3" t="str">
-        <v>Driver - Noyon</v>
-      </c>
-      <c r="F649" s="17" t="str">
-        <v>01748127818</v>
+        <v>Driver - Shetu</v>
+      </c>
+      <c r="F649" s="13" t="str">
+        <v>01719034964</v>
       </c>
       <c r="G649" s="11"/>
       <c r="H649" s="10"/>
@@ -13978,7 +13986,7 @@
       <c r="A650" s="23">
         <v>46140</v>
       </c>
-      <c r="B650" s="21" t="s">
+      <c r="B650" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C650" s="3" t="str" cm="1">
@@ -13989,7 +13997,7 @@
         <v>01703409900</v>
       </c>
       <c r="E650" s="11" t="str" cm="1">
-        <f t="array" ref="E650:F653">E646:F649</f>
+        <f t="array" ref="E650:F653">E626:F629</f>
         <v>Maruf Hossain (LM)</v>
       </c>
       <c r="F650" s="19" t="str">
@@ -14018,7 +14026,7 @@
     </row>
     <row r="651" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A651" s="23"/>
-      <c r="B651" s="21"/>
+      <c r="B651" s="22"/>
       <c r="C651" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -14040,7 +14048,7 @@
     </row>
     <row r="652" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A652" s="23"/>
-      <c r="B652" s="21"/>
+      <c r="B652" s="22"/>
       <c r="C652" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -14062,7 +14070,7 @@
     </row>
     <row r="653" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A653" s="23"/>
-      <c r="B653" s="21"/>
+      <c r="B653" s="22"/>
       <c r="C653" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -14084,7 +14092,7 @@
     </row>
     <row r="654" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A654" s="23"/>
-      <c r="B654" s="21"/>
+      <c r="B654" s="22"/>
       <c r="C654" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -14098,7 +14106,7 @@
     </row>
     <row r="655" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A655" s="23"/>
-      <c r="B655" s="21"/>
+      <c r="B655" s="22"/>
       <c r="C655" s="3"/>
       <c r="D655" s="13"/>
       <c r="E655" s="3"/>
@@ -14110,13 +14118,13 @@
     </row>
     <row r="656" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A656" s="23"/>
-      <c r="B656" s="21"/>
+      <c r="B656" s="22"/>
       <c r="C656" s="5" t="str">
-        <f t="shared" ref="C656:D656" si="130">E649</f>
+        <f t="shared" ref="C656:D656" si="125">E629</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="D656" s="17" t="str">
-        <f t="shared" si="130"/>
+        <f t="shared" si="125"/>
         <v>01748127818</v>
       </c>
       <c r="E656" s="3"/>
@@ -14128,7 +14136,7 @@
     </row>
     <row r="657" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A657" s="23"/>
-      <c r="B657" s="21"/>
+      <c r="B657" s="22"/>
       <c r="E657" s="3"/>
       <c r="F657" s="17"/>
       <c r="G657" s="3"/>
@@ -14140,7 +14148,7 @@
     </row>
     <row r="658" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A658" s="23"/>
-      <c r="B658" s="21"/>
+      <c r="B658" s="22"/>
       <c r="E658" s="3"/>
       <c r="F658" s="17"/>
       <c r="G658" s="3"/>
@@ -14152,7 +14160,7 @@
     </row>
     <row r="659" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A659" s="23"/>
-      <c r="B659" s="21"/>
+      <c r="B659" s="22"/>
       <c r="C659" s="5"/>
       <c r="D659" s="13"/>
       <c r="E659" s="3"/>
@@ -14166,7 +14174,7 @@
     </row>
     <row r="660" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A660" s="23"/>
-      <c r="B660" s="22" t="s">
+      <c r="B660" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C660" s="6" t="str" cm="1">
@@ -14177,7 +14185,7 @@
         <v>01703409900</v>
       </c>
       <c r="E660" s="3" t="str" cm="1">
-        <f t="array" ref="E660:F663">E626:F629</f>
+        <f t="array" ref="E660:F663">E636:F639</f>
         <v>Sumon (LM)</v>
       </c>
       <c r="F660" s="13" t="str">
@@ -14206,7 +14214,7 @@
     </row>
     <row r="661" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A661" s="23"/>
-      <c r="B661" s="22"/>
+      <c r="B661" s="24"/>
       <c r="C661" s="6" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -14228,7 +14236,7 @@
     </row>
     <row r="662" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A662" s="23"/>
-      <c r="B662" s="22"/>
+      <c r="B662" s="24"/>
       <c r="C662" s="6" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -14250,7 +14258,7 @@
     </row>
     <row r="663" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A663" s="23"/>
-      <c r="B663" s="22"/>
+      <c r="B663" s="24"/>
       <c r="C663" s="6" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -14272,7 +14280,7 @@
     </row>
     <row r="664" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A664" s="23"/>
-      <c r="B664" s="22"/>
+      <c r="B664" s="24"/>
       <c r="C664" s="6" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -14290,12 +14298,12 @@
     </row>
     <row r="665" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A665" s="23"/>
-      <c r="B665" s="22"/>
+      <c r="B665" s="24"/>
       <c r="C665" s="6" t="str">
-        <v>Driver - Shetu</v>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D665" s="14" t="str">
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E665" s="6"/>
       <c r="F665" s="18"/>
@@ -14308,7 +14316,7 @@
     </row>
     <row r="666" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A666" s="23"/>
-      <c r="B666" s="22"/>
+      <c r="B666" s="24"/>
       <c r="C666" s="6" t="str" cm="1">
         <f t="array" ref="C666:D666">E653:F653</f>
         <v>Driver - Noyon</v>
@@ -14327,7 +14335,7 @@
     </row>
     <row r="667" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A667" s="23"/>
-      <c r="B667" s="22"/>
+      <c r="B667" s="24"/>
       <c r="C667" s="8"/>
       <c r="D667" s="14"/>
       <c r="E667" s="6"/>
@@ -14341,7 +14349,7 @@
     </row>
     <row r="668" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A668" s="23"/>
-      <c r="B668" s="22"/>
+      <c r="B668" s="24"/>
       <c r="C668" s="8"/>
       <c r="D668" s="14"/>
       <c r="E668" s="6"/>
@@ -14355,7 +14363,7 @@
     </row>
     <row r="669" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A669" s="23"/>
-      <c r="B669" s="22"/>
+      <c r="B669" s="24"/>
       <c r="C669" s="8"/>
       <c r="D669" s="14"/>
       <c r="G669" s="6"/>
@@ -14367,13 +14375,13 @@
     </row>
     <row r="670" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A670" s="23"/>
-      <c r="B670" s="20" t="s">
+      <c r="B670" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C670" s="9"/>
       <c r="D670" s="15"/>
       <c r="E670" s="3" t="str" cm="1">
-        <f t="array" ref="E670:F673">E636:F639</f>
+        <f t="array" ref="E670:F673">E646:F649</f>
         <v>Rakib (LM)</v>
       </c>
       <c r="F670" s="17" t="str">
@@ -14402,7 +14410,7 @@
     </row>
     <row r="671" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A671" s="23"/>
-      <c r="B671" s="20"/>
+      <c r="B671" s="21"/>
       <c r="C671" s="9"/>
       <c r="D671" s="15"/>
       <c r="E671" s="3" t="str">
@@ -14420,7 +14428,7 @@
     </row>
     <row r="672" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A672" s="23"/>
-      <c r="B672" s="20"/>
+      <c r="B672" s="21"/>
       <c r="C672" s="9"/>
       <c r="D672" s="15"/>
       <c r="E672" s="3" t="str">
@@ -14438,7 +14446,7 @@
     </row>
     <row r="673" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A673" s="23"/>
-      <c r="B673" s="20"/>
+      <c r="B673" s="21"/>
       <c r="C673" s="9"/>
       <c r="D673" s="15"/>
       <c r="E673" s="3" t="str">
@@ -14458,7 +14466,7 @@
       <c r="A674" s="23">
         <v>46141</v>
       </c>
-      <c r="B674" s="21" t="s">
+      <c r="B674" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C674" s="3" t="str" cm="1">
@@ -14499,7 +14507,7 @@
     </row>
     <row r="675" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A675" s="23"/>
-      <c r="B675" s="21"/>
+      <c r="B675" s="22"/>
       <c r="C675" s="3" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
@@ -14521,7 +14529,7 @@
     </row>
     <row r="676" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A676" s="23"/>
-      <c r="B676" s="21"/>
+      <c r="B676" s="22"/>
       <c r="C676" s="3" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
@@ -14543,7 +14551,7 @@
     </row>
     <row r="677" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A677" s="23"/>
-      <c r="B677" s="21"/>
+      <c r="B677" s="22"/>
       <c r="C677" s="3" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
@@ -14565,7 +14573,7 @@
     </row>
     <row r="678" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A678" s="23"/>
-      <c r="B678" s="21"/>
+      <c r="B678" s="22"/>
       <c r="C678" s="3" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -14579,12 +14587,12 @@
     </row>
     <row r="679" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A679" s="23"/>
-      <c r="B679" s="21"/>
+      <c r="B679" s="22"/>
       <c r="C679" s="3" t="str">
         <v>Yeakub (LH)</v>
       </c>
-      <c r="D679" s="13">
-        <v>0</v>
+      <c r="D679" s="13" t="str">
+        <v>01723504940</v>
       </c>
       <c r="E679" s="3"/>
       <c r="F679" s="17"/>
@@ -14595,13 +14603,13 @@
     </row>
     <row r="680" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A680" s="23"/>
-      <c r="B680" s="21"/>
+      <c r="B680" s="22"/>
       <c r="C680" s="5" t="str">
-        <f t="shared" ref="C680:D680" si="131">E673</f>
+        <f t="shared" ref="C680:D680" si="126">E673</f>
         <v>Driver - Shetu</v>
       </c>
       <c r="D680" s="17" t="str">
-        <f t="shared" si="131"/>
+        <f t="shared" si="126"/>
         <v>01719034964</v>
       </c>
       <c r="E680" s="3"/>
@@ -14613,7 +14621,7 @@
     </row>
     <row r="681" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A681" s="23"/>
-      <c r="B681" s="21"/>
+      <c r="B681" s="22"/>
       <c r="E681" s="3"/>
       <c r="F681" s="17"/>
       <c r="G681" s="3"/>
@@ -14625,7 +14633,7 @@
     </row>
     <row r="682" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A682" s="23"/>
-      <c r="B682" s="21"/>
+      <c r="B682" s="22"/>
       <c r="E682" s="3"/>
       <c r="F682" s="17"/>
       <c r="G682" s="3"/>
@@ -14637,7 +14645,7 @@
     </row>
     <row r="683" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A683" s="23"/>
-      <c r="B683" s="21"/>
+      <c r="B683" s="22"/>
       <c r="C683" s="5"/>
       <c r="D683" s="13"/>
       <c r="E683" s="3"/>
@@ -14651,7 +14659,7 @@
     </row>
     <row r="684" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A684" s="23"/>
-      <c r="B684" s="22" t="s">
+      <c r="B684" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C684" s="6" t="str" cm="1">
@@ -14692,7 +14700,7 @@
     </row>
     <row r="685" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A685" s="23"/>
-      <c r="B685" s="22"/>
+      <c r="B685" s="24"/>
       <c r="C685" s="6" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -14714,7 +14722,7 @@
     </row>
     <row r="686" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A686" s="23"/>
-      <c r="B686" s="22"/>
+      <c r="B686" s="24"/>
       <c r="C686" s="6" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -14736,7 +14744,7 @@
     </row>
     <row r="687" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A687" s="23"/>
-      <c r="B687" s="22"/>
+      <c r="B687" s="24"/>
       <c r="C687" s="6" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -14758,7 +14766,7 @@
     </row>
     <row r="688" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A688" s="23"/>
-      <c r="B688" s="22"/>
+      <c r="B688" s="24"/>
       <c r="C688" s="6" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -14776,7 +14784,7 @@
     </row>
     <row r="689" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A689" s="23"/>
-      <c r="B689" s="22"/>
+      <c r="B689" s="24"/>
       <c r="C689" s="6"/>
       <c r="D689" s="14"/>
       <c r="E689" s="6"/>
@@ -14790,7 +14798,7 @@
     </row>
     <row r="690" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A690" s="23"/>
-      <c r="B690" s="22"/>
+      <c r="B690" s="24"/>
       <c r="C690" s="6" t="str" cm="1">
         <f t="array" ref="C690:D690">E677:F677</f>
         <v>Driver - Hasan</v>
@@ -14809,7 +14817,7 @@
     </row>
     <row r="691" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A691" s="23"/>
-      <c r="B691" s="22"/>
+      <c r="B691" s="24"/>
       <c r="C691" s="8"/>
       <c r="D691" s="14"/>
       <c r="E691" s="6"/>
@@ -14823,7 +14831,7 @@
     </row>
     <row r="692" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A692" s="23"/>
-      <c r="B692" s="22"/>
+      <c r="B692" s="24"/>
       <c r="C692" s="8"/>
       <c r="D692" s="14"/>
       <c r="E692" s="6"/>
@@ -14837,7 +14845,7 @@
     </row>
     <row r="693" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A693" s="23"/>
-      <c r="B693" s="22"/>
+      <c r="B693" s="24"/>
       <c r="C693" s="8"/>
       <c r="D693" s="14"/>
       <c r="G693" s="6"/>
@@ -14849,7 +14857,7 @@
     </row>
     <row r="694" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A694" s="23"/>
-      <c r="B694" s="20" t="s">
+      <c r="B694" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C694" s="9"/>
@@ -14885,7 +14893,7 @@
     </row>
     <row r="695" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A695" s="23"/>
-      <c r="B695" s="20"/>
+      <c r="B695" s="21"/>
       <c r="C695" s="9"/>
       <c r="D695" s="15"/>
       <c r="E695" s="3" t="str">
@@ -14903,7 +14911,7 @@
     </row>
     <row r="696" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A696" s="23"/>
-      <c r="B696" s="20"/>
+      <c r="B696" s="21"/>
       <c r="C696" s="9"/>
       <c r="D696" s="15"/>
       <c r="E696" s="3" t="str">
@@ -14921,7 +14929,7 @@
     </row>
     <row r="697" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A697" s="23"/>
-      <c r="B697" s="20"/>
+      <c r="B697" s="21"/>
       <c r="C697" s="9"/>
       <c r="D697" s="15"/>
       <c r="E697" s="3" t="str">
@@ -14941,7 +14949,7 @@
       <c r="A698" s="23">
         <v>46142</v>
       </c>
-      <c r="B698" s="21" t="s">
+      <c r="B698" s="22" t="s">
         <v>0</v>
       </c>
       <c r="C698" s="3" t="str" cm="1">
@@ -14981,7 +14989,7 @@
     </row>
     <row r="699" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A699" s="23"/>
-      <c r="B699" s="21"/>
+      <c r="B699" s="22"/>
       <c r="C699" s="3" t="str">
         <v>Abdus Sattar (LM)</v>
       </c>
@@ -15003,7 +15011,7 @@
     </row>
     <row r="700" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A700" s="23"/>
-      <c r="B700" s="21"/>
+      <c r="B700" s="22"/>
       <c r="C700" s="3" t="str">
         <v>Sazzad  (LM)</v>
       </c>
@@ -15025,7 +15033,7 @@
     </row>
     <row r="701" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A701" s="23"/>
-      <c r="B701" s="21"/>
+      <c r="B701" s="22"/>
       <c r="C701" s="3" t="str">
         <v>Jonny (LH)</v>
       </c>
@@ -15047,7 +15055,7 @@
     </row>
     <row r="702" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A702" s="23"/>
-      <c r="B702" s="21"/>
+      <c r="B702" s="22"/>
       <c r="C702" s="3" t="str">
         <v>Nazmul (LEM)</v>
       </c>
@@ -15061,12 +15069,12 @@
     </row>
     <row r="703" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A703" s="23"/>
-      <c r="B703" s="21"/>
+      <c r="B703" s="22"/>
       <c r="C703" s="3" t="str">
-        <v>Driver - Shetu</v>
+        <v>Driver - Hasan</v>
       </c>
       <c r="D703" s="13" t="str">
-        <v>01719034964</v>
+        <v>01730824934</v>
       </c>
       <c r="E703" s="3"/>
       <c r="F703" s="17"/>
@@ -15077,13 +15085,13 @@
     </row>
     <row r="704" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A704" s="23"/>
-      <c r="B704" s="21"/>
+      <c r="B704" s="22"/>
       <c r="C704" s="5" t="str">
-        <f t="shared" ref="C704:D704" si="132">E697</f>
+        <f t="shared" ref="C704:D704" si="127">E697</f>
         <v>Driver - Noyon</v>
       </c>
       <c r="D704" s="17" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="127"/>
         <v>01748127818</v>
       </c>
       <c r="E704" s="3"/>
@@ -15095,7 +15103,7 @@
     </row>
     <row r="705" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A705" s="23"/>
-      <c r="B705" s="21"/>
+      <c r="B705" s="22"/>
       <c r="E705" s="3"/>
       <c r="F705" s="17"/>
       <c r="G705" s="3"/>
@@ -15107,7 +15115,7 @@
     </row>
     <row r="706" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A706" s="23"/>
-      <c r="B706" s="21"/>
+      <c r="B706" s="22"/>
       <c r="E706" s="3"/>
       <c r="F706" s="17"/>
       <c r="G706" s="3"/>
@@ -15119,7 +15127,7 @@
     </row>
     <row r="707" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A707" s="23"/>
-      <c r="B707" s="21"/>
+      <c r="B707" s="22"/>
       <c r="C707" s="5"/>
       <c r="D707" s="13"/>
       <c r="E707" s="3"/>
@@ -15133,7 +15141,7 @@
     </row>
     <row r="708" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A708" s="23"/>
-      <c r="B708" s="22" t="s">
+      <c r="B708" s="24" t="s">
         <v>1</v>
       </c>
       <c r="C708" s="6" t="str" cm="1">
@@ -15173,7 +15181,7 @@
     </row>
     <row r="709" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A709" s="23"/>
-      <c r="B709" s="22"/>
+      <c r="B709" s="24"/>
       <c r="C709" s="6" t="str">
         <v>Monzur Kader (LM)</v>
       </c>
@@ -15195,7 +15203,7 @@
     </row>
     <row r="710" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A710" s="23"/>
-      <c r="B710" s="22"/>
+      <c r="B710" s="24"/>
       <c r="C710" s="6" t="str">
         <v>Mosaddek  (LM)</v>
       </c>
@@ -15217,7 +15225,7 @@
     </row>
     <row r="711" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A711" s="23"/>
-      <c r="B711" s="22"/>
+      <c r="B711" s="24"/>
       <c r="C711" s="6" t="str">
         <v>Abdus Salam (LM)</v>
       </c>
@@ -15239,7 +15247,7 @@
     </row>
     <row r="712" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A712" s="23"/>
-      <c r="B712" s="22"/>
+      <c r="B712" s="24"/>
       <c r="C712" s="6" t="str">
         <v>Salim Reza-2 (LH)</v>
       </c>
@@ -15257,7 +15265,7 @@
     </row>
     <row r="713" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A713" s="23"/>
-      <c r="B713" s="22"/>
+      <c r="B713" s="24"/>
       <c r="C713" s="6"/>
       <c r="D713" s="14"/>
       <c r="E713" s="6"/>
@@ -15271,7 +15279,7 @@
     </row>
     <row r="714" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A714" s="23"/>
-      <c r="B714" s="22"/>
+      <c r="B714" s="24"/>
       <c r="C714" s="6" t="str" cm="1">
         <f t="array" ref="C714:D714">E701:F701</f>
         <v>Driver - Hasan</v>
@@ -15290,7 +15298,7 @@
     </row>
     <row r="715" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A715" s="23"/>
-      <c r="B715" s="22"/>
+      <c r="B715" s="24"/>
       <c r="C715" s="8"/>
       <c r="D715" s="14"/>
       <c r="E715" s="6"/>
@@ -15304,7 +15312,7 @@
     </row>
     <row r="716" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A716" s="23"/>
-      <c r="B716" s="22"/>
+      <c r="B716" s="24"/>
       <c r="C716" s="8"/>
       <c r="D716" s="14"/>
       <c r="E716" s="6"/>
@@ -15318,7 +15326,7 @@
     </row>
     <row r="717" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A717" s="23"/>
-      <c r="B717" s="22"/>
+      <c r="B717" s="24"/>
       <c r="C717" s="8"/>
       <c r="D717" s="14"/>
       <c r="G717" s="6"/>
@@ -15330,7 +15338,7 @@
     </row>
     <row r="718" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A718" s="23"/>
-      <c r="B718" s="20" t="s">
+      <c r="B718" s="21" t="s">
         <v>2</v>
       </c>
       <c r="C718" s="9"/>
@@ -15365,7 +15373,7 @@
     </row>
     <row r="719" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A719" s="23"/>
-      <c r="B719" s="20"/>
+      <c r="B719" s="21"/>
       <c r="C719" s="9"/>
       <c r="D719" s="15"/>
       <c r="E719" s="3" t="str">
@@ -15383,7 +15391,7 @@
     </row>
     <row r="720" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A720" s="23"/>
-      <c r="B720" s="20"/>
+      <c r="B720" s="21"/>
       <c r="C720" s="9"/>
       <c r="D720" s="15"/>
       <c r="E720" s="3" t="str">
@@ -15401,7 +15409,7 @@
     </row>
     <row r="721" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A721" s="23"/>
-      <c r="B721" s="20"/>
+      <c r="B721" s="21"/>
       <c r="C721" s="9"/>
       <c r="D721" s="15"/>
       <c r="E721" s="3" t="str">

--- a/Duty.xlsx
+++ b/Duty.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B469DDF3-590B-410B-A978-F087DB27F1ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352083B6-F857-44A1-9CDA-BD503E9F0D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="9960" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team1" sheetId="1" r:id="rId1"/>
@@ -781,35 +781,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B2" s="17" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B4" s="16" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -827,35 +827,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>40</v>
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B3" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B4" s="17" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -873,35 +873,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>6</v>
+      <c r="A1" s="5" t="s">
+        <v>8</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B4" s="15" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Duty.xlsx
+++ b/Duty.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{352083B6-F857-44A1-9CDA-BD503E9F0D0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CFC392-CCEE-4F48-A575-8DEF81089194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="9960" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Duty.xlsx
+++ b/Duty.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8CFC392-CCEE-4F48-A575-8DEF81089194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87516329-5DCA-4ACC-8C6A-C2BDE189DB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="9960" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team1" sheetId="1" r:id="rId1"/>
@@ -645,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" style="2" customWidth="1"/>
@@ -663,51 +663,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>13</v>
+      <c r="A1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>21</v>
+      <c r="A4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>56</v>
+      <c r="A5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207F2025-39CC-4B78-8E55-B501FA54C7DA}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -727,43 +719,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>20</v>
+      <c r="A1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>14</v>
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>19</v>
+      <c r="A5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>

--- a/Duty.xlsx
+++ b/Duty.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87516329-5DCA-4ACC-8C6A-C2BDE189DB4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EBF7CD-21E7-4F28-BDC9-E440FFC812AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Team1" sheetId="1" r:id="rId1"/>
-    <sheet name="Team2" sheetId="2" r:id="rId2"/>
+    <sheet name="Team1" sheetId="2" r:id="rId1"/>
+    <sheet name="Team2" sheetId="1" r:id="rId2"/>
     <sheet name="Team3" sheetId="3" r:id="rId3"/>
     <sheet name="Team4" sheetId="4" r:id="rId4"/>
     <sheet name="Team5" sheetId="5" r:id="rId5"/>
@@ -644,8 +644,62 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207F2025-39CC-4B78-8E55-B501FA54C7DA}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="20.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" style="2" customWidth="1"/>
@@ -663,111 +717,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>20</v>
+      <c r="A1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>14</v>
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>19</v>
+      <c r="A5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{207F2025-39CC-4B78-8E55-B501FA54C7DA}">
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="20.109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/Duty.xlsx
+++ b/Duty.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80EBF7CD-21E7-4F28-BDC9-E440FFC812AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3246983-480D-45DD-94A5-E02E4F1DCA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2688" yWindow="2688" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="9960" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team1" sheetId="2" r:id="rId1"/>
@@ -286,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -296,17 +296,12 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -656,7 +651,7 @@
       <c r="A1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -664,7 +659,7 @@
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>16</v>
       </c>
     </row>
@@ -672,7 +667,7 @@
       <c r="A3" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>12</v>
       </c>
     </row>
@@ -680,7 +675,7 @@
       <c r="A4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>14</v>
       </c>
     </row>
@@ -688,7 +683,7 @@
       <c r="A5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="11" t="s">
         <v>19</v>
       </c>
     </row>
@@ -705,9 +700,9 @@
     <col min="1" max="1" width="18.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" customWidth="1"/>
     <col min="3" max="3" width="23.21875" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="11" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="9" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" style="14" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" style="12" customWidth="1"/>
     <col min="7" max="7" width="14.21875" customWidth="1"/>
     <col min="8" max="8" width="14.6640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="16.5546875" customWidth="1"/>
@@ -720,7 +715,7 @@
       <c r="A1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>13</v>
       </c>
     </row>
@@ -728,7 +723,7 @@
       <c r="A2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>15</v>
       </c>
     </row>
@@ -736,7 +731,7 @@
       <c r="A3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>17</v>
       </c>
     </row>
@@ -744,7 +739,7 @@
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="10" t="s">
         <v>21</v>
       </c>
     </row>
@@ -752,7 +747,7 @@
       <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -781,18 +776,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="11" t="s">
         <v>44</v>
       </c>
     </row>
@@ -800,7 +795,7 @@
       <c r="A3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="11" t="s">
         <v>41</v>
       </c>
     </row>
@@ -808,7 +803,7 @@
       <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="11" t="s">
         <v>42</v>
       </c>
     </row>
@@ -830,7 +825,7 @@
       <c r="A1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="11" t="s">
         <v>45</v>
       </c>
     </row>
@@ -838,7 +833,7 @@
       <c r="A2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>40</v>
       </c>
     </row>
@@ -846,15 +841,15 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="11" t="s">
         <v>46</v>
       </c>
     </row>
@@ -876,7 +871,7 @@
       <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="11" t="s">
         <v>32</v>
       </c>
     </row>
@@ -884,7 +879,7 @@
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="11" t="s">
         <v>38</v>
       </c>
     </row>
@@ -892,7 +887,7 @@
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="11" t="s">
         <v>35</v>
       </c>
     </row>
@@ -900,7 +895,7 @@
       <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="11" t="s">
         <v>39</v>
       </c>
     </row>
@@ -922,7 +917,7 @@
       <c r="A1" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -930,7 +925,7 @@
       <c r="A2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -938,7 +933,7 @@
       <c r="A3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="11" t="s">
         <v>52</v>
       </c>
     </row>
@@ -957,26 +952,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="11" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="11" t="s">
         <v>52</v>
       </c>
     </row>
@@ -998,7 +993,7 @@
       <c r="A1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1006,7 +1001,7 @@
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="11" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1014,7 +1009,7 @@
       <c r="A3" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="11" t="s">
         <v>52</v>
       </c>
     </row>

--- a/Duty.xlsx
+++ b/Duty.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3246983-480D-45DD-94A5-E02E4F1DCA75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A97C6E-10BF-48D3-980F-D473F99C4D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="9960" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team1" sheetId="2" r:id="rId1"/>
@@ -33,10 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
-  <si>
-    <t>Jonny (LH)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
   <si>
     <t>Abdus Sattar (LM)</t>
   </si>
@@ -204,6 +201,9 @@
   </si>
   <si>
     <t>01723504940</t>
+  </si>
+  <si>
+    <t>Jonny (LM)</t>
   </si>
 </sst>
 </file>
@@ -649,42 +649,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>0</v>
+      <c r="A4" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -713,50 +713,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -777,34 +777,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>3</v>
+      <c r="A4" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -814,43 +814,49 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABA7064-F399-4AE7-AFEC-768265339322}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" customWidth="1"/>
     <col min="2" max="2" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="11" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -860,43 +866,49 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FCE66EE-E88A-440B-ACE4-1BD9EDA010E0}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.109375" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="B3" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>33</v>
+      <c r="E3" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -915,26 +927,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>51</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -953,26 +965,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -991,26 +1003,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/Duty.xlsx
+++ b/Duty.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A97C6E-10BF-48D3-980F-D473F99C4D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC289DC-4ED9-4EB6-A449-F8534299885A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team1" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
+  <si>
+    <t>Jonny (LH)</t>
+  </si>
   <si>
     <t>Abdus Sattar (LM)</t>
   </si>
@@ -201,9 +204,6 @@
   </si>
   <si>
     <t>01723504940</t>
-  </si>
-  <si>
-    <t>Jonny (LM)</t>
   </si>
 </sst>
 </file>
@@ -286,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -296,12 +296,17 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -649,42 +654,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>19</v>
+        <v>26</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>11</v>
+        <v>28</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>18</v>
+      <c r="A5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -700,9 +705,9 @@
     <col min="1" max="1" width="18.6640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" customWidth="1"/>
     <col min="3" max="3" width="23.21875" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="11" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="14.5546875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" style="14" customWidth="1"/>
     <col min="7" max="7" width="14.21875" customWidth="1"/>
     <col min="8" max="8" width="14.6640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="16.5546875" customWidth="1"/>
@@ -713,50 +718,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>12</v>
+        <v>22</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>14</v>
+        <v>23</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>16</v>
+        <v>27</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>20</v>
+        <v>5</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>17</v>
+        <v>24</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -776,35 +781,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>42</v>
+      <c r="A1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>43</v>
+      <c r="A2" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>40</v>
+        <v>36</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>34</v>
+      <c r="A4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -814,49 +819,43 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ABA7064-F399-4AE7-AFEC-768265339322}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.21875" customWidth="1"/>
     <col min="2" max="2" width="15.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>45</v>
+      <c r="B4" s="13" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -866,49 +865,43 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FCE66EE-E88A-440B-ACE4-1BD9EDA010E0}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.109375" customWidth="1"/>
     <col min="2" max="2" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>41</v>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -927,26 +920,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="11" t="s">
         <v>47</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="11" t="s">
         <v>51</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -964,27 +957,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>47</v>
+      <c r="A1" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>47</v>
+      <c r="A2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>51</v>
+      <c r="A3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1003,26 +996,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>47</v>
+        <v>10</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>51</v>
+        <v>34</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/Duty.xlsx
+++ b/Duty.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC289DC-4ED9-4EB6-A449-F8534299885A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E5967A-5E93-4944-88ED-0595D508E03F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team1" sheetId="2" r:id="rId1"/>
@@ -62,9 +62,6 @@
     <t>Driver - Hasan</t>
   </si>
   <si>
-    <t>Moin Uddin</t>
-  </si>
-  <si>
     <t>Abul Kalam Azad</t>
   </si>
   <si>
@@ -204,6 +201,9 @@
   </si>
   <si>
     <t>01723504940</t>
+  </si>
+  <si>
+    <t>Sattar</t>
   </si>
 </sst>
 </file>
@@ -654,10 +654,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -665,31 +665,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -718,26 +718,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -745,23 +745,23 @@
         <v>5</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -785,23 +785,23 @@
         <v>4</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -809,7 +809,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -828,10 +828,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -847,15 +847,15 @@
         <v>7</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -877,7 +877,7 @@
         <v>8</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -885,7 +885,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -893,15 +893,15 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -920,26 +920,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>51</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -958,26 +958,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -996,26 +996,26 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
